--- a/docs/test-cases/SPM-50_Test_Cases.xlsx
+++ b/docs/test-cases/SPM-50_Test_Cases.xlsx
@@ -597,7 +597,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Reserved and Partially fulfilled cannot be chosen by hand, and a reserved line can only become Unavailable</t>
+          <t>Reserved and Partially fulfilled cannot be chosen by hand, and a reserved line can only become 'Cannot be provided'</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -629,7 +629,7 @@
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Line marked Unavailable can be reopened to Under review</t>
+          <t>Line marked 'Cannot be provided' can be reopened to Under review</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Marking an item Unavailable without a real reason is blocked</t>
+          <t>Marking an item 'Cannot be provided' without a real reason is blocked</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Marking a reserved line Unavailable releases its reserved units</t>
+          <t>Marking a reserved line 'Cannot be provided' releases its units, and reserving it again clears the old reason</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -1407,7 +1407,7 @@
         <is>
           <t>1. Open the equipment request for the Robotics Expo event
 2. On the Confidence Monitor line, click 'Update'
-3. In 'Fulfilment status', choose 'Unavailable'
+3. In 'Fulfilment status', choose 'Cannot be provided'
 4. Paste the 501-character test text into 'Technical notes'
 5. Click 'Save'
 6. Delete one character, leaving 500
@@ -1437,7 +1437,7 @@
       <c r="B6" s="13" t="inlineStr">
         <is>
           <t>Step 5: The error 'Technical notes must be 500 characters or fewer.' is shown under Technical notes. The Status chip still shows 'Requested' and nothing is saved.
-Step 7: 'Update saved.' appears and the Status chip shows 'Unavailable'.
+Step 7: 'Update saved.' appears and the Status chip shows 'Cannot be provided'.
 Step 8: All 500 characters are shown in the line's technical notes; nothing is cut off.</t>
         </is>
       </c>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Run TC05 first: Robotics Expo's Confidence Monitor is 'Unavailable' with a reason.
+          <t>Run TC05 first: Robotics Expo's Confidence Monitor is 'Cannot be provided' with a reason.
 Logged in as the assigned Coordinator, daniel.tan@connectsphere.com (password123).</t>
         </is>
       </c>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Step 4: Confidence Monitor shows the status chip 'Unavailable' and 'Technical Support notes: Only 1 working unit; suggest 2x 55-inch TV on stands as an alternative'. The notes are read-only for the Coordinator; their own Quantity and Technical requirements fields are still editable.</t>
+          <t>Step 4: Confidence Monitor shows the status chip 'Cannot be provided' and 'Technical Support notes: Only 1 working unit; suggest 2x 55-inch TV on stands as an alternative'. The notes are read-only for the Coordinator; their own Quantity and Technical requirements fields are still editable.</t>
         </is>
       </c>
     </row>
@@ -1720,7 +1720,7 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Run TC05 first: Robotics Expo's Confidence Monitor is 'Unavailable' with a reason.
+          <t>Run TC05 first: Robotics Expo's Confidence Monitor is 'Cannot be provided' with a reason.
 Event 'Design Week' also requests 'Confidence Monitor' x1, status 'Requested', no notes.
 Logged in as Technical Support Staff (vikram.nair@connectsphere.com, password123).</t>
         </is>
@@ -1752,7 +1752,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="44.5" customHeight="1">
+    <row r="6" ht="58" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Step 3: Design Week's Confidence Monitor line still shows 'Requested' with no Technical Support notes. The 'Unavailable' status and reason from Robotics Expo do not appear here.</t>
+          <t>Step 3: Design Week's Confidence Monitor line still shows 'Requested' with no Technical Support notes. The 'Cannot be provided' status and reason from Robotics Expo do not appear here.</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2369,24 +2369,24 @@
       </c>
       <c r="C2" s="11" t="n"/>
     </row>
-    <row r="3" ht="71.5" customHeight="1">
+    <row r="3" ht="85" customHeight="1">
       <c r="A3" s="11" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>OPEN - Reserve button on an Unavailable line: with the current SPM-49 code (canOfferReserve), an Unavailable line still offers Reserve once stock frees up. Both options are consistent. Allowing it is more convenient; requiring a reopen to 'Under review' first (TC04) is more deliberate. Product call, so no case is written until it is decided.</t>
+          <t>DECIDED (Janelle, 2 Oct) - Reserve stays on a line marked 'Cannot be provided': if stock frees up, Technical Support can reserve it in one click. Reserving it clears the old 'cannot be provided' reason, so the line never shows 'Reserved' next to a reason that no longer holds (TC07; reserveClearsStaffNotes() in src/lib/equipmentFulfilment.ts, used by the SPM-49 reserve route).</t>
         </is>
       </c>
       <c r="C3" s="11" t="n"/>
     </row>
-    <row r="4" ht="71.5" customHeight="1">
+    <row r="4" ht="58" customHeight="1">
       <c r="A4" s="11" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>OPEN - getting from the Equipment request page to the event: Technical Support has no Events item in the side menu, and the Equipment request page has no link to the event. The page now shows the Coordinator's technical requirements, so Technical Support may never need to leave it, and no test case depends on the link. Team to confirm.</t>
+          <t>DECIDED (Janelle, 2 Oct) - no link from the Equipment request page back to the event. The page shows everything Technical Support needs (the Coordinator's requirements, status, notes), and no test case depends on the link.</t>
         </is>
       </c>
       <c r="C4" s="11" t="n"/>
@@ -2402,13 +2402,13 @@
       </c>
       <c r="C5" s="11" t="n"/>
     </row>
-    <row r="6" ht="112" customHeight="1">
+    <row r="6" ht="166" customHeight="1">
       <c r="A6" s="11" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>OPEN - fulfilment status vs approve/reject (Kristen's comment on the ticket): venue booking has request then approve/reject (SPM-42 then SPM-43), but equipment goes record, check, reserve (SPM-47, 48, 49) with fulfilment statuses. Every story in the SPM-47 to SPM-50 chain is written against the fulfilment-status model, so switching would mean revisiting ACs on shipped stories. Team to confirm the divergence is intentional; meanwhile these cases follow the model already used across the chain.</t>
+          <t>OPEN (answered by customer Q&amp;A #19) - fulfilment status vs approve/reject (Kristen's comment on the ticket): venue booking has request then approve/reject (SPM-42 then SPM-43), but equipment goes record, check, reserve (SPM-47, 48, 49) with fulfilment statuses. Every story in the SPM-47 to SPM-50 chain is written against the fulfilment-status model, so switching would mean revisiting ACs on shipped stories. Team to confirm the divergence is intentional; meanwhile these cases follow the model already used across the chain. Customer Q&amp;A #19 asked whether equipment has a formal request → approval workflow like venue booking: the answer is that the Coordinator records the requirement, Technical Support reviews suitability and availability, and available equipment can then be reserved - no approval step.</t>
         </is>
       </c>
       <c r="C6" s="11" t="n"/>
@@ -2435,57 +2435,57 @@
       </c>
       <c r="C8" s="11" t="n"/>
     </row>
-    <row r="9" ht="85" customHeight="1">
+    <row r="9" ht="98.5" customHeight="1">
       <c r="A9" s="11" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>DECIDED - hand-pickable statuses (TC02, TC03): 'Reserved' and 'Partially fulfilled' are set only by the Reserve button, which keeps Reserved = the smaller of requested and available everywhere (the SPM-49 rule). 'Requested' can be chosen to undo 'Under review'. A Reserved or Partially fulfilled line cannot be moved back to 'Requested' or 'Under review'; leaving it goes through 'Unavailable' with a reason.</t>
+          <t>DECIDED (Janelle, 2 Oct) - labels: the request status 'unavailable' is shown as 'Cannot be provided' (Technical Support's decision) and the availability result 'unavailable' as 'None available' (no stock free for those dates), so the two never read the same on one line. Only the displayed text changed; the stored value is still 'unavailable'. Differs from the S-25 mockup, which says 'Unavailable'. SPM-48/49 expected results updated to match.</t>
         </is>
       </c>
       <c r="C9" s="11" t="n"/>
     </row>
-    <row r="10" ht="44.5" customHeight="1">
+    <row r="10" ht="85" customHeight="1">
       <c r="A10" s="11" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>DECIDED - reason for Unavailable (TC06, TC09): required, as Q&amp;A #90 needs text the Coordinator can act on. Technical notes are capped at 500 characters to match SPM-55's out-of-service reason.</t>
+          <t>DECIDED - hand-pickable statuses (TC02, TC03): 'Reserved' and 'Partially fulfilled' are set only by the Reserve button, which keeps Reserved = the smaller of requested and available everywhere (the SPM-49 rule). 'Requested' can be chosen to undo 'Under review'. A Reserved or Partially fulfilled line cannot be moved back to 'Requested' or 'Under review'; leaving it goes through 'Cannot be provided' with a reason.</t>
         </is>
       </c>
       <c r="C10" s="11" t="n"/>
     </row>
-    <row r="11" ht="112" customHeight="1">
+    <row r="11" ht="44.5" customHeight="1">
       <c r="A11" s="11" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>DECIDED - releasing stock when a line is marked Unavailable (TC07): availability counts only lines with status 'reserved' or 'partially_fulfilled' (committedQuantity in src/lib/equipmentAvailability.ts), so the status change alone frees the units, whatever is left in quantityReserved. TC07 therefore checks the other event's availability, not the stored field. Clearing quantityReserved when marking Unavailable is still recommended as data hygiene, so no row reads 'unavailable' with 1 reserved, but it is not needed for correctness.</t>
+          <t>DECIDED - reason for 'Cannot be provided' (TC06, TC09): required, as Q&amp;A #90 needs text the Coordinator can act on. Technical notes are capped at 500 characters to match SPM-55's out-of-service reason.</t>
         </is>
       </c>
       <c r="C11" s="11" t="n"/>
     </row>
-    <row r="12" ht="58" customHeight="1">
+    <row r="12" ht="112" customHeight="1">
       <c r="A12" s="11" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>DECIDED - technical notes storage (TC08, TC10): stored in the existing EquipmentRequest.staffNotes column, separate from the Coordinator's technicalRequirements. The assigned Coordinator and the owning Organiser see them read-only.</t>
+          <t>DECIDED - releasing stock when a line is marked 'Cannot be provided' (TC07): availability counts only lines with status 'reserved' or 'partially_fulfilled' (committedQuantity in src/lib/equipmentAvailability.ts), so the status change alone frees the units, whatever is left in quantityReserved. TC07 therefore checks the other event's availability, not the stored field. Clearing quantityReserved when marking 'Cannot be provided' is still recommended as data hygiene, so no row reads 'unavailable' with 1 reserved, but it is not needed for correctness.</t>
         </is>
       </c>
       <c r="C12" s="11" t="n"/>
     </row>
-    <row r="13" ht="44.5" customHeight="1">
+    <row r="13" ht="58" customHeight="1">
       <c r="A13" s="11" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>ANSWERED, out of scope - notifying the Coordinator when an item is marked Unavailable belongs to the batched notification story, so no case is written here (same position as SPM-49).</t>
+          <t>DECIDED - technical notes storage (TC08, TC10): stored in the existing EquipmentRequest.staffNotes column, separate from the Coordinator's technicalRequirements. The assigned Coordinator and the owning Organiser see them read-only.</t>
         </is>
       </c>
       <c r="C13" s="11" t="n"/>
@@ -2496,21 +2496,32 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>BUILT (AC1) - the Equipment request page now shows each line's 'Technical requirements' from the Coordinator, 'Technical Support notes', and 'Last updated by' (TC01, TC08, TC08).</t>
+          <t>ANSWERED, out of scope - notifying the Coordinator when an item is marked 'Cannot be provided' belongs to the batched notification story, so no case is written here (same position as SPM-49).</t>
         </is>
       </c>
       <c r="C14" s="11" t="n"/>
     </row>
-    <row r="15" ht="85" customHeight="1">
+    <row r="15" ht="44.5" customHeight="1">
       <c r="A15" s="11" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
+          <t>BUILT (AC1) - the Equipment request page now shows each line's 'Technical requirements' from the Coordinator, 'Technical Support notes', and 'Last updated by' (TC01, TC08, TC08).</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="n"/>
+    </row>
+    <row r="16" ht="85" customHeight="1">
+      <c r="A16" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
           <t>Test data - `npm run fixtures:spm50` (scripts/seed-spm50.ts) creates or resets the SPM-50 events: Robotics Expo, Design Week, Charity Briefing, Charity Gala, Cancelled Hackathon and Pending Showcase (Aug-Sep 2027, assigned Coordinator daniel.tan, Robotics Expo owned by Rachel Ng). prisma/seed.ts creates the same rows. Run the script again before repeating any case that saves a change.</t>
         </is>
       </c>
-      <c r="C15" s="11" t="n"/>
+      <c r="C16" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2898,7 +2909,7 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Rule (team decision): 'Reserved' and 'Partially fulfilled' mean stock is held, so only the Reserve button (SPM-49), which checks availability, can set them. Leaving them releases stock, so a reserved line can only be marked 'Unavailable' (with a reason, TC07).
+          <t>Rule (team decision): 'Reserved' and 'Partially fulfilled' mean stock is held, so only the Reserve button (SPM-49), which checks availability, can set them. Leaving them releases stock, so a reserved line can only be marked 'Cannot be provided' (with a reason, TC07).
 Robotics Expo's Wireless Presenter line is 'Requested'. Charity Briefing's Mobile Charging Cart line is 'Reserved' (Reserved = 1).
 Data: run `npm run fixtures:spm50` first.
 Logged in as Technical Support Staff (vikram.nair@connectsphere.com, password123).</t>
@@ -2943,8 +2954,8 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Step 3: The list offers 'Requested', 'Under review' and 'Unavailable' only. 'Reserved' and 'Partially fulfilled' are not offered. The Reserve button remains on the line.
-Step 7: The list offers 'Reserved' (the current status) and 'Unavailable' only. 'Requested' and 'Under review' are not offered.</t>
+          <t>Step 3: The list offers 'Requested', 'Under review' and 'Cannot be provided' only. 'Reserved' and 'Partially fulfilled' are not offered. The Reserve button remains on the line.
+Step 7: The list offers 'Reserved' (the current status) and 'Cannot be provided' only. 'Requested' and 'Under review' are not offered.</t>
         </is>
       </c>
     </row>
@@ -3065,7 +3076,7 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Event 'Design Week' (2027-08-16, status 'Planning') has a 'Ring Light' x2 line already marked 'Unavailable' with technical notes 'Both units out for repair'.
+          <t>Event 'Design Week' (2027-08-16, status 'Planning') has a 'Ring Light' x2 line already marked 'Cannot be provided' with technical notes 'Both units out for repair'.
 Data: run `npm run fixtures:spm50` first, and again before repeating the case.
 Logged in as Technical Support Staff (vikram.nair@connectsphere.com, password123).</t>
         </is>
@@ -3095,7 +3106,7 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Fulfilment status: Unavailable -&gt; Under review
+          <t>Fulfilment status: Cannot be provided -&gt; Under review
 Technical notes: Repair finished early, re-checking availability</t>
         </is>
       </c>
@@ -3245,7 +3256,7 @@
         <is>
           <t>1. Open the equipment request for the Robotics Expo event
 2. On the Confidence Monitor line, click 'Update'
-3. In 'Fulfilment status', choose 'Unavailable'
+3. In 'Fulfilment status', choose 'Cannot be provided'
 4. In 'Technical notes', enter the test data
 5. Click 'Save'
 6. Refresh the page
@@ -3261,7 +3272,7 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Fulfilment status: Unavailable
+          <t>Fulfilment status: Cannot be provided
 Technical notes: Only 1 working unit; suggest 2x 55-inch TV on stands as an alternative</t>
         </is>
       </c>
@@ -3274,8 +3285,8 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Step 5: 'Update saved.' appears. The Status chip shows 'Unavailable' (red).
-Step 6: The Status chip still shows 'Unavailable' and the notes 'Only 1 working unit; suggest 2x 55-inch TV on stands as an alternative' are shown on the line after 'Technical Support notes:'.
+          <t>Step 5: 'Update saved.' appears. The Status chip shows 'Cannot be provided' (red).
+Step 6: The Status chip still shows 'Cannot be provided' and the notes 'Only 1 working unit; suggest 2x 55-inch TV on stands as an alternative' are shown on the line after 'Technical Support notes:'.
 Step 7: The Wireless Presenter line still shows the Status chip 'Requested' and no Technical Support notes. Because the lines are no longer at the same stage, the 'Requested items' header shows no single status chip.</t>
         </is>
       </c>
@@ -3413,7 +3424,7 @@
         <is>
           <t>1. Open the equipment request for the Robotics Expo event
 2. On the Confidence Monitor line, click 'Update'
-3. In 'Fulfilment status', choose 'Unavailable'
+3. In 'Fulfilment status', choose 'Cannot be provided'
 4. Leave 'Technical notes' empty
 5. Click 'Save'
 6. In 'Technical notes', type three spaces
@@ -3429,7 +3440,7 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Fulfilment status: Unavailable
+          <t>Fulfilment status: Cannot be provided
 Technical notes: (empty), then '   ' (3 spaces)</t>
         </is>
       </c>
@@ -3564,7 +3575,7 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Rule: only lines with status 'Reserved' or 'Partially fulfilled' count against stock, so changing the status to 'Unavailable' frees the units by itself.
+          <t>Rule: only lines with status 'Reserved' or 'Partially fulfilled' count against stock, so changing the status to 'Cannot be provided' frees the units by itself.
 'Mobile Charging Cart' has 1 unit in total.
 Event 'Charity Briefing' (2027-08-23) has 1x Mobile Charging Cart already 'Reserved' (Reserved = 1).
 Event 'Charity Gala' (same date, overlapping times) requests 1x Mobile Charging Cart, status 'Requested'.
@@ -3573,7 +3584,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="125.5" customHeight="1">
+    <row r="4" ht="152.5" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -3585,10 +3596,12 @@
 2. Read the Mobile Charging Cart line
 3. Click Equipment Requests in the breadcrumb and open the Charity Briefing event
 4. On the Mobile Charging Cart line, click 'Update'
-5. In 'Fulfilment status', choose 'Unavailable'
+5. In 'Fulfilment status', choose 'Cannot be provided'
 6. In 'Technical notes', enter the test data
 7. Click 'Save'
-8. Go back to the Charity Gala equipment request</t>
+8. Go back to the Charity Gala equipment request
+9. Go back to the Charity Briefing equipment request
+10. Click Reserve on the Mobile Charging Cart line</t>
         </is>
       </c>
     </row>
@@ -3605,7 +3618,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="139" customHeight="1">
+    <row r="6" ht="206.5" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -3613,9 +3626,10 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Step 2: Charity Gala's line shows '1 total − 0 in maintenance − 1 reserved elsewhere = 0 available' and the Availability chip 'Unavailable', with 'Held by Charity Briefing (1 unit)'.
-Step 7: Charity Briefing's line shows the Status chip 'Unavailable'.
-Step 8: Charity Gala's line now shows '1 total − 0 in maintenance − 0 reserved elsewhere = 1 available' with the Availability chip 'Available'. Charity Briefing is no longer listed as holding it, and the Reserve button is offered.</t>
+          <t>Step 2: Charity Gala's line shows '1 total − 0 in maintenance − 1 reserved elsewhere = 0 available' and the Availability chip 'None available', with 'Held by Charity Briefing (1 unit)'.
+Step 7: Charity Briefing's line shows the Status chip 'Cannot be provided'.
+Step 8: Charity Gala's line now shows '1 total − 0 in maintenance − 0 reserved elsewhere = 1 available' with the Availability chip 'Available'. Charity Briefing is no longer listed as holding it, and the Reserve button is offered.
+Step 10: 'Reservation saved: 1 reserved.' appears. The Status chip shows 'Reserved', the Reserved box shows 1, and the line shows 'Technical Support notes: —': the old reason 'Cart battery failed inspection, cannot be sent out' is cleared, because it no longer holds.</t>
         </is>
       </c>
     </row>

--- a/docs/test-cases/SPM-50_Test_Cases.xlsx
+++ b/docs/test-cases/SPM-50_Test_Cases.xlsx
@@ -917,12 +917,12 @@
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Lines on a cancelled event cannot be updated</t>
+          <t>A confirmed event's equipment is shown but cannot be changed</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>AC2, AC3, AC4</t>
+          <t>AC1, AC2, AC3, AC4</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="F16" s="11" t="inlineStr">
         <is>
-          <t>Code</t>
+          <t>Acceptance Criteria</t>
         </is>
       </c>
     </row>
@@ -949,12 +949,12 @@
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Equipment on an event that is not yet approved cannot be updated</t>
+          <t>Technical Support does not see an event's equipment before the Coordinator starts planning</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>AC2, AC3, AC4</t>
+          <t>AC1, AC2</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="F20" s="9" t="n"/>
     </row>
-    <row r="21" ht="17.5" customHeight="1">
+    <row r="21" ht="44.5" customHeight="1">
       <c r="A21" s="11" t="inlineStr">
         <is>
           <t>AC1</t>
@@ -1003,7 +1003,9 @@
       <c r="D21" s="9" t="n"/>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>SPM-50-TC01</t>
+          <t>SPM-50-TC01
+SPM-50-TC13
+SPM-50-TC14</t>
         </is>
       </c>
       <c r="F21" s="9" t="n"/>
@@ -1034,7 +1036,7 @@
       </c>
       <c r="F22" s="9" t="n"/>
     </row>
-    <row r="23" ht="98.5" customHeight="1">
+    <row r="23" ht="85" customHeight="1">
       <c r="A23" s="11" t="inlineStr">
         <is>
           <t>AC3</t>
@@ -1054,13 +1056,12 @@
 SPM-50-TC06
 SPM-50-TC07
 SPM-50-TC09
-SPM-50-TC13
-SPM-50-TC14</t>
+SPM-50-TC13</t>
         </is>
       </c>
       <c r="F23" s="9" t="n"/>
     </row>
-    <row r="24" ht="71.5" customHeight="1">
+    <row r="24" ht="58" customHeight="1">
       <c r="A24" s="11" t="inlineStr">
         <is>
           <t>AC4</t>
@@ -1078,8 +1079,7 @@
           <t>SPM-50-TC08
 SPM-50-TC09
 SPM-50-TC12
-SPM-50-TC13
-SPM-50-TC14</t>
+SPM-50-TC13</t>
         </is>
       </c>
       <c r="F24" s="9" t="n"/>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="58" customHeight="1">
+    <row r="3" ht="139" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -2043,12 +2043,14 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Event 'Cancelled Hackathon' (2027-08-30, status 'Cancelled') requests 2x Wireless Presenter, status 'Requested'.
+          <t>Rule (team decision, 3 Oct, following the BPMN): Technical Support checks, reserves and updates equipment while the event is in Planning. Once the event is Confirmed its equipment is final - they still see it, to prepare it, but a change goes through a change request.
+Event 'Confirmed Launch' (2027-08-30, status 'Confirmed') has 2x Wireless Presenter, status 'Reserved' (Reserved = 2).
+Data: run `npm run fixtures:spm50` first.
 Logged in as Technical Support Staff (vikram.nair@connectsphere.com, password123).</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="71.5" customHeight="1">
+    <row r="4" ht="58" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -2057,8 +2059,8 @@
       <c r="B4" s="13" t="inlineStr">
         <is>
           <t>1. Click Equipment Requests in the side menu
-2. Open the equipment request for the Cancelled Hackathon event
-3. Look for an 'Update' button on the Wireless Presenter line</t>
+2. Open the equipment request for the Confirmed Launch event
+3. Look for an 'Update' or 'Reserve' button on the Wireless Presenter line</t>
         </is>
       </c>
     </row>
@@ -2070,11 +2072,11 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Event status: Cancelled</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="85" customHeight="1">
+          <t>Event status: Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="112" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -2082,9 +2084,9 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Step 1: Cancelled Hackathon is listed with Event status 'Cancelled'.
-Step 2: The page shows 'This event is cancelled — equipment can no longer be reserved.'
-Step 3: No 'Update' button and no Reserve button are shown. The line still shows 'Requested' with Requested 2.</t>
+          <t>Step 1: Confirmed Launch is listed, with Event status 'Confirmed'.
+Step 2: The page shows 'This event is confirmed — its equipment is final. A change now goes through a change request.' The Wireless Presenter line shows the Status chip 'Reserved' and Reserved 2.
+Step 3: No 'Update' button and no 'Reserve' button are shown.</t>
         </is>
       </c>
     </row>
@@ -2197,7 +2199,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="112" customHeight="1">
+    <row r="3" ht="179.5" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -2205,14 +2207,15 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Rule (team decision, 2 Oct): until Operations approves an event, only its Organiser and Coordinator work on it. Technical Support starts once it is Approved.
-Event 'Pending Showcase' (2027-09-06, status 'Under review') requests 1x Wireless Presenter, status 'Requested'.
+          <t>Rule (team decision, 3 Oct, following the BPMN): Technical Support's lane starts after the Coordinator's 'Record equipment request' - in Planning. Before that, the equipment is only part of the organiser's request.
+Event 'Pending Showcase' (2027-09-06, status 'Under review') and event 'Approved Briefing' (2027-09-13, status 'Approved', the Coordinator has not started planning) each request 1x Wireless Presenter.
+Their references (EVT-…) are printed by `npm run fixtures:spm50`.
 Data: run `npm run fixtures:spm50` first.
 Logged in as Technical Support Staff (vikram.nair@connectsphere.com, password123).</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="58" customHeight="1">
+    <row r="4" ht="98.5" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -2221,8 +2224,9 @@
       <c r="B4" s="13" t="inlineStr">
         <is>
           <t>1. Click Equipment Requests in the side menu
-2. Open the equipment request for the Pending Showcase event
-3. Look for an 'Update' button on the Wireless Presenter line</t>
+2. Look for Pending Showcase and Approved Briefing in the list
+3. Type /equipment/requests/&lt;Pending Showcase's reference&gt; into the address bar
+4. Type /equipment/requests/&lt;Approved Briefing's reference&gt; into the address bar</t>
         </is>
       </c>
     </row>
@@ -2234,11 +2238,11 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Event status: Under review</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="58" customHeight="1">
+          <t>Event statuses: Under review, Approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="71.5" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -2246,8 +2250,9 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Step 2: The page shows 'This event is under review — equipment requests can be updated once the event is approved.'
-Step 3: No 'Update' button is shown. The line still shows 'Requested' with Requested 1.</t>
+          <t>Step 2: Neither event is listed.
+Step 3: The page shows 'This event was not found, or its equipment is not ready for Technical Support yet.' No equipment lines, Update or Reserve buttons are shown.
+Step 4: The same message is shown for Approved Briefing.</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2338,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2413,79 +2418,79 @@
       </c>
       <c r="C6" s="11" t="n"/>
     </row>
-    <row r="7" ht="98.5" customHeight="1">
+    <row r="7" ht="166" customHeight="1">
       <c r="A7" s="11" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>IN PROGRESS (Kristen, her status story) - SPM-49's Reserve button is not limited the same way yet: it still works on Submitted and Under review events (eventAllowsReserving in src/lib/equipmentAvailability.ts). Until Kristen's change lands, Pending Showcase (TC14) still offers Reserve while Update is not offered. TC14 checks only the Update button. Her change also needs SPM-49's seeded events moved from 'Under review' to 'Planning'.</t>
+          <t>DECIDED (Kristen, 3 Oct, following the BPMN) - Technical Support sees an event's equipment only in Planning and Confirmed (TECH_SUPPORT_EQUIPMENT_STATUSES): the BPMN's Technical Support lane starts after the Coordinator's 'Record equipment request', with 'Check equipment availability' and 'Reserve equipment' in Planning and 'Prepare equipment' in Confirmed. Checking, reserving and updating happen in Planning only; Confirmed is read-only (TC13). Before Planning - including Approved, when the Coordinator has not started - and after it (postponed, cancelled, rejected, completed) the event is not listed and a direct link says it is not found (TC14). Not in SPM-48/49/50's ACs: a process alignment, applied to all three; supersedes the earlier 'Approved onwards' rule and the Reserve gap.</t>
         </is>
       </c>
       <c r="C7" s="11" t="n"/>
     </row>
-    <row r="8" ht="85" customHeight="1">
+    <row r="8" ht="98.5" customHeight="1">
       <c r="A8" s="11" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>DECIDED (Kristen, 2 Oct) - Technical Support only updates an event's equipment once the event is Approved, Planning or Confirmed (TC14). Before approval only the Organiser and Coordinator work on it, as there is no point arranging equipment for an event that may be rejected. Completed, cancelled, rejected and postponed events cannot be updated either (TC13).</t>
+          <t>DECIDED (Janelle, 2 Oct) - labels: the request status 'unavailable' is shown as 'Cannot be provided' (Technical Support's decision) and the availability result 'unavailable' as 'None available' (no stock free for those dates), so the two never read the same on one line. Only the displayed text changed; the stored value is still 'unavailable'. Differs from the S-25 mockup, which says 'Unavailable'. SPM-48/49 expected results updated to match.</t>
         </is>
       </c>
       <c r="C8" s="11" t="n"/>
     </row>
-    <row r="9" ht="98.5" customHeight="1">
+    <row r="9" ht="85" customHeight="1">
       <c r="A9" s="11" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>DECIDED (Janelle, 2 Oct) - labels: the request status 'unavailable' is shown as 'Cannot be provided' (Technical Support's decision) and the availability result 'unavailable' as 'None available' (no stock free for those dates), so the two never read the same on one line. Only the displayed text changed; the stored value is still 'unavailable'. Differs from the S-25 mockup, which says 'Unavailable'. SPM-48/49 expected results updated to match.</t>
+          <t>DECIDED - hand-pickable statuses (TC02, TC03): 'Reserved' and 'Partially fulfilled' are set only by the Reserve button, which keeps Reserved = the smaller of requested and available everywhere (the SPM-49 rule). 'Requested' can be chosen to undo 'Under review'. A Reserved or Partially fulfilled line cannot be moved back to 'Requested' or 'Under review'; leaving it goes through 'Cannot be provided' with a reason.</t>
         </is>
       </c>
       <c r="C9" s="11" t="n"/>
     </row>
-    <row r="10" ht="85" customHeight="1">
+    <row r="10" ht="44.5" customHeight="1">
       <c r="A10" s="11" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>DECIDED - hand-pickable statuses (TC02, TC03): 'Reserved' and 'Partially fulfilled' are set only by the Reserve button, which keeps Reserved = the smaller of requested and available everywhere (the SPM-49 rule). 'Requested' can be chosen to undo 'Under review'. A Reserved or Partially fulfilled line cannot be moved back to 'Requested' or 'Under review'; leaving it goes through 'Cannot be provided' with a reason.</t>
+          <t>DECIDED - reason for 'Cannot be provided' (TC06, TC09): required, as Q&amp;A #90 needs text the Coordinator can act on. Technical notes are capped at 500 characters to match SPM-55's out-of-service reason.</t>
         </is>
       </c>
       <c r="C10" s="11" t="n"/>
     </row>
-    <row r="11" ht="44.5" customHeight="1">
+    <row r="11" ht="112" customHeight="1">
       <c r="A11" s="11" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>DECIDED - reason for 'Cannot be provided' (TC06, TC09): required, as Q&amp;A #90 needs text the Coordinator can act on. Technical notes are capped at 500 characters to match SPM-55's out-of-service reason.</t>
+          <t>DECIDED - releasing stock when a line is marked 'Cannot be provided' (TC07): availability counts only lines with status 'reserved' or 'partially_fulfilled' (committedQuantity in src/lib/equipmentAvailability.ts), so the status change alone frees the units, whatever is left in quantityReserved. TC07 therefore checks the other event's availability, not the stored field. Clearing quantityReserved when marking 'Cannot be provided' is still recommended as data hygiene, so no row reads 'unavailable' with 1 reserved, but it is not needed for correctness.</t>
         </is>
       </c>
       <c r="C11" s="11" t="n"/>
     </row>
-    <row r="12" ht="112" customHeight="1">
+    <row r="12" ht="58" customHeight="1">
       <c r="A12" s="11" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>DECIDED - releasing stock when a line is marked 'Cannot be provided' (TC07): availability counts only lines with status 'reserved' or 'partially_fulfilled' (committedQuantity in src/lib/equipmentAvailability.ts), so the status change alone frees the units, whatever is left in quantityReserved. TC07 therefore checks the other event's availability, not the stored field. Clearing quantityReserved when marking 'Cannot be provided' is still recommended as data hygiene, so no row reads 'unavailable' with 1 reserved, but it is not needed for correctness.</t>
+          <t>DECIDED - technical notes storage (TC08, TC10): stored in the existing EquipmentRequest.staffNotes column, separate from the Coordinator's technicalRequirements. The assigned Coordinator and the owning Organiser see them read-only.</t>
         </is>
       </c>
       <c r="C12" s="11" t="n"/>
     </row>
-    <row r="13" ht="58" customHeight="1">
+    <row r="13" ht="44.5" customHeight="1">
       <c r="A13" s="11" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>DECIDED - technical notes storage (TC08, TC10): stored in the existing EquipmentRequest.staffNotes column, separate from the Coordinator's technicalRequirements. The assigned Coordinator and the owning Organiser see them read-only.</t>
+          <t>ANSWERED, out of scope - notifying the Coordinator when an item is marked 'Cannot be provided' belongs to the batched notification story, so no case is written here (same position as SPM-49).</t>
         </is>
       </c>
       <c r="C13" s="11" t="n"/>
@@ -2496,32 +2501,21 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>ANSWERED, out of scope - notifying the Coordinator when an item is marked 'Cannot be provided' belongs to the batched notification story, so no case is written here (same position as SPM-49).</t>
+          <t>BUILT (AC1) - the Equipment request page now shows each line's 'Technical requirements' from the Coordinator, 'Technical Support notes', and 'Last updated by' (TC01, TC08, TC08).</t>
         </is>
       </c>
       <c r="C14" s="11" t="n"/>
     </row>
-    <row r="15" ht="44.5" customHeight="1">
+    <row r="15" ht="85" customHeight="1">
       <c r="A15" s="11" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>BUILT (AC1) - the Equipment request page now shows each line's 'Technical requirements' from the Coordinator, 'Technical Support notes', and 'Last updated by' (TC01, TC08, TC08).</t>
+          <t>Test data - `npm run fixtures:spm50` (scripts/seed-spm50.ts) creates or resets the SPM-50 events: Robotics Expo, Design Week, Charity Briefing, Charity Gala, Confirmed Launch, Pending Showcase and Approved Briefing (Aug-Sep 2027, assigned Coordinator daniel.tan, Robotics Expo owned by Rachel Ng). prisma/seed.ts creates the same rows. Run the script again before repeating any case that saves a change.</t>
         </is>
       </c>
       <c r="C15" s="11" t="n"/>
-    </row>
-    <row r="16" ht="85" customHeight="1">
-      <c r="A16" s="11" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="11" t="inlineStr">
-        <is>
-          <t>Test data - `npm run fixtures:spm50` (scripts/seed-spm50.ts) creates or resets the SPM-50 events: Robotics Expo, Design Week, Charity Briefing, Charity Gala, Cancelled Hackathon and Pending Showcase (Aug-Sep 2027, assigned Coordinator daniel.tan, Robotics Expo owned by Rachel Ng). prisma/seed.ts creates the same rows. Run the script again before repeating any case that saves a change.</t>
-        </is>
-      </c>
-      <c r="C16" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/test-cases/SPM-50_Test_Cases.xlsx
+++ b/docs/test-cases/SPM-50_Test_Cases.xlsx
@@ -488,6 +488,7 @@
       <c r="E1" s="8" t="n"/>
       <c r="F1" s="9" t="n"/>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
@@ -968,6 +969,8 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
@@ -1106,6 +1109,7 @@
       </c>
       <c r="F25" s="9" t="n"/>
     </row>
+    <row r="26"/>
     <row r="27" ht="301" customHeight="1">
       <c r="A27" s="7" t="inlineStr">
         <is>
@@ -1268,7 +1272,7 @@
       <c r="B6" s="13" t="inlineStr">
         <is>
           <t>Step 5: 'Update saved.' appears. The Status chip still shows 'Requested'.
-Step 6: The line shows 'Technical Support notes: Presenters need fresh AAA batteries; USB-C dongle is in kit bag 3', separately from 'Technical requirements: Must pair with the stage laptop over USB-C', which is unchanged. It also shows 'Last updated by Vikram Nair, ' followed by the date and time of the save (for example '2 Oct 2026, 14:05').
+Step 6: The line shows 'Technical Support notes: Presenters need fresh AAA batteries; USB-C dongle is in kit bag 3', separately from 'Technical requirements: Must pair with the stage laptop over USB-C', which is unchanged. It also shows 'Last updated by Vikram Nair, ' followed by the date and time of the save (for example '2 Oct 2026, 14:05'). The line's Requested, Reserved, Status and Availability boxes and its 'Update' and 'Reserve' buttons stay on the right of its details, level with the other lines, at any laptop window width - the long note wraps within the details (SPM-102).
 Step 9: 'Update saved.' appears and the line shows 'Technical Support notes: —'. The Status chip still shows 'Requested'.</t>
         </is>
       </c>

--- a/docs/test-cases/SPM-50_Test_Cases.xlsx
+++ b/docs/test-cases/SPM-50_Test_Cases.xlsx
@@ -4,20 +4,21 @@
   <workbookPr/>
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="TC01" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="TC02" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="TC03" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="TC04" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="TC05" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="TC06" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="TC07" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="TC08" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="TC09" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="TC10" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="TC11" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="TC12" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="TC13" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="TC14" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Open Questions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="TC01" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="TC02" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="TC03" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="TC04" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="TC05" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TC06" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="TC07" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="TC08" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="TC09" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="TC10" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="TC11" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="TC12" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="TC13" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="TC14" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -142,7 +143,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -199,6 +200,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -490,12 +497,12 @@
   </cols>
   <sheetData>
     <row r="1" ht="30.75" customHeight="1" s="22">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="25" t="inlineStr">
         <is>
           <t>Story</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="25" t="inlineStr">
         <is>
           <t>SPM-50: As Technical Support Staff, I want to review and update equipment requests so that equipment arrangements accurately reflect what can be provided</t>
         </is>
@@ -507,32 +514,32 @@
     </row>
     <row r="2"/>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="25" t="inlineStr">
         <is>
           <t>Sheet</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="B3" s="25" t="inlineStr">
         <is>
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C3" s="25" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="D3" s="25" t="inlineStr">
         <is>
           <t>Linked AC</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="E3" s="25" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="F3" s="25" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -559,27 +566,27 @@
           <t>TC01</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="26" t="inlineStr">
         <is>
           <t>SPM-50-TC01</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="26" t="inlineStr">
         <is>
           <t>Technical Support sees every requested item with its quantity and the Coordinator's technical requirements</t>
         </is>
       </c>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="D4" s="26" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="E4" s="13" t="inlineStr">
+      <c r="E4" s="26" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F4" s="13" t="inlineStr">
+      <c r="F4" s="26" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -598,27 +605,27 @@
           <t>TC02</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="26" t="inlineStr">
         <is>
           <t>SPM-50-TC02</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C5" s="26" t="inlineStr">
         <is>
           <t>Technical Support moves a line to Under review, and can undo it back to Requested</t>
         </is>
       </c>
-      <c r="D5" s="13" t="inlineStr">
+      <c r="D5" s="26" t="inlineStr">
         <is>
           <t>AC2</t>
         </is>
       </c>
-      <c r="E5" s="13" t="inlineStr">
+      <c r="E5" s="26" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F5" s="13" t="inlineStr">
+      <c r="F5" s="26" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -637,27 +644,27 @@
           <t>TC03</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="26" t="inlineStr">
         <is>
           <t>SPM-50-TC03</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="26" t="inlineStr">
         <is>
           <t>Reserved and Partially fulfilled cannot be chosen by hand, and a reserved line can only become 'Cannot be provided'</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="26" t="inlineStr">
         <is>
           <t>AC2</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="26" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F6" s="13" t="inlineStr">
+      <c r="F6" s="26" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -676,27 +683,27 @@
           <t>TC04</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="26" t="inlineStr">
         <is>
           <t>SPM-50-TC04</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C7" s="26" t="inlineStr">
         <is>
           <t>Line marked 'Cannot be provided' can be reopened to Under review</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr">
+      <c r="D7" s="26" t="inlineStr">
         <is>
           <t>AC2, AC3</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="26" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F7" s="13" t="inlineStr">
+      <c r="F7" s="26" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -715,27 +722,27 @@
           <t>TC05</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="26" t="inlineStr">
         <is>
           <t>SPM-50-TC05</t>
         </is>
       </c>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="C8" s="26" t="inlineStr">
         <is>
           <t>Technical Support marks an item as cannot be provided, with a reason, without changing other lines</t>
         </is>
       </c>
-      <c r="D8" s="13" t="inlineStr">
+      <c r="D8" s="26" t="inlineStr">
         <is>
           <t>AC2, AC3</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="E8" s="26" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F8" s="13" t="inlineStr">
+      <c r="F8" s="26" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -754,27 +761,27 @@
           <t>TC06</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="26" t="inlineStr">
         <is>
           <t>SPM-50-TC06</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="C9" s="26" t="inlineStr">
         <is>
           <t>Marking an item 'Cannot be provided' without a real reason is blocked</t>
         </is>
       </c>
-      <c r="D9" s="13" t="inlineStr">
+      <c r="D9" s="26" t="inlineStr">
         <is>
           <t>AC3</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="26" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F9" s="13" t="inlineStr">
+      <c r="F9" s="26" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -793,27 +800,27 @@
           <t>TC07</t>
         </is>
       </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B10" s="26" t="inlineStr">
         <is>
           <t>SPM-50-TC07</t>
         </is>
       </c>
-      <c r="C10" s="13" t="inlineStr">
+      <c r="C10" s="26" t="inlineStr">
         <is>
           <t>Marking a reserved line 'Cannot be provided' releases its units, and reserving it again clears the old reason</t>
         </is>
       </c>
-      <c r="D10" s="13" t="inlineStr">
+      <c r="D10" s="26" t="inlineStr">
         <is>
           <t>AC3</t>
         </is>
       </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="E10" s="26" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F10" s="13" t="inlineStr">
+      <c r="F10" s="26" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -832,27 +839,27 @@
           <t>TC08</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B11" s="26" t="inlineStr">
         <is>
           <t>SPM-50-TC08</t>
         </is>
       </c>
-      <c r="C11" s="13" t="inlineStr">
+      <c r="C11" s="26" t="inlineStr">
         <is>
           <t>Technical Support records technical notes, sees who updated the line, and can clear them</t>
         </is>
       </c>
-      <c r="D11" s="13" t="inlineStr">
+      <c r="D11" s="26" t="inlineStr">
         <is>
           <t>AC4, AC5</t>
         </is>
       </c>
-      <c r="E11" s="13" t="inlineStr">
+      <c r="E11" s="26" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F11" s="13" t="inlineStr">
+      <c r="F11" s="26" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -871,27 +878,27 @@
           <t>TC09</t>
         </is>
       </c>
-      <c r="B12" s="13" t="inlineStr">
+      <c r="B12" s="26" t="inlineStr">
         <is>
           <t>SPM-50-TC09</t>
         </is>
       </c>
-      <c r="C12" s="13" t="inlineStr">
+      <c r="C12" s="26" t="inlineStr">
         <is>
           <t>Technical notes are limited to 500 characters</t>
         </is>
       </c>
-      <c r="D12" s="13" t="inlineStr">
+      <c r="D12" s="26" t="inlineStr">
         <is>
           <t>AC3, AC4</t>
         </is>
       </c>
-      <c r="E12" s="13" t="inlineStr">
+      <c r="E12" s="26" t="inlineStr">
         <is>
           <t>Boundary</t>
         </is>
       </c>
-      <c r="F12" s="13" t="inlineStr">
+      <c r="F12" s="26" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -910,27 +917,27 @@
           <t>TC10</t>
         </is>
       </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B13" s="26" t="inlineStr">
         <is>
           <t>SPM-50-TC10</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="C13" s="26" t="inlineStr">
         <is>
           <t>The Coordinator sees Technical Support's status and notes on the event's Equipment tab</t>
         </is>
       </c>
-      <c r="D13" s="13" t="inlineStr">
+      <c r="D13" s="26" t="inlineStr">
         <is>
           <t>AC5</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E13" s="26" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F13" s="13" t="inlineStr">
+      <c r="F13" s="26" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -949,27 +956,27 @@
           <t>TC11</t>
         </is>
       </c>
-      <c r="B14" s="13" t="inlineStr">
+      <c r="B14" s="26" t="inlineStr">
         <is>
           <t>SPM-50-TC11</t>
         </is>
       </c>
-      <c r="C14" s="13" t="inlineStr">
+      <c r="C14" s="26" t="inlineStr">
         <is>
           <t>An update on one event does not appear on another event requesting the same item</t>
         </is>
       </c>
-      <c r="D14" s="13" t="inlineStr">
+      <c r="D14" s="26" t="inlineStr">
         <is>
           <t>AC5</t>
         </is>
       </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="E14" s="26" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F14" s="13" t="inlineStr">
+      <c r="F14" s="26" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -988,27 +995,27 @@
           <t>TC12</t>
         </is>
       </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="B15" s="26" t="inlineStr">
         <is>
           <t>SPM-50-TC12</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C15" s="26" t="inlineStr">
         <is>
           <t>A Coordinator cannot update fulfilment status or technical notes</t>
         </is>
       </c>
-      <c r="D15" s="13" t="inlineStr">
+      <c r="D15" s="26" t="inlineStr">
         <is>
           <t>AC2, AC4</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E15" s="26" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F15" s="13" t="inlineStr">
+      <c r="F15" s="26" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -1027,27 +1034,27 @@
           <t>TC13</t>
         </is>
       </c>
-      <c r="B16" s="13" t="inlineStr">
+      <c r="B16" s="26" t="inlineStr">
         <is>
           <t>SPM-50-TC13</t>
         </is>
       </c>
-      <c r="C16" s="13" t="inlineStr">
+      <c r="C16" s="26" t="inlineStr">
         <is>
           <t>Lines on a cancelled event cannot be updated</t>
         </is>
       </c>
-      <c r="D16" s="13" t="inlineStr">
+      <c r="D16" s="26" t="inlineStr">
         <is>
           <t>AC2, AC3, AC4</t>
         </is>
       </c>
-      <c r="E16" s="13" t="inlineStr">
+      <c r="E16" s="26" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F16" s="13" t="inlineStr">
+      <c r="F16" s="26" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
@@ -1066,27 +1073,27 @@
           <t>TC14</t>
         </is>
       </c>
-      <c r="B17" s="13" t="inlineStr">
+      <c r="B17" s="26" t="inlineStr">
         <is>
           <t>SPM-50-TC14</t>
         </is>
       </c>
-      <c r="C17" s="13" t="inlineStr">
+      <c r="C17" s="26" t="inlineStr">
         <is>
           <t>Equipment on an event that is not yet approved cannot be updated</t>
         </is>
       </c>
-      <c r="D17" s="13" t="inlineStr">
+      <c r="D17" s="26" t="inlineStr">
         <is>
           <t>AC2, AC3, AC4</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E17" s="26" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F17" s="13" t="inlineStr">
+      <c r="F17" s="26" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -1100,20 +1107,21 @@
       <c r="I17" s="26" t="n"/>
     </row>
     <row r="18"/>
+    <row r="19"/>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+      <c r="A20" s="25" t="inlineStr">
         <is>
           <t>AC</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
+      <c r="B20" s="25" t="inlineStr">
         <is>
           <t>Acceptance Criterion</t>
         </is>
       </c>
       <c r="C20" s="23" t="n"/>
       <c r="D20" s="24" t="n"/>
-      <c r="E20" s="1" t="inlineStr">
+      <c r="E20" s="25" t="inlineStr">
         <is>
           <t>Covered by</t>
         </is>
@@ -1121,19 +1129,19 @@
       <c r="F20" s="24" t="n"/>
     </row>
     <row r="21" ht="17.25" customHeight="1" s="22">
-      <c r="A21" s="13" t="inlineStr">
+      <c r="A21" s="26" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="B21" s="13" t="inlineStr">
+      <c r="B21" s="26" t="inlineStr">
         <is>
           <t>Technical Support Staff can view equipment requirements for an event.</t>
         </is>
       </c>
       <c r="C21" s="23" t="n"/>
       <c r="D21" s="24" t="n"/>
-      <c r="E21" s="13" t="inlineStr">
+      <c r="E21" s="26" t="inlineStr">
         <is>
           <t>SPM-50-TC01</t>
         </is>
@@ -1141,19 +1149,19 @@
       <c r="F21" s="24" t="n"/>
     </row>
     <row r="22" ht="98.25" customHeight="1" s="22">
-      <c r="A22" s="13" t="inlineStr">
+      <c r="A22" s="26" t="inlineStr">
         <is>
           <t>AC2</t>
         </is>
       </c>
-      <c r="B22" s="13" t="inlineStr">
+      <c r="B22" s="26" t="inlineStr">
         <is>
           <t>Technical Support Staff can update the fulfilment status of requested equipment.</t>
         </is>
       </c>
       <c r="C22" s="23" t="n"/>
       <c r="D22" s="24" t="n"/>
-      <c r="E22" s="13" t="inlineStr">
+      <c r="E22" s="26" t="inlineStr">
         <is>
           <t>SPM-50-TC02
 SPM-50-TC03
@@ -1167,19 +1175,19 @@
       <c r="F22" s="24" t="n"/>
     </row>
     <row r="23" ht="98.25" customHeight="1" s="22">
-      <c r="A23" s="13" t="inlineStr">
+      <c r="A23" s="26" t="inlineStr">
         <is>
           <t>AC3</t>
         </is>
       </c>
-      <c r="B23" s="13" t="inlineStr">
+      <c r="B23" s="26" t="inlineStr">
         <is>
           <t>Technical Support Staff can indicate when equipment cannot be provided.</t>
         </is>
       </c>
       <c r="C23" s="23" t="n"/>
       <c r="D23" s="24" t="n"/>
-      <c r="E23" s="13" t="inlineStr">
+      <c r="E23" s="26" t="inlineStr">
         <is>
           <t>SPM-50-TC04
 SPM-50-TC05
@@ -1193,19 +1201,19 @@
       <c r="F23" s="24" t="n"/>
     </row>
     <row r="24" ht="71.25" customHeight="1" s="22">
-      <c r="A24" s="13" t="inlineStr">
+      <c r="A24" s="26" t="inlineStr">
         <is>
           <t>AC4</t>
         </is>
       </c>
-      <c r="B24" s="13" t="inlineStr">
+      <c r="B24" s="26" t="inlineStr">
         <is>
           <t>Technical Support Staff can record relevant technical information.</t>
         </is>
       </c>
       <c r="C24" s="23" t="n"/>
       <c r="D24" s="24" t="n"/>
-      <c r="E24" s="13" t="inlineStr">
+      <c r="E24" s="26" t="inlineStr">
         <is>
           <t>SPM-50-TC08
 SPM-50-TC09
@@ -1217,19 +1225,19 @@
       <c r="F24" s="24" t="n"/>
     </row>
     <row r="25" ht="44.25" customHeight="1" s="22">
-      <c r="A25" s="13" t="inlineStr">
+      <c r="A25" s="26" t="inlineStr">
         <is>
           <t>AC5</t>
         </is>
       </c>
-      <c r="B25" s="13" t="inlineStr">
+      <c r="B25" s="26" t="inlineStr">
         <is>
           <t>Updates are associated with the relevant event.</t>
         </is>
       </c>
       <c r="C25" s="23" t="n"/>
       <c r="D25" s="24" t="n"/>
-      <c r="E25" s="13" t="inlineStr">
+      <c r="E25" s="26" t="inlineStr">
         <is>
           <t>SPM-50-TC08
 SPM-50-TC10
@@ -1240,12 +1248,12 @@
     </row>
     <row r="26" ht="15.75" customHeight="1" s="22"/>
     <row r="27" ht="300.75" customHeight="1" s="22">
-      <c r="A27" s="1" t="inlineStr">
+      <c r="A27" s="25" t="inlineStr">
         <is>
           <t>Code reviewed</t>
         </is>
       </c>
-      <c r="B27" s="13" t="inlineStr">
+      <c r="B27" s="26" t="inlineStr">
         <is>
           <t>src/lib/equipmentFulfilment.ts
 src/app/api/events/[id]/equipment/[requestId]/fulfilment/route.ts
@@ -2315,43 +2323,43 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
-        <is>
-          <t>SPM-50-TC09</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="98.25" customHeight="1" s="22">
+      <c r="B2" s="26" t="inlineStr">
+        <is>
+          <t>SPM-50-TC08</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="84.75" customHeight="1" s="22">
       <c r="A3" s="6" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>Rule (team decision): Technical notes allow up to 500 characters, matching the out-of-service reason (SPM-55).
-Robotics Expo's Confidence Monitor line is 'Requested'.
+      <c r="B3" s="26" t="inlineStr">
+        <is>
+          <t>Robotics Expo's Wireless Presenter line is 'Requested' with no technical notes.
 Data: run `npm run fixtures:spm50` first, and again before repeating the case.
 Logged in as Technical Support Staff (vikram.nair@connectsphere.com, password123).</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="185.25" customHeight="1" s="22">
+    <row r="4" ht="125.25" customHeight="1" s="22">
       <c r="A4" s="6" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="26" t="inlineStr">
         <is>
           <t>1. Open the equipment request for the Robotics Expo event
-2. On the Confidence Monitor line, click 'Update'
-3. In 'Fulfilment status', choose 'Cannot be provided'
-4. Paste any 501-character test text into 'Technical notes' (use this : Only 1 working unit is currently available. As an alternative, we suggest using 2 × 55-inch TVs mounted on stands to provide sufficient visibility and coverage. This setup can be positioned side by side or at suitable locations depending on the space and viewing requirements. It also provides greater flexibility in placement and can be adjusted to ensure that the content is clearly visible to all participants. This alternative may be more practical while maintaining a good display setup for all. extra)
+2. On the Wireless Presenter line, click 'Update'
+3. Leave 'Fulfilment status' as 'Requested'
+4. In 'Technical notes', enter "Presenters need fresh AAA batteries; USB-C dongle is in kit bag 3'
 5. Click 'Save'
-6. Delete one character, leaving 500
-7. Click 'Save'
-8. Refresh the page</t>
+6. Refresh the page
+7. On the Wireless Presenter line, click 'Update'
+8. Delete all text in 'Technical notes'
+9. Click 'Save'</t>
         </is>
       </c>
     </row>
@@ -2361,23 +2369,23 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>Technical notes: the letter 'A' repeated 501 times, then 500 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="98.25" customHeight="1" s="22">
+      <c r="B5" s="26" t="inlineStr">
+        <is>
+          <t>Technical notes: Presenters need fresh AAA batteries; USB-C dongle is in kit bag 3 -&gt; (empty)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="152.25" customHeight="1" s="22">
       <c r="A6" s="6" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>Step 5: The error 'Technical notes must be 500 characters or fewer.' is shown under Technical notes. The Status chip still shows 'Requested' and nothing is saved.
-Step 7: 'Update saved.' appears and the Status chip shows 'Cannot be provided'.
-Step 8: All 500 characters are shown in the line's technical notes; nothing is cut off.</t>
+      <c r="B6" s="26" t="inlineStr">
+        <is>
+          <t>Step 5: 'Update saved.' appears. The Status chip still shows 'Requested'.
+Step 6: The line shows 'Technical Support notes: Presenters need fresh AAA batteries; USB-C dongle is in kit bag 3', separately from 'Technical requirements: Must pair with the stage laptop over USB-C', which is unchanged. It also shows 'Last updated by Vikram Nair, ' followed by the date and time of the save (for example '2 Oct 2026, 14:05').
+Step 9: 'Update saved.' appears and the line shows 'Technical Support notes: —'. The Status chip still shows 'Requested'.</t>
         </is>
       </c>
     </row>
@@ -2387,7 +2395,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="26" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -2419,11 +2427,11 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>Step 5: The error 'Technical notes must be 500 characters or fewer.' is shown under Technical notes. The Status chip still shows 'Requested' and nothing is saved.
-Step 7: 'Update saved.' appears and the Status chip shows 'Cannot be provided'.
-Step 8: All 500 characters are shown in the line's technical notes; nothing is cut off.</t>
+      <c r="B11" s="26" t="inlineStr">
+        <is>
+          <t>Step 5: 'Update saved.' appears. The Status chip still shows 'Requested'.
+Step 6: The line shows 'Technical Support notes: Presenters need fresh AAA batteries; USB-C dongle is in kit bag 3', separately from 'Technical requirements: Must pair with the stage laptop over USB-C', which is unchanged. It also shows 'Last updated by Vikram Nair, ' followed by the date and time of the save (for example '2 Oct 2026, 14:05').
+Step 9: 'Update saved.' appears and the line shows 'Technical Support notes: —'. The Status chip still shows 'Requested'.</t>
         </is>
       </c>
     </row>
@@ -2459,7 +2467,7 @@
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>Janelle</t>
+          <t xml:space="preserve">Janelle </t>
         </is>
       </c>
     </row>
@@ -2488,11 +2496,11 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="13" t="inlineStr">
-        <is>
-          <t>Step 5: The error 'Technical notes must be 500 characters or fewer.' is shown under Technical notes. The Status chip still shows 'Requested' and nothing is saved.
-Step 7: 'Update saved.' appears and the Status chip shows 'Cannot be provided'.
-Step 8: All 500 characters are shown in the line's technical notes; nothing is cut off.</t>
+      <c r="B18" s="26" t="inlineStr">
+        <is>
+          <t>Step 5: 'Update saved.' appears. The Status chip still shows 'Requested'.
+Step 6: The line shows 'Technical Support notes: Presenters need fresh AAA batteries; USB-C dongle is in kit bag 3', separately from 'Technical requirements: Must pair with the stage laptop over USB-C', which is unchanged. It also shows 'Last updated by Vikram Nair, ' followed by the date and time of the save (for example '2 Oct 2026, 14:05').
+Step 9: 'Update saved.' appears and the line shows 'Technical Support notes: —'. The Status chip still shows 'Requested'.</t>
         </is>
       </c>
     </row>
@@ -3554,62 +3562,69 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
-        <is>
-          <t>SPM-50-TC10</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="57.75" customHeight="1" s="22">
+      <c r="B2" s="26" t="inlineStr">
+        <is>
+          <t>SPM-50-TC09</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="98.25" customHeight="1" s="22">
       <c r="A3" s="6" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>Run TC05 first: Robotics Expo's Confidence Monitor is 'Cannot be provided' with a reason.
-Logged in as the assigned Coordinator, daniel.tan@connectsphere.com (password123).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="57.75" customHeight="1" s="22">
+      <c r="B3" s="26" t="inlineStr">
+        <is>
+          <t>Rule (team decision): Technical notes allow up to 500 characters, matching the out-of-service reason (SPM-55).
+Robotics Expo's Confidence Monitor line is 'Requested'.
+Data: run `npm run fixtures:spm50` first, and again before repeating the case.
+Logged in as Technical Support Staff (vikram.nair@connectsphere.com, password123).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="185.25" customHeight="1" s="22">
       <c r="A4" s="6" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>1. Click Events in the side menu
-2. Open the Robotics Expo event
-3. Click the Equipment tab
-4. Read the Confidence Monitor row</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="17.25" customHeight="1" s="22">
+      <c r="B4" s="26" t="inlineStr">
+        <is>
+          <t>1. Open the equipment request for the Robotics Expo event
+2. On the Confidence Monitor line, click 'Update'
+3. In 'Fulfilment status', choose 'Cannot be provided'
+4. Paste any 501-character test text into 'Technical notes' (use this : Only 1 working unit is currently available. As an alternative, we suggest using 2 × 55-inch TVs mounted on stands to provide sufficient visibility and coverage. This setup can be positioned side by side or at suitable locations depending on the space and viewing requirements. It also provides greater flexibility in placement and can be adjusted to ensure that the content is clearly visible to all participants. This alternative may be more practical while maintaining a good display setup for all. extra)
+5. Click 'Save'
+6. Delete one character, leaving 500
+7. Click 'Save'
+8. Refresh the page</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30.75" customHeight="1" s="22">
       <c r="A5" s="6" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>Event: Robotics Expo</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
+      <c r="B5" s="26" t="inlineStr">
+        <is>
+          <t>Technical notes: the letter 'A' repeated 501 times, then 500 times</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="98.25" customHeight="1" s="22">
       <c r="A6" s="6" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>Step 4: Confidence Monitor shows the status chip 'Cannot be provided' and 'Technical Support notes: Only 1 working unit; suggest 2x 55-inch TV on stands as an alternative'. The notes are read-only for the Coordinator; their own Quantity and Technical requirements fields are still editable.
-Note: if u did this after tc09 you should see the 500 character (Only 1 working unit is currently available. As an alternative, we suggest using 2 × 55-inch TVs mounted on stands to provide sufficient visibility and coverage. This setup can be positioned side by side or at suitable locations depending on the space and viewing requirements. It also provides greater flexibility in placement and can be adjusted to ensure that the content is clearly visible to all participants. This alternative may be more practical while maintaining a good display setup for all.)</t>
+      <c r="B6" s="26" t="inlineStr">
+        <is>
+          <t>Step 5: The error 'Technical notes must be 500 characters or fewer.' is shown under Technical notes. The Status chip still shows 'Requested' and nothing is saved.
+Step 7: 'Update saved.' appears and the Status chip shows 'Cannot be provided'.
+Step 8: All 500 characters are shown in the line's technical notes; nothing is cut off.</t>
         </is>
       </c>
     </row>
@@ -3619,7 +3634,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="26" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -3651,10 +3666,11 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>Step 4: Confidence Monitor shows the status chip 'Cannot be provided' and 'Technical Support notes: Only 1 working unit; suggest 2x 55-inch TV on stands as an alternative'. The notes are read-only for the Coordinator; their own Quantity and Technical requirements fields are still editable.
-Note: if u did this after tc09 you should see the 500 character (Only 1 working unit is currently available. As an alternative, we suggest using 2 × 55-inch TVs mounted on stands to provide sufficient visibility and coverage. This setup can be positioned side by side or at suitable locations depending on the space and viewing requirements. It also provides greater flexibility in placement and can be adjusted to ensure that the content is clearly visible to all participants. This alternative may be more practical while maintaining a good display setup for all.)</t>
+      <c r="B11" s="26" t="inlineStr">
+        <is>
+          <t>Step 5: The error 'Technical notes must be 500 characters or fewer.' is shown under Technical notes. The Status chip still shows 'Requested' and nothing is saved.
+Step 7: 'Update saved.' appears and the Status chip shows 'Cannot be provided'.
+Step 8: All 500 characters are shown in the line's technical notes; nothing is cut off.</t>
         </is>
       </c>
     </row>
@@ -3719,10 +3735,11 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="13" t="inlineStr">
-        <is>
-          <t>Step 4: Confidence Monitor shows the status chip 'Cannot be provided' and 'Technical Support notes: Only 1 working unit; suggest 2x 55-inch TV on stands as an alternative'. The notes are read-only for the Coordinator; their own Quantity and Technical requirements fields are still editable.
-Note: if u did this after tc09 you should see the 500 character (Only 1 working unit is currently available. As an alternative, we suggest using 2 × 55-inch TVs mounted on stands to provide sufficient visibility and coverage. This setup can be positioned side by side or at suitable locations depending on the space and viewing requirements. It also provides greater flexibility in placement and can be adjusted to ensure that the content is clearly visible to all participants. This alternative may be more practical while maintaining a good display setup for all.)</t>
+      <c r="B18" s="26" t="inlineStr">
+        <is>
+          <t>Step 5: The error 'Technical notes must be 500 characters or fewer.' is shown under Technical notes. The Status chip still shows 'Requested' and nothing is saved.
+Step 7: 'Update saved.' appears and the Status chip shows 'Cannot be provided'.
+Step 8: All 500 characters are shown in the line's technical notes; nothing is cut off.</t>
         </is>
       </c>
     </row>
@@ -4784,61 +4801,62 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
-        <is>
-          <t>SPM-50-TC11</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="84.75" customHeight="1" s="22">
+      <c r="B2" s="26" t="inlineStr">
+        <is>
+          <t>SPM-50-TC10</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="57.75" customHeight="1" s="22">
       <c r="A3" s="6" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="26" t="inlineStr">
         <is>
           <t>Run TC05 first: Robotics Expo's Confidence Monitor is 'Cannot be provided' with a reason.
-Event 'Design Week' also requests 'Confidence Monitor' x1, status 'Requested', no notes.
-Logged in as Technical Support Staff (vikram.nair@connectsphere.com, password123).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="44.25" customHeight="1" s="22">
+Logged in as the assigned Coordinator, daniel.tan@connectsphere.com (password123).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="57.75" customHeight="1" s="22">
       <c r="A4" s="6" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>1. Click Equipment Requests in the side menu
-2. Open the equipment request for the Design Week event
-3. Read the Confidence Monitor line</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30.75" customHeight="1" s="22">
+      <c r="B4" s="26" t="inlineStr">
+        <is>
+          <t>1. Click Events in the side menu
+2. Open the Robotics Expo event
+3. Click the Equipment tab
+4. Read the Confidence Monitor row</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="17.25" customHeight="1" s="22">
       <c r="A5" s="6" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>Item: Confidence Monitor on Robotics Expo (updated) and Design Week (not updated)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="57.75" customHeight="1" s="22">
+      <c r="B5" s="26" t="inlineStr">
+        <is>
+          <t>Event: Robotics Expo</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>Step 3: Design Week's Confidence Monitor line still shows 'Requested' with no Technical Support notes. The 'Cannot be provided' status and reason from Robotics Expo do not appear here.</t>
+      <c r="B6" s="26" t="inlineStr">
+        <is>
+          <t>Step 4: Confidence Monitor shows the status chip 'Cannot be provided' and 'Technical Support notes: Only 1 working unit; suggest 2x 55-inch TV on stands as an alternative'. The notes are read-only for the Coordinator; their own Quantity and Technical requirements fields are still editable.
+Note: if u did this after tc09 you should see the 500 character (Only 1 working unit is currently available. As an alternative, we suggest using 2 × 55-inch TVs mounted on stands to provide sufficient visibility and coverage. This setup can be positioned side by side or at suitable locations depending on the space and viewing requirements. It also provides greater flexibility in placement and can be adjusted to ensure that the content is clearly visible to all participants. This alternative may be more practical while maintaining a good display setup for all.)</t>
         </is>
       </c>
     </row>
@@ -4848,7 +4866,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="26" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -4880,9 +4898,10 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>Step 3: Design Week's Confidence Monitor line still shows 'Requested' with no Technical Support notes. The 'Cannot be provided' status and reason from Robotics Expo do not appear here.</t>
+      <c r="B11" s="26" t="inlineStr">
+        <is>
+          <t>Step 4: Confidence Monitor shows the status chip 'Cannot be provided' and 'Technical Support notes: Only 1 working unit; suggest 2x 55-inch TV on stands as an alternative'. The notes are read-only for the Coordinator; their own Quantity and Technical requirements fields are still editable.
+Note: if u did this after tc09 you should see the 500 character (Only 1 working unit is currently available. As an alternative, we suggest using 2 × 55-inch TVs mounted on stands to provide sufficient visibility and coverage. This setup can be positioned side by side or at suitable locations depending on the space and viewing requirements. It also provides greater flexibility in placement and can be adjusted to ensure that the content is clearly visible to all participants. This alternative may be more practical while maintaining a good display setup for all.)</t>
         </is>
       </c>
     </row>
@@ -4947,9 +4966,10 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="13" t="inlineStr">
-        <is>
-          <t>Step 3: Design Week's Confidence Monitor line still shows 'Requested' with no Technical Support notes. The 'Cannot be provided' status and reason from Robotics Expo do not appear here.</t>
+      <c r="B18" s="26" t="inlineStr">
+        <is>
+          <t>Step 4: Confidence Monitor shows the status chip 'Cannot be provided' and 'Technical Support notes: Only 1 working unit; suggest 2x 55-inch TV on stands as an alternative'. The notes are read-only for the Coordinator; their own Quantity and Technical requirements fields are still editable.
+Note: if u did this after tc09 you should see the 500 character (Only 1 working unit is currently available. As an alternative, we suggest using 2 × 55-inch TVs mounted on stands to provide sufficient visibility and coverage. This setup can be positioned side by side or at suitable locations depending on the space and viewing requirements. It also provides greater flexibility in placement and can be adjusted to ensure that the content is clearly visible to all participants. This alternative may be more practical while maintaining a good display setup for all.)</t>
         </is>
       </c>
     </row>
@@ -6011,63 +6031,61 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
-        <is>
-          <t>SPM-50-TC12</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="44.25" customHeight="1" s="22">
+      <c r="B2" s="26" t="inlineStr">
+        <is>
+          <t>SPM-50-TC11</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="84.75" customHeight="1" s="22">
       <c r="A3" s="6" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>Robotics Expo's Wireless Presenter line is 'Requested'.
-Logged in as the assigned Coordinator, daniel.tan@connectsphere.com (password123).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="98.25" customHeight="1" s="22">
+      <c r="B3" s="26" t="inlineStr">
+        <is>
+          <t>Run TC05 first: Robotics Expo's Confidence Monitor is 'Cannot be provided' with a reason.
+Event 'Design Week' also requests 'Confidence Monitor' x1, status 'Requested', no notes.
+Logged in as Technical Support Staff (vikram.nair@connectsphere.com, password123).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="44.25" customHeight="1" s="22">
       <c r="A4" s="6" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>1. Open the Robotics Expo event and click its Equipment tab
-2. Look for an 'Update' button, a Fulfilment status field or a Technical notes field on the Wireless Presenter row
-3. Note the event's reference (for example EVT-000123) shown at the top of the page
-4. Type /equipment/requests/&lt;that reference&gt; into the address bar</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="17.25" customHeight="1" s="22">
+      <c r="B4" s="26" t="inlineStr">
+        <is>
+          <t>1. Click Equipment Requests in the side menu
+2. Open the equipment request for the Design Week event
+3. Read the Confidence Monitor line</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30.75" customHeight="1" s="22">
       <c r="A5" s="6" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>Role: Coordinator, Event: Robotics Expo</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="71.25" customHeight="1" s="22">
+      <c r="B5" s="26" t="inlineStr">
+        <is>
+          <t>Item: Confidence Monitor on Robotics Expo (updated) and Design Week (not updated)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="57.75" customHeight="1" s="22">
       <c r="A6" s="6" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>Step 2: None of these controls are shown. Only the Coordinator's own Quantity, Technical requirements, Save and Remove controls are present.
-Step 4: The page shows 'Equipment availability is for Technical Support Staff.' and "Could not load this. Only Technical Support Staff can check equipment availability." with
-no Update or Reserve controls.</t>
+      <c r="B6" s="26" t="inlineStr">
+        <is>
+          <t>Step 3: Design Week's Confidence Monitor line still shows 'Requested' with no Technical Support notes. The 'Cannot be provided' status and reason from Robotics Expo do not appear here.</t>
         </is>
       </c>
     </row>
@@ -6077,7 +6095,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="26" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -6109,11 +6127,9 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>Step 2: None of these controls are shown. Only the Coordinator's own Quantity, Technical requirements, Save and Remove controls are present.
-Step 4: The page shows 'Equipment availability is for Technical Support Staff.' and "Could not load this. Only Technical Support Staff can check equipment availability." with
-no Update or Reserve controls.</t>
+      <c r="B11" s="26" t="inlineStr">
+        <is>
+          <t>Step 3: Design Week's Confidence Monitor line still shows 'Requested' with no Technical Support notes. The 'Cannot be provided' status and reason from Robotics Expo do not appear here.</t>
         </is>
       </c>
     </row>
@@ -6178,11 +6194,9 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="13" t="inlineStr">
-        <is>
-          <t>Step 2: None of these controls are shown. Only the Coordinator's own Quantity, Technical requirements, Save and Remove controls are present.
-Step 4: The page shows 'Equipment availability is for Technical Support Staff.' and "Could not load this. Only Technical Support Staff can check equipment availability." with
-no Update or Reserve controls.</t>
+      <c r="B18" s="26" t="inlineStr">
+        <is>
+          <t>Step 3: Design Week's Confidence Monitor line still shows 'Requested' with no Technical Support notes. The 'Cannot be provided' status and reason from Robotics Expo do not appear here.</t>
         </is>
       </c>
     </row>
@@ -7244,38 +7258,37 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
-        <is>
-          <t>SPM-50-TC13</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="119.25" customHeight="1" s="22">
+      <c r="B2" s="26" t="inlineStr">
+        <is>
+          <t>SPM-50-TC12</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="44.25" customHeight="1" s="22">
       <c r="A3" s="6" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>Rule (team decision, 3 Oct, following the BPMN): Technical Support checks, reserves and updates equipment while the event is in Planning. Once the event is Confirmed its equipment is final - they still see it, to prepare it, but a change goes through a change request.
-Event 'Confirmed Launch' (2027-08-30, status 'Confirmed') has 2x Wireless Presenter, status 'Reserved' (Reserved = 2).
-Data: run `npm run fixtures:spm50` first.
-Logged in as Technical Support Staff (vikram.nair@connectsphere.com, password123).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="71.25" customHeight="1" s="22">
+      <c r="B3" s="26" t="inlineStr">
+        <is>
+          <t>Robotics Expo's Wireless Presenter line is 'Requested'.
+Logged in as the assigned Coordinator, daniel.tan@connectsphere.com (password123).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="98.25" customHeight="1" s="22">
       <c r="A4" s="6" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>1. Click Equipment Requests in the side menu
-2. Open the equipment request for the Confirmed Launch event
-3. Look for an 'Update' or 'Reserve' button on the Wireless Presenter line</t>
+      <c r="B4" s="26" t="inlineStr">
+        <is>
+          <t>1. Open the Robotics Expo event and click its Equipment tab
+2. Look for an 'Update' button, a Fulfilment status field or a Technical notes field on the Wireless Presenter row
+3. Note the event's reference (for example EVT-000123) shown at the top of the page
+4. Type /equipment/requests/&lt;that reference&gt; into the address bar</t>
         </is>
       </c>
     </row>
@@ -7285,23 +7298,23 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>Event status: Confirmed</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="84.75" customHeight="1" s="22">
+      <c r="B5" s="26" t="inlineStr">
+        <is>
+          <t>Role: Coordinator, Event: Robotics Expo</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="71.25" customHeight="1" s="22">
       <c r="A6" s="6" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="19" t="inlineStr">
-        <is>
-          <t>Step 1: Confirmed Launch is listed, with Event status 'Confirmed'.
- Step 2: The page shows 'This event is confirmed — its equipment is final. A change now goes through a change request.' The Wireless Presenter line shows the Status chip 'Reserved' and Reserved 2.
- Step 3: No 'Update' button and no 'Reserve' button are shown.</t>
+      <c r="B6" s="26" t="inlineStr">
+        <is>
+          <t>Step 2: None of these controls are shown. Only the Coordinator's own Quantity, Technical requirements, Save and Remove controls are present.
+Step 4: The page shows 'Equipment availability is for Technical Support Staff.' and "Could not load this. Only Technical Support Staff can check equipment availability." with
+no Update or Reserve controls.</t>
         </is>
       </c>
     </row>
@@ -7311,7 +7324,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="26" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -7343,11 +7356,11 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="19" t="inlineStr">
-        <is>
-          <t>Step 1: Confirmed Launch is listed, with Event status 'Confirmed'.
- Step 2: The page shows 'This event is confirmed — its equipment is final. A change now goes through a change request.' The Wireless Presenter line shows the Status chip 'Reserved' and Reserved 2.
- Step 3: No 'Update' button and no 'Reserve' button are shown.</t>
+      <c r="B11" s="26" t="inlineStr">
+        <is>
+          <t>Step 2: None of these controls are shown. Only the Coordinator's own Quantity, Technical requirements, Save and Remove controls are present.
+Step 4: The page shows 'Equipment availability is for Technical Support Staff.' and "Could not load this. Only Technical Support Staff can check equipment availability." with
+no Update or Reserve controls.</t>
         </is>
       </c>
     </row>
@@ -7412,11 +7425,11 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="19" t="inlineStr">
-        <is>
-          <t>Step 1: Confirmed Launch is listed, with Event status 'Confirmed'.
- Step 2: The page shows 'This event is confirmed — its equipment is final. A change now goes through a change request.' The Wireless Presenter line shows the Status chip 'Reserved' and Reserved 2.
- Step 3: No 'Update' button and no 'Reserve' button are shown.</t>
+      <c r="B18" s="26" t="inlineStr">
+        <is>
+          <t>Step 2: None of these controls are shown. Only the Coordinator's own Quantity, Technical requirements, Save and Remove controls are present.
+Step 4: The page shows 'Equipment availability is for Technical Support Staff.' and "Could not load this. Only Technical Support Staff can check equipment availability." with
+no Update or Reserve controls.</t>
         </is>
       </c>
     </row>
@@ -8478,40 +8491,38 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
-        <is>
-          <t>SPM-50-TC14</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="175.5" customHeight="1" s="22">
+      <c r="B2" s="26" t="inlineStr">
+        <is>
+          <t>SPM-50-TC13</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="119.25" customHeight="1" s="22">
       <c r="A3" s="6" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>Rule (team decision, 3 Oct, following the BPMN): Technical Support's lane starts after the Coordinator's 'Record equipment request' - in Planning. Before that, the equipment is only part of the organiser's request.
-Event 'Pending Showcase' (2027-09-06, status 'Under review') and event 'Approved Briefing' (2027-09-13, status 'Approved', the Coordinator has not started planning) each request 1x Wireless Presenter.
-Their references (EVT-…) are printed by `npm run fixtures:spm50`.
+      <c r="B3" s="26" t="inlineStr">
+        <is>
+          <t>Rule (team decision, 3 Oct, following the BPMN): Technical Support checks, reserves and updates equipment while the event is in Planning. Once the event is Confirmed its equipment is final - they still see it, to prepare it, but a change goes through a change request.
+Event 'Confirmed Launch' (2027-08-30, status 'Confirmed') has 2x Wireless Presenter, status 'Reserved' (Reserved = 2).
 Data: run `npm run fixtures:spm50` first.
 Logged in as Technical Support Staff (vikram.nair@connectsphere.com, password123).</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="88.5" customHeight="1" s="22">
+    <row r="4" ht="71.25" customHeight="1" s="22">
       <c r="A4" s="6" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="26" t="inlineStr">
         <is>
           <t>1. Click Equipment Requests in the side menu
-2. Look for Pending Showcase and Approved Briefing in the list
-3. Type /equipment/requests/&lt;Pending Showcase's reference&gt; into the address bar
-4. Type /equipment/requests/&lt;Approved Briefing's reference&gt; into the address bar</t>
+2. Open the equipment request for the Confirmed Launch event
+3. Look for an 'Update' or 'Reserve' button on the Wireless Presenter line</t>
         </is>
       </c>
     </row>
@@ -8521,23 +8532,23 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr">
-        <is>
-          <t>Event statuses: Under review, Approved</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="57.75" customHeight="1" s="22">
+      <c r="B5" s="26" t="inlineStr">
+        <is>
+          <t>Event status: Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="84.75" customHeight="1" s="22">
       <c r="A6" s="6" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
-        <is>
-          <t>Step 2: Neither event is listed.
- Step 3: The page shows 'This event was not found, or its equipment is not ready for Technical Support yet.' No equipment lines, Update or Reserve buttons are shown.
- Step 4: The same message is shown for Approved Briefing.</t>
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>Step 1: Confirmed Launch is listed, with Event status 'Confirmed'.
+ Step 2: The page shows 'This event is confirmed — its equipment is final. A change now goes through a change request.' The Wireless Presenter line shows the Status chip 'Reserved' and Reserved 2.
+ Step 3: No 'Update' button and no 'Reserve' button are shown.</t>
         </is>
       </c>
     </row>
@@ -8547,7 +8558,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="26" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -8579,11 +8590,11 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="21" t="inlineStr">
-        <is>
-          <t>Step 2: Neither event is listed.
- Step 3: The page shows 'This event was not found, or its equipment is not ready for Technical Support yet.' No equipment lines, Update or Reserve buttons are shown.
- Step 4: The same message is shown for Approved Briefing.</t>
+      <c r="B11" s="19" t="inlineStr">
+        <is>
+          <t>Step 1: Confirmed Launch is listed, with Event status 'Confirmed'.
+ Step 2: The page shows 'This event is confirmed — its equipment is final. A change now goes through a change request.' The Wireless Presenter line shows the Status chip 'Reserved' and Reserved 2.
+ Step 3: No 'Update' button and no 'Reserve' button are shown.</t>
         </is>
       </c>
     </row>
@@ -8648,1245 +8659,11 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="21" t="inlineStr">
-        <is>
-          <t>Step 2: Neither event is listed.
- Step 3: The page shows 'This event was not found, or its equipment is not ready for Technical Support yet.' No equipment lines, Update or Reserve buttons are shown.
- Step 4: The same message is shown for Approved Briefing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="15.75" customHeight="1" s="22">
-      <c r="A19" s="16" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="15.75" customHeight="1" s="22">
-      <c r="A20" s="16" t="inlineStr">
-        <is>
-          <t>Remarks</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="15.75" customHeight="1" s="22">
-      <c r="A21" s="16" t="inlineStr">
-        <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>Kristen</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="15.75" customHeight="1" s="22">
-      <c r="A22" s="16" t="inlineStr">
-        <is>
-          <t>Date of Execution</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="n">
-        <v>46298</v>
-      </c>
-    </row>
-    <row r="23" ht="15.75" customHeight="1" s="22"/>
-    <row r="24" ht="15.75" customHeight="1" s="22"/>
-    <row r="25" ht="15.75" customHeight="1" s="22"/>
-    <row r="26" ht="15.75" customHeight="1" s="22"/>
-    <row r="27" ht="15.75" customHeight="1" s="22"/>
-    <row r="28" ht="15.75" customHeight="1" s="22"/>
-    <row r="29" ht="15.75" customHeight="1" s="22"/>
-    <row r="30" ht="15.75" customHeight="1" s="22"/>
-    <row r="31" ht="15.75" customHeight="1" s="22"/>
-    <row r="32" ht="15.75" customHeight="1" s="22"/>
-    <row r="33" ht="15.75" customHeight="1" s="22"/>
-    <row r="34" ht="15.75" customHeight="1" s="22"/>
-    <row r="35" ht="15.75" customHeight="1" s="22"/>
-    <row r="36" ht="15.75" customHeight="1" s="22"/>
-    <row r="37" ht="15.75" customHeight="1" s="22"/>
-    <row r="38" ht="15.75" customHeight="1" s="22"/>
-    <row r="39" ht="15.75" customHeight="1" s="22"/>
-    <row r="40" ht="15.75" customHeight="1" s="22"/>
-    <row r="41" ht="15.75" customHeight="1" s="22"/>
-    <row r="42" ht="15.75" customHeight="1" s="22"/>
-    <row r="43" ht="15.75" customHeight="1" s="22"/>
-    <row r="44" ht="15.75" customHeight="1" s="22"/>
-    <row r="45" ht="15.75" customHeight="1" s="22"/>
-    <row r="46" ht="15.75" customHeight="1" s="22"/>
-    <row r="47" ht="15.75" customHeight="1" s="22"/>
-    <row r="48" ht="15.75" customHeight="1" s="22"/>
-    <row r="49" ht="15.75" customHeight="1" s="22"/>
-    <row r="50" ht="15.75" customHeight="1" s="22"/>
-    <row r="51" ht="15.75" customHeight="1" s="22"/>
-    <row r="52" ht="15.75" customHeight="1" s="22"/>
-    <row r="53" ht="15.75" customHeight="1" s="22"/>
-    <row r="54" ht="15.75" customHeight="1" s="22"/>
-    <row r="55" ht="15.75" customHeight="1" s="22"/>
-    <row r="56" ht="15.75" customHeight="1" s="22"/>
-    <row r="57" ht="15.75" customHeight="1" s="22"/>
-    <row r="58" ht="15.75" customHeight="1" s="22"/>
-    <row r="59" ht="15.75" customHeight="1" s="22"/>
-    <row r="60" ht="15.75" customHeight="1" s="22"/>
-    <row r="61" ht="15.75" customHeight="1" s="22"/>
-    <row r="62" ht="15.75" customHeight="1" s="22"/>
-    <row r="63" ht="15.75" customHeight="1" s="22"/>
-    <row r="64" ht="15.75" customHeight="1" s="22"/>
-    <row r="65" ht="15.75" customHeight="1" s="22"/>
-    <row r="66" ht="15.75" customHeight="1" s="22"/>
-    <row r="67" ht="15.75" customHeight="1" s="22"/>
-    <row r="68" ht="15.75" customHeight="1" s="22"/>
-    <row r="69" ht="15.75" customHeight="1" s="22"/>
-    <row r="70" ht="15.75" customHeight="1" s="22"/>
-    <row r="71" ht="15.75" customHeight="1" s="22"/>
-    <row r="72" ht="15.75" customHeight="1" s="22"/>
-    <row r="73" ht="15.75" customHeight="1" s="22"/>
-    <row r="74" ht="15.75" customHeight="1" s="22"/>
-    <row r="75" ht="15.75" customHeight="1" s="22"/>
-    <row r="76" ht="15.75" customHeight="1" s="22"/>
-    <row r="77" ht="15.75" customHeight="1" s="22"/>
-    <row r="78" ht="15.75" customHeight="1" s="22"/>
-    <row r="79" ht="15.75" customHeight="1" s="22"/>
-    <row r="80" ht="15.75" customHeight="1" s="22"/>
-    <row r="81" ht="15.75" customHeight="1" s="22"/>
-    <row r="82" ht="15.75" customHeight="1" s="22"/>
-    <row r="83" ht="15.75" customHeight="1" s="22"/>
-    <row r="84" ht="15.75" customHeight="1" s="22"/>
-    <row r="85" ht="15.75" customHeight="1" s="22"/>
-    <row r="86" ht="15.75" customHeight="1" s="22"/>
-    <row r="87" ht="15.75" customHeight="1" s="22"/>
-    <row r="88" ht="15.75" customHeight="1" s="22"/>
-    <row r="89" ht="15.75" customHeight="1" s="22"/>
-    <row r="90" ht="15.75" customHeight="1" s="22"/>
-    <row r="91" ht="15.75" customHeight="1" s="22"/>
-    <row r="92" ht="15.75" customHeight="1" s="22"/>
-    <row r="93" ht="15.75" customHeight="1" s="22"/>
-    <row r="94" ht="15.75" customHeight="1" s="22"/>
-    <row r="95" ht="15.75" customHeight="1" s="22"/>
-    <row r="96" ht="15.75" customHeight="1" s="22"/>
-    <row r="97" ht="15.75" customHeight="1" s="22"/>
-    <row r="98" ht="15.75" customHeight="1" s="22"/>
-    <row r="99" ht="15.75" customHeight="1" s="22"/>
-    <row r="100" ht="15.75" customHeight="1" s="22"/>
-    <row r="101" ht="15.75" customHeight="1" s="22"/>
-    <row r="102" ht="15.75" customHeight="1" s="22"/>
-    <row r="103" ht="15.75" customHeight="1" s="22"/>
-    <row r="104" ht="15.75" customHeight="1" s="22"/>
-    <row r="105" ht="15.75" customHeight="1" s="22"/>
-    <row r="106" ht="15.75" customHeight="1" s="22"/>
-    <row r="107" ht="15.75" customHeight="1" s="22"/>
-    <row r="108" ht="15.75" customHeight="1" s="22"/>
-    <row r="109" ht="15.75" customHeight="1" s="22"/>
-    <row r="110" ht="15.75" customHeight="1" s="22"/>
-    <row r="111" ht="15.75" customHeight="1" s="22"/>
-    <row r="112" ht="15.75" customHeight="1" s="22"/>
-    <row r="113" ht="15.75" customHeight="1" s="22"/>
-    <row r="114" ht="15.75" customHeight="1" s="22"/>
-    <row r="115" ht="15.75" customHeight="1" s="22"/>
-    <row r="116" ht="15.75" customHeight="1" s="22"/>
-    <row r="117" ht="15.75" customHeight="1" s="22"/>
-    <row r="118" ht="15.75" customHeight="1" s="22"/>
-    <row r="119" ht="15.75" customHeight="1" s="22"/>
-    <row r="120" ht="15.75" customHeight="1" s="22"/>
-    <row r="121" ht="15.75" customHeight="1" s="22"/>
-    <row r="122" ht="15.75" customHeight="1" s="22"/>
-    <row r="123" ht="15.75" customHeight="1" s="22"/>
-    <row r="124" ht="15.75" customHeight="1" s="22"/>
-    <row r="125" ht="15.75" customHeight="1" s="22"/>
-    <row r="126" ht="15.75" customHeight="1" s="22"/>
-    <row r="127" ht="15.75" customHeight="1" s="22"/>
-    <row r="128" ht="15.75" customHeight="1" s="22"/>
-    <row r="129" ht="15.75" customHeight="1" s="22"/>
-    <row r="130" ht="15.75" customHeight="1" s="22"/>
-    <row r="131" ht="15.75" customHeight="1" s="22"/>
-    <row r="132" ht="15.75" customHeight="1" s="22"/>
-    <row r="133" ht="15.75" customHeight="1" s="22"/>
-    <row r="134" ht="15.75" customHeight="1" s="22"/>
-    <row r="135" ht="15.75" customHeight="1" s="22"/>
-    <row r="136" ht="15.75" customHeight="1" s="22"/>
-    <row r="137" ht="15.75" customHeight="1" s="22"/>
-    <row r="138" ht="15.75" customHeight="1" s="22"/>
-    <row r="139" ht="15.75" customHeight="1" s="22"/>
-    <row r="140" ht="15.75" customHeight="1" s="22"/>
-    <row r="141" ht="15.75" customHeight="1" s="22"/>
-    <row r="142" ht="15.75" customHeight="1" s="22"/>
-    <row r="143" ht="15.75" customHeight="1" s="22"/>
-    <row r="144" ht="15.75" customHeight="1" s="22"/>
-    <row r="145" ht="15.75" customHeight="1" s="22"/>
-    <row r="146" ht="15.75" customHeight="1" s="22"/>
-    <row r="147" ht="15.75" customHeight="1" s="22"/>
-    <row r="148" ht="15.75" customHeight="1" s="22"/>
-    <row r="149" ht="15.75" customHeight="1" s="22"/>
-    <row r="150" ht="15.75" customHeight="1" s="22"/>
-    <row r="151" ht="15.75" customHeight="1" s="22"/>
-    <row r="152" ht="15.75" customHeight="1" s="22"/>
-    <row r="153" ht="15.75" customHeight="1" s="22"/>
-    <row r="154" ht="15.75" customHeight="1" s="22"/>
-    <row r="155" ht="15.75" customHeight="1" s="22"/>
-    <row r="156" ht="15.75" customHeight="1" s="22"/>
-    <row r="157" ht="15.75" customHeight="1" s="22"/>
-    <row r="158" ht="15.75" customHeight="1" s="22"/>
-    <row r="159" ht="15.75" customHeight="1" s="22"/>
-    <row r="160" ht="15.75" customHeight="1" s="22"/>
-    <row r="161" ht="15.75" customHeight="1" s="22"/>
-    <row r="162" ht="15.75" customHeight="1" s="22"/>
-    <row r="163" ht="15.75" customHeight="1" s="22"/>
-    <row r="164" ht="15.75" customHeight="1" s="22"/>
-    <row r="165" ht="15.75" customHeight="1" s="22"/>
-    <row r="166" ht="15.75" customHeight="1" s="22"/>
-    <row r="167" ht="15.75" customHeight="1" s="22"/>
-    <row r="168" ht="15.75" customHeight="1" s="22"/>
-    <row r="169" ht="15.75" customHeight="1" s="22"/>
-    <row r="170" ht="15.75" customHeight="1" s="22"/>
-    <row r="171" ht="15.75" customHeight="1" s="22"/>
-    <row r="172" ht="15.75" customHeight="1" s="22"/>
-    <row r="173" ht="15.75" customHeight="1" s="22"/>
-    <row r="174" ht="15.75" customHeight="1" s="22"/>
-    <row r="175" ht="15.75" customHeight="1" s="22"/>
-    <row r="176" ht="15.75" customHeight="1" s="22"/>
-    <row r="177" ht="15.75" customHeight="1" s="22"/>
-    <row r="178" ht="15.75" customHeight="1" s="22"/>
-    <row r="179" ht="15.75" customHeight="1" s="22"/>
-    <row r="180" ht="15.75" customHeight="1" s="22"/>
-    <row r="181" ht="15.75" customHeight="1" s="22"/>
-    <row r="182" ht="15.75" customHeight="1" s="22"/>
-    <row r="183" ht="15.75" customHeight="1" s="22"/>
-    <row r="184" ht="15.75" customHeight="1" s="22"/>
-    <row r="185" ht="15.75" customHeight="1" s="22"/>
-    <row r="186" ht="15.75" customHeight="1" s="22"/>
-    <row r="187" ht="15.75" customHeight="1" s="22"/>
-    <row r="188" ht="15.75" customHeight="1" s="22"/>
-    <row r="189" ht="15.75" customHeight="1" s="22"/>
-    <row r="190" ht="15.75" customHeight="1" s="22"/>
-    <row r="191" ht="15.75" customHeight="1" s="22"/>
-    <row r="192" ht="15.75" customHeight="1" s="22"/>
-    <row r="193" ht="15.75" customHeight="1" s="22"/>
-    <row r="194" ht="15.75" customHeight="1" s="22"/>
-    <row r="195" ht="15.75" customHeight="1" s="22"/>
-    <row r="196" ht="15.75" customHeight="1" s="22"/>
-    <row r="197" ht="15.75" customHeight="1" s="22"/>
-    <row r="198" ht="15.75" customHeight="1" s="22"/>
-    <row r="199" ht="15.75" customHeight="1" s="22"/>
-    <row r="200" ht="15.75" customHeight="1" s="22"/>
-    <row r="201" ht="15.75" customHeight="1" s="22"/>
-    <row r="202" ht="15.75" customHeight="1" s="22"/>
-    <row r="203" ht="15.75" customHeight="1" s="22"/>
-    <row r="204" ht="15.75" customHeight="1" s="22"/>
-    <row r="205" ht="15.75" customHeight="1" s="22"/>
-    <row r="206" ht="15.75" customHeight="1" s="22"/>
-    <row r="207" ht="15.75" customHeight="1" s="22"/>
-    <row r="208" ht="15.75" customHeight="1" s="22"/>
-    <row r="209" ht="15.75" customHeight="1" s="22"/>
-    <row r="210" ht="15.75" customHeight="1" s="22"/>
-    <row r="211" ht="15.75" customHeight="1" s="22"/>
-    <row r="212" ht="15.75" customHeight="1" s="22"/>
-    <row r="213" ht="15.75" customHeight="1" s="22"/>
-    <row r="214" ht="15.75" customHeight="1" s="22"/>
-    <row r="215" ht="15.75" customHeight="1" s="22"/>
-    <row r="216" ht="15.75" customHeight="1" s="22"/>
-    <row r="217" ht="15.75" customHeight="1" s="22"/>
-    <row r="218" ht="15.75" customHeight="1" s="22"/>
-    <row r="219" ht="15.75" customHeight="1" s="22"/>
-    <row r="220" ht="15.75" customHeight="1" s="22"/>
-    <row r="221" ht="15.75" customHeight="1" s="22"/>
-    <row r="222" ht="15.75" customHeight="1" s="22"/>
-    <row r="223" ht="15.75" customHeight="1" s="22"/>
-    <row r="224" ht="15.75" customHeight="1" s="22"/>
-    <row r="225" ht="15.75" customHeight="1" s="22"/>
-    <row r="226" ht="15.75" customHeight="1" s="22"/>
-    <row r="227" ht="15.75" customHeight="1" s="22"/>
-    <row r="228" ht="15.75" customHeight="1" s="22"/>
-    <row r="229" ht="15.75" customHeight="1" s="22"/>
-    <row r="230" ht="15.75" customHeight="1" s="22"/>
-    <row r="231" ht="15.75" customHeight="1" s="22"/>
-    <row r="232" ht="15.75" customHeight="1" s="22"/>
-    <row r="233" ht="15.75" customHeight="1" s="22"/>
-    <row r="234" ht="15.75" customHeight="1" s="22"/>
-    <row r="235" ht="15.75" customHeight="1" s="22"/>
-    <row r="236" ht="15.75" customHeight="1" s="22"/>
-    <row r="237" ht="15.75" customHeight="1" s="22"/>
-    <row r="238" ht="15.75" customHeight="1" s="22"/>
-    <row r="239" ht="15.75" customHeight="1" s="22"/>
-    <row r="240" ht="15.75" customHeight="1" s="22"/>
-    <row r="241" ht="15.75" customHeight="1" s="22"/>
-    <row r="242" ht="15.75" customHeight="1" s="22"/>
-    <row r="243" ht="15.75" customHeight="1" s="22"/>
-    <row r="244" ht="15.75" customHeight="1" s="22"/>
-    <row r="245" ht="15.75" customHeight="1" s="22"/>
-    <row r="246" ht="15.75" customHeight="1" s="22"/>
-    <row r="247" ht="15.75" customHeight="1" s="22"/>
-    <row r="248" ht="15.75" customHeight="1" s="22"/>
-    <row r="249" ht="15.75" customHeight="1" s="22"/>
-    <row r="250" ht="15.75" customHeight="1" s="22"/>
-    <row r="251" ht="15.75" customHeight="1" s="22"/>
-    <row r="252" ht="15.75" customHeight="1" s="22"/>
-    <row r="253" ht="15.75" customHeight="1" s="22"/>
-    <row r="254" ht="15.75" customHeight="1" s="22"/>
-    <row r="255" ht="15.75" customHeight="1" s="22"/>
-    <row r="256" ht="15.75" customHeight="1" s="22"/>
-    <row r="257" ht="15.75" customHeight="1" s="22"/>
-    <row r="258" ht="15.75" customHeight="1" s="22"/>
-    <row r="259" ht="15.75" customHeight="1" s="22"/>
-    <row r="260" ht="15.75" customHeight="1" s="22"/>
-    <row r="261" ht="15.75" customHeight="1" s="22"/>
-    <row r="262" ht="15.75" customHeight="1" s="22"/>
-    <row r="263" ht="15.75" customHeight="1" s="22"/>
-    <row r="264" ht="15.75" customHeight="1" s="22"/>
-    <row r="265" ht="15.75" customHeight="1" s="22"/>
-    <row r="266" ht="15.75" customHeight="1" s="22"/>
-    <row r="267" ht="15.75" customHeight="1" s="22"/>
-    <row r="268" ht="15.75" customHeight="1" s="22"/>
-    <row r="269" ht="15.75" customHeight="1" s="22"/>
-    <row r="270" ht="15.75" customHeight="1" s="22"/>
-    <row r="271" ht="15.75" customHeight="1" s="22"/>
-    <row r="272" ht="15.75" customHeight="1" s="22"/>
-    <row r="273" ht="15.75" customHeight="1" s="22"/>
-    <row r="274" ht="15.75" customHeight="1" s="22"/>
-    <row r="275" ht="15.75" customHeight="1" s="22"/>
-    <row r="276" ht="15.75" customHeight="1" s="22"/>
-    <row r="277" ht="15.75" customHeight="1" s="22"/>
-    <row r="278" ht="15.75" customHeight="1" s="22"/>
-    <row r="279" ht="15.75" customHeight="1" s="22"/>
-    <row r="280" ht="15.75" customHeight="1" s="22"/>
-    <row r="281" ht="15.75" customHeight="1" s="22"/>
-    <row r="282" ht="15.75" customHeight="1" s="22"/>
-    <row r="283" ht="15.75" customHeight="1" s="22"/>
-    <row r="284" ht="15.75" customHeight="1" s="22"/>
-    <row r="285" ht="15.75" customHeight="1" s="22"/>
-    <row r="286" ht="15.75" customHeight="1" s="22"/>
-    <row r="287" ht="15.75" customHeight="1" s="22"/>
-    <row r="288" ht="15.75" customHeight="1" s="22"/>
-    <row r="289" ht="15.75" customHeight="1" s="22"/>
-    <row r="290" ht="15.75" customHeight="1" s="22"/>
-    <row r="291" ht="15.75" customHeight="1" s="22"/>
-    <row r="292" ht="15.75" customHeight="1" s="22"/>
-    <row r="293" ht="15.75" customHeight="1" s="22"/>
-    <row r="294" ht="15.75" customHeight="1" s="22"/>
-    <row r="295" ht="15.75" customHeight="1" s="22"/>
-    <row r="296" ht="15.75" customHeight="1" s="22"/>
-    <row r="297" ht="15.75" customHeight="1" s="22"/>
-    <row r="298" ht="15.75" customHeight="1" s="22"/>
-    <row r="299" ht="15.75" customHeight="1" s="22"/>
-    <row r="300" ht="15.75" customHeight="1" s="22"/>
-    <row r="301" ht="15.75" customHeight="1" s="22"/>
-    <row r="302" ht="15.75" customHeight="1" s="22"/>
-    <row r="303" ht="15.75" customHeight="1" s="22"/>
-    <row r="304" ht="15.75" customHeight="1" s="22"/>
-    <row r="305" ht="15.75" customHeight="1" s="22"/>
-    <row r="306" ht="15.75" customHeight="1" s="22"/>
-    <row r="307" ht="15.75" customHeight="1" s="22"/>
-    <row r="308" ht="15.75" customHeight="1" s="22"/>
-    <row r="309" ht="15.75" customHeight="1" s="22"/>
-    <row r="310" ht="15.75" customHeight="1" s="22"/>
-    <row r="311" ht="15.75" customHeight="1" s="22"/>
-    <row r="312" ht="15.75" customHeight="1" s="22"/>
-    <row r="313" ht="15.75" customHeight="1" s="22"/>
-    <row r="314" ht="15.75" customHeight="1" s="22"/>
-    <row r="315" ht="15.75" customHeight="1" s="22"/>
-    <row r="316" ht="15.75" customHeight="1" s="22"/>
-    <row r="317" ht="15.75" customHeight="1" s="22"/>
-    <row r="318" ht="15.75" customHeight="1" s="22"/>
-    <row r="319" ht="15.75" customHeight="1" s="22"/>
-    <row r="320" ht="15.75" customHeight="1" s="22"/>
-    <row r="321" ht="15.75" customHeight="1" s="22"/>
-    <row r="322" ht="15.75" customHeight="1" s="22"/>
-    <row r="323" ht="15.75" customHeight="1" s="22"/>
-    <row r="324" ht="15.75" customHeight="1" s="22"/>
-    <row r="325" ht="15.75" customHeight="1" s="22"/>
-    <row r="326" ht="15.75" customHeight="1" s="22"/>
-    <row r="327" ht="15.75" customHeight="1" s="22"/>
-    <row r="328" ht="15.75" customHeight="1" s="22"/>
-    <row r="329" ht="15.75" customHeight="1" s="22"/>
-    <row r="330" ht="15.75" customHeight="1" s="22"/>
-    <row r="331" ht="15.75" customHeight="1" s="22"/>
-    <row r="332" ht="15.75" customHeight="1" s="22"/>
-    <row r="333" ht="15.75" customHeight="1" s="22"/>
-    <row r="334" ht="15.75" customHeight="1" s="22"/>
-    <row r="335" ht="15.75" customHeight="1" s="22"/>
-    <row r="336" ht="15.75" customHeight="1" s="22"/>
-    <row r="337" ht="15.75" customHeight="1" s="22"/>
-    <row r="338" ht="15.75" customHeight="1" s="22"/>
-    <row r="339" ht="15.75" customHeight="1" s="22"/>
-    <row r="340" ht="15.75" customHeight="1" s="22"/>
-    <row r="341" ht="15.75" customHeight="1" s="22"/>
-    <row r="342" ht="15.75" customHeight="1" s="22"/>
-    <row r="343" ht="15.75" customHeight="1" s="22"/>
-    <row r="344" ht="15.75" customHeight="1" s="22"/>
-    <row r="345" ht="15.75" customHeight="1" s="22"/>
-    <row r="346" ht="15.75" customHeight="1" s="22"/>
-    <row r="347" ht="15.75" customHeight="1" s="22"/>
-    <row r="348" ht="15.75" customHeight="1" s="22"/>
-    <row r="349" ht="15.75" customHeight="1" s="22"/>
-    <row r="350" ht="15.75" customHeight="1" s="22"/>
-    <row r="351" ht="15.75" customHeight="1" s="22"/>
-    <row r="352" ht="15.75" customHeight="1" s="22"/>
-    <row r="353" ht="15.75" customHeight="1" s="22"/>
-    <row r="354" ht="15.75" customHeight="1" s="22"/>
-    <row r="355" ht="15.75" customHeight="1" s="22"/>
-    <row r="356" ht="15.75" customHeight="1" s="22"/>
-    <row r="357" ht="15.75" customHeight="1" s="22"/>
-    <row r="358" ht="15.75" customHeight="1" s="22"/>
-    <row r="359" ht="15.75" customHeight="1" s="22"/>
-    <row r="360" ht="15.75" customHeight="1" s="22"/>
-    <row r="361" ht="15.75" customHeight="1" s="22"/>
-    <row r="362" ht="15.75" customHeight="1" s="22"/>
-    <row r="363" ht="15.75" customHeight="1" s="22"/>
-    <row r="364" ht="15.75" customHeight="1" s="22"/>
-    <row r="365" ht="15.75" customHeight="1" s="22"/>
-    <row r="366" ht="15.75" customHeight="1" s="22"/>
-    <row r="367" ht="15.75" customHeight="1" s="22"/>
-    <row r="368" ht="15.75" customHeight="1" s="22"/>
-    <row r="369" ht="15.75" customHeight="1" s="22"/>
-    <row r="370" ht="15.75" customHeight="1" s="22"/>
-    <row r="371" ht="15.75" customHeight="1" s="22"/>
-    <row r="372" ht="15.75" customHeight="1" s="22"/>
-    <row r="373" ht="15.75" customHeight="1" s="22"/>
-    <row r="374" ht="15.75" customHeight="1" s="22"/>
-    <row r="375" ht="15.75" customHeight="1" s="22"/>
-    <row r="376" ht="15.75" customHeight="1" s="22"/>
-    <row r="377" ht="15.75" customHeight="1" s="22"/>
-    <row r="378" ht="15.75" customHeight="1" s="22"/>
-    <row r="379" ht="15.75" customHeight="1" s="22"/>
-    <row r="380" ht="15.75" customHeight="1" s="22"/>
-    <row r="381" ht="15.75" customHeight="1" s="22"/>
-    <row r="382" ht="15.75" customHeight="1" s="22"/>
-    <row r="383" ht="15.75" customHeight="1" s="22"/>
-    <row r="384" ht="15.75" customHeight="1" s="22"/>
-    <row r="385" ht="15.75" customHeight="1" s="22"/>
-    <row r="386" ht="15.75" customHeight="1" s="22"/>
-    <row r="387" ht="15.75" customHeight="1" s="22"/>
-    <row r="388" ht="15.75" customHeight="1" s="22"/>
-    <row r="389" ht="15.75" customHeight="1" s="22"/>
-    <row r="390" ht="15.75" customHeight="1" s="22"/>
-    <row r="391" ht="15.75" customHeight="1" s="22"/>
-    <row r="392" ht="15.75" customHeight="1" s="22"/>
-    <row r="393" ht="15.75" customHeight="1" s="22"/>
-    <row r="394" ht="15.75" customHeight="1" s="22"/>
-    <row r="395" ht="15.75" customHeight="1" s="22"/>
-    <row r="396" ht="15.75" customHeight="1" s="22"/>
-    <row r="397" ht="15.75" customHeight="1" s="22"/>
-    <row r="398" ht="15.75" customHeight="1" s="22"/>
-    <row r="399" ht="15.75" customHeight="1" s="22"/>
-    <row r="400" ht="15.75" customHeight="1" s="22"/>
-    <row r="401" ht="15.75" customHeight="1" s="22"/>
-    <row r="402" ht="15.75" customHeight="1" s="22"/>
-    <row r="403" ht="15.75" customHeight="1" s="22"/>
-    <row r="404" ht="15.75" customHeight="1" s="22"/>
-    <row r="405" ht="15.75" customHeight="1" s="22"/>
-    <row r="406" ht="15.75" customHeight="1" s="22"/>
-    <row r="407" ht="15.75" customHeight="1" s="22"/>
-    <row r="408" ht="15.75" customHeight="1" s="22"/>
-    <row r="409" ht="15.75" customHeight="1" s="22"/>
-    <row r="410" ht="15.75" customHeight="1" s="22"/>
-    <row r="411" ht="15.75" customHeight="1" s="22"/>
-    <row r="412" ht="15.75" customHeight="1" s="22"/>
-    <row r="413" ht="15.75" customHeight="1" s="22"/>
-    <row r="414" ht="15.75" customHeight="1" s="22"/>
-    <row r="415" ht="15.75" customHeight="1" s="22"/>
-    <row r="416" ht="15.75" customHeight="1" s="22"/>
-    <row r="417" ht="15.75" customHeight="1" s="22"/>
-    <row r="418" ht="15.75" customHeight="1" s="22"/>
-    <row r="419" ht="15.75" customHeight="1" s="22"/>
-    <row r="420" ht="15.75" customHeight="1" s="22"/>
-    <row r="421" ht="15.75" customHeight="1" s="22"/>
-    <row r="422" ht="15.75" customHeight="1" s="22"/>
-    <row r="423" ht="15.75" customHeight="1" s="22"/>
-    <row r="424" ht="15.75" customHeight="1" s="22"/>
-    <row r="425" ht="15.75" customHeight="1" s="22"/>
-    <row r="426" ht="15.75" customHeight="1" s="22"/>
-    <row r="427" ht="15.75" customHeight="1" s="22"/>
-    <row r="428" ht="15.75" customHeight="1" s="22"/>
-    <row r="429" ht="15.75" customHeight="1" s="22"/>
-    <row r="430" ht="15.75" customHeight="1" s="22"/>
-    <row r="431" ht="15.75" customHeight="1" s="22"/>
-    <row r="432" ht="15.75" customHeight="1" s="22"/>
-    <row r="433" ht="15.75" customHeight="1" s="22"/>
-    <row r="434" ht="15.75" customHeight="1" s="22"/>
-    <row r="435" ht="15.75" customHeight="1" s="22"/>
-    <row r="436" ht="15.75" customHeight="1" s="22"/>
-    <row r="437" ht="15.75" customHeight="1" s="22"/>
-    <row r="438" ht="15.75" customHeight="1" s="22"/>
-    <row r="439" ht="15.75" customHeight="1" s="22"/>
-    <row r="440" ht="15.75" customHeight="1" s="22"/>
-    <row r="441" ht="15.75" customHeight="1" s="22"/>
-    <row r="442" ht="15.75" customHeight="1" s="22"/>
-    <row r="443" ht="15.75" customHeight="1" s="22"/>
-    <row r="444" ht="15.75" customHeight="1" s="22"/>
-    <row r="445" ht="15.75" customHeight="1" s="22"/>
-    <row r="446" ht="15.75" customHeight="1" s="22"/>
-    <row r="447" ht="15.75" customHeight="1" s="22"/>
-    <row r="448" ht="15.75" customHeight="1" s="22"/>
-    <row r="449" ht="15.75" customHeight="1" s="22"/>
-    <row r="450" ht="15.75" customHeight="1" s="22"/>
-    <row r="451" ht="15.75" customHeight="1" s="22"/>
-    <row r="452" ht="15.75" customHeight="1" s="22"/>
-    <row r="453" ht="15.75" customHeight="1" s="22"/>
-    <row r="454" ht="15.75" customHeight="1" s="22"/>
-    <row r="455" ht="15.75" customHeight="1" s="22"/>
-    <row r="456" ht="15.75" customHeight="1" s="22"/>
-    <row r="457" ht="15.75" customHeight="1" s="22"/>
-    <row r="458" ht="15.75" customHeight="1" s="22"/>
-    <row r="459" ht="15.75" customHeight="1" s="22"/>
-    <row r="460" ht="15.75" customHeight="1" s="22"/>
-    <row r="461" ht="15.75" customHeight="1" s="22"/>
-    <row r="462" ht="15.75" customHeight="1" s="22"/>
-    <row r="463" ht="15.75" customHeight="1" s="22"/>
-    <row r="464" ht="15.75" customHeight="1" s="22"/>
-    <row r="465" ht="15.75" customHeight="1" s="22"/>
-    <row r="466" ht="15.75" customHeight="1" s="22"/>
-    <row r="467" ht="15.75" customHeight="1" s="22"/>
-    <row r="468" ht="15.75" customHeight="1" s="22"/>
-    <row r="469" ht="15.75" customHeight="1" s="22"/>
-    <row r="470" ht="15.75" customHeight="1" s="22"/>
-    <row r="471" ht="15.75" customHeight="1" s="22"/>
-    <row r="472" ht="15.75" customHeight="1" s="22"/>
-    <row r="473" ht="15.75" customHeight="1" s="22"/>
-    <row r="474" ht="15.75" customHeight="1" s="22"/>
-    <row r="475" ht="15.75" customHeight="1" s="22"/>
-    <row r="476" ht="15.75" customHeight="1" s="22"/>
-    <row r="477" ht="15.75" customHeight="1" s="22"/>
-    <row r="478" ht="15.75" customHeight="1" s="22"/>
-    <row r="479" ht="15.75" customHeight="1" s="22"/>
-    <row r="480" ht="15.75" customHeight="1" s="22"/>
-    <row r="481" ht="15.75" customHeight="1" s="22"/>
-    <row r="482" ht="15.75" customHeight="1" s="22"/>
-    <row r="483" ht="15.75" customHeight="1" s="22"/>
-    <row r="484" ht="15.75" customHeight="1" s="22"/>
-    <row r="485" ht="15.75" customHeight="1" s="22"/>
-    <row r="486" ht="15.75" customHeight="1" s="22"/>
-    <row r="487" ht="15.75" customHeight="1" s="22"/>
-    <row r="488" ht="15.75" customHeight="1" s="22"/>
-    <row r="489" ht="15.75" customHeight="1" s="22"/>
-    <row r="490" ht="15.75" customHeight="1" s="22"/>
-    <row r="491" ht="15.75" customHeight="1" s="22"/>
-    <row r="492" ht="15.75" customHeight="1" s="22"/>
-    <row r="493" ht="15.75" customHeight="1" s="22"/>
-    <row r="494" ht="15.75" customHeight="1" s="22"/>
-    <row r="495" ht="15.75" customHeight="1" s="22"/>
-    <row r="496" ht="15.75" customHeight="1" s="22"/>
-    <row r="497" ht="15.75" customHeight="1" s="22"/>
-    <row r="498" ht="15.75" customHeight="1" s="22"/>
-    <row r="499" ht="15.75" customHeight="1" s="22"/>
-    <row r="500" ht="15.75" customHeight="1" s="22"/>
-    <row r="501" ht="15.75" customHeight="1" s="22"/>
-    <row r="502" ht="15.75" customHeight="1" s="22"/>
-    <row r="503" ht="15.75" customHeight="1" s="22"/>
-    <row r="504" ht="15.75" customHeight="1" s="22"/>
-    <row r="505" ht="15.75" customHeight="1" s="22"/>
-    <row r="506" ht="15.75" customHeight="1" s="22"/>
-    <row r="507" ht="15.75" customHeight="1" s="22"/>
-    <row r="508" ht="15.75" customHeight="1" s="22"/>
-    <row r="509" ht="15.75" customHeight="1" s="22"/>
-    <row r="510" ht="15.75" customHeight="1" s="22"/>
-    <row r="511" ht="15.75" customHeight="1" s="22"/>
-    <row r="512" ht="15.75" customHeight="1" s="22"/>
-    <row r="513" ht="15.75" customHeight="1" s="22"/>
-    <row r="514" ht="15.75" customHeight="1" s="22"/>
-    <row r="515" ht="15.75" customHeight="1" s="22"/>
-    <row r="516" ht="15.75" customHeight="1" s="22"/>
-    <row r="517" ht="15.75" customHeight="1" s="22"/>
-    <row r="518" ht="15.75" customHeight="1" s="22"/>
-    <row r="519" ht="15.75" customHeight="1" s="22"/>
-    <row r="520" ht="15.75" customHeight="1" s="22"/>
-    <row r="521" ht="15.75" customHeight="1" s="22"/>
-    <row r="522" ht="15.75" customHeight="1" s="22"/>
-    <row r="523" ht="15.75" customHeight="1" s="22"/>
-    <row r="524" ht="15.75" customHeight="1" s="22"/>
-    <row r="525" ht="15.75" customHeight="1" s="22"/>
-    <row r="526" ht="15.75" customHeight="1" s="22"/>
-    <row r="527" ht="15.75" customHeight="1" s="22"/>
-    <row r="528" ht="15.75" customHeight="1" s="22"/>
-    <row r="529" ht="15.75" customHeight="1" s="22"/>
-    <row r="530" ht="15.75" customHeight="1" s="22"/>
-    <row r="531" ht="15.75" customHeight="1" s="22"/>
-    <row r="532" ht="15.75" customHeight="1" s="22"/>
-    <row r="533" ht="15.75" customHeight="1" s="22"/>
-    <row r="534" ht="15.75" customHeight="1" s="22"/>
-    <row r="535" ht="15.75" customHeight="1" s="22"/>
-    <row r="536" ht="15.75" customHeight="1" s="22"/>
-    <row r="537" ht="15.75" customHeight="1" s="22"/>
-    <row r="538" ht="15.75" customHeight="1" s="22"/>
-    <row r="539" ht="15.75" customHeight="1" s="22"/>
-    <row r="540" ht="15.75" customHeight="1" s="22"/>
-    <row r="541" ht="15.75" customHeight="1" s="22"/>
-    <row r="542" ht="15.75" customHeight="1" s="22"/>
-    <row r="543" ht="15.75" customHeight="1" s="22"/>
-    <row r="544" ht="15.75" customHeight="1" s="22"/>
-    <row r="545" ht="15.75" customHeight="1" s="22"/>
-    <row r="546" ht="15.75" customHeight="1" s="22"/>
-    <row r="547" ht="15.75" customHeight="1" s="22"/>
-    <row r="548" ht="15.75" customHeight="1" s="22"/>
-    <row r="549" ht="15.75" customHeight="1" s="22"/>
-    <row r="550" ht="15.75" customHeight="1" s="22"/>
-    <row r="551" ht="15.75" customHeight="1" s="22"/>
-    <row r="552" ht="15.75" customHeight="1" s="22"/>
-    <row r="553" ht="15.75" customHeight="1" s="22"/>
-    <row r="554" ht="15.75" customHeight="1" s="22"/>
-    <row r="555" ht="15.75" customHeight="1" s="22"/>
-    <row r="556" ht="15.75" customHeight="1" s="22"/>
-    <row r="557" ht="15.75" customHeight="1" s="22"/>
-    <row r="558" ht="15.75" customHeight="1" s="22"/>
-    <row r="559" ht="15.75" customHeight="1" s="22"/>
-    <row r="560" ht="15.75" customHeight="1" s="22"/>
-    <row r="561" ht="15.75" customHeight="1" s="22"/>
-    <row r="562" ht="15.75" customHeight="1" s="22"/>
-    <row r="563" ht="15.75" customHeight="1" s="22"/>
-    <row r="564" ht="15.75" customHeight="1" s="22"/>
-    <row r="565" ht="15.75" customHeight="1" s="22"/>
-    <row r="566" ht="15.75" customHeight="1" s="22"/>
-    <row r="567" ht="15.75" customHeight="1" s="22"/>
-    <row r="568" ht="15.75" customHeight="1" s="22"/>
-    <row r="569" ht="15.75" customHeight="1" s="22"/>
-    <row r="570" ht="15.75" customHeight="1" s="22"/>
-    <row r="571" ht="15.75" customHeight="1" s="22"/>
-    <row r="572" ht="15.75" customHeight="1" s="22"/>
-    <row r="573" ht="15.75" customHeight="1" s="22"/>
-    <row r="574" ht="15.75" customHeight="1" s="22"/>
-    <row r="575" ht="15.75" customHeight="1" s="22"/>
-    <row r="576" ht="15.75" customHeight="1" s="22"/>
-    <row r="577" ht="15.75" customHeight="1" s="22"/>
-    <row r="578" ht="15.75" customHeight="1" s="22"/>
-    <row r="579" ht="15.75" customHeight="1" s="22"/>
-    <row r="580" ht="15.75" customHeight="1" s="22"/>
-    <row r="581" ht="15.75" customHeight="1" s="22"/>
-    <row r="582" ht="15.75" customHeight="1" s="22"/>
-    <row r="583" ht="15.75" customHeight="1" s="22"/>
-    <row r="584" ht="15.75" customHeight="1" s="22"/>
-    <row r="585" ht="15.75" customHeight="1" s="22"/>
-    <row r="586" ht="15.75" customHeight="1" s="22"/>
-    <row r="587" ht="15.75" customHeight="1" s="22"/>
-    <row r="588" ht="15.75" customHeight="1" s="22"/>
-    <row r="589" ht="15.75" customHeight="1" s="22"/>
-    <row r="590" ht="15.75" customHeight="1" s="22"/>
-    <row r="591" ht="15.75" customHeight="1" s="22"/>
-    <row r="592" ht="15.75" customHeight="1" s="22"/>
-    <row r="593" ht="15.75" customHeight="1" s="22"/>
-    <row r="594" ht="15.75" customHeight="1" s="22"/>
-    <row r="595" ht="15.75" customHeight="1" s="22"/>
-    <row r="596" ht="15.75" customHeight="1" s="22"/>
-    <row r="597" ht="15.75" customHeight="1" s="22"/>
-    <row r="598" ht="15.75" customHeight="1" s="22"/>
-    <row r="599" ht="15.75" customHeight="1" s="22"/>
-    <row r="600" ht="15.75" customHeight="1" s="22"/>
-    <row r="601" ht="15.75" customHeight="1" s="22"/>
-    <row r="602" ht="15.75" customHeight="1" s="22"/>
-    <row r="603" ht="15.75" customHeight="1" s="22"/>
-    <row r="604" ht="15.75" customHeight="1" s="22"/>
-    <row r="605" ht="15.75" customHeight="1" s="22"/>
-    <row r="606" ht="15.75" customHeight="1" s="22"/>
-    <row r="607" ht="15.75" customHeight="1" s="22"/>
-    <row r="608" ht="15.75" customHeight="1" s="22"/>
-    <row r="609" ht="15.75" customHeight="1" s="22"/>
-    <row r="610" ht="15.75" customHeight="1" s="22"/>
-    <row r="611" ht="15.75" customHeight="1" s="22"/>
-    <row r="612" ht="15.75" customHeight="1" s="22"/>
-    <row r="613" ht="15.75" customHeight="1" s="22"/>
-    <row r="614" ht="15.75" customHeight="1" s="22"/>
-    <row r="615" ht="15.75" customHeight="1" s="22"/>
-    <row r="616" ht="15.75" customHeight="1" s="22"/>
-    <row r="617" ht="15.75" customHeight="1" s="22"/>
-    <row r="618" ht="15.75" customHeight="1" s="22"/>
-    <row r="619" ht="15.75" customHeight="1" s="22"/>
-    <row r="620" ht="15.75" customHeight="1" s="22"/>
-    <row r="621" ht="15.75" customHeight="1" s="22"/>
-    <row r="622" ht="15.75" customHeight="1" s="22"/>
-    <row r="623" ht="15.75" customHeight="1" s="22"/>
-    <row r="624" ht="15.75" customHeight="1" s="22"/>
-    <row r="625" ht="15.75" customHeight="1" s="22"/>
-    <row r="626" ht="15.75" customHeight="1" s="22"/>
-    <row r="627" ht="15.75" customHeight="1" s="22"/>
-    <row r="628" ht="15.75" customHeight="1" s="22"/>
-    <row r="629" ht="15.75" customHeight="1" s="22"/>
-    <row r="630" ht="15.75" customHeight="1" s="22"/>
-    <row r="631" ht="15.75" customHeight="1" s="22"/>
-    <row r="632" ht="15.75" customHeight="1" s="22"/>
-    <row r="633" ht="15.75" customHeight="1" s="22"/>
-    <row r="634" ht="15.75" customHeight="1" s="22"/>
-    <row r="635" ht="15.75" customHeight="1" s="22"/>
-    <row r="636" ht="15.75" customHeight="1" s="22"/>
-    <row r="637" ht="15.75" customHeight="1" s="22"/>
-    <row r="638" ht="15.75" customHeight="1" s="22"/>
-    <row r="639" ht="15.75" customHeight="1" s="22"/>
-    <row r="640" ht="15.75" customHeight="1" s="22"/>
-    <row r="641" ht="15.75" customHeight="1" s="22"/>
-    <row r="642" ht="15.75" customHeight="1" s="22"/>
-    <row r="643" ht="15.75" customHeight="1" s="22"/>
-    <row r="644" ht="15.75" customHeight="1" s="22"/>
-    <row r="645" ht="15.75" customHeight="1" s="22"/>
-    <row r="646" ht="15.75" customHeight="1" s="22"/>
-    <row r="647" ht="15.75" customHeight="1" s="22"/>
-    <row r="648" ht="15.75" customHeight="1" s="22"/>
-    <row r="649" ht="15.75" customHeight="1" s="22"/>
-    <row r="650" ht="15.75" customHeight="1" s="22"/>
-    <row r="651" ht="15.75" customHeight="1" s="22"/>
-    <row r="652" ht="15.75" customHeight="1" s="22"/>
-    <row r="653" ht="15.75" customHeight="1" s="22"/>
-    <row r="654" ht="15.75" customHeight="1" s="22"/>
-    <row r="655" ht="15.75" customHeight="1" s="22"/>
-    <row r="656" ht="15.75" customHeight="1" s="22"/>
-    <row r="657" ht="15.75" customHeight="1" s="22"/>
-    <row r="658" ht="15.75" customHeight="1" s="22"/>
-    <row r="659" ht="15.75" customHeight="1" s="22"/>
-    <row r="660" ht="15.75" customHeight="1" s="22"/>
-    <row r="661" ht="15.75" customHeight="1" s="22"/>
-    <row r="662" ht="15.75" customHeight="1" s="22"/>
-    <row r="663" ht="15.75" customHeight="1" s="22"/>
-    <row r="664" ht="15.75" customHeight="1" s="22"/>
-    <row r="665" ht="15.75" customHeight="1" s="22"/>
-    <row r="666" ht="15.75" customHeight="1" s="22"/>
-    <row r="667" ht="15.75" customHeight="1" s="22"/>
-    <row r="668" ht="15.75" customHeight="1" s="22"/>
-    <row r="669" ht="15.75" customHeight="1" s="22"/>
-    <row r="670" ht="15.75" customHeight="1" s="22"/>
-    <row r="671" ht="15.75" customHeight="1" s="22"/>
-    <row r="672" ht="15.75" customHeight="1" s="22"/>
-    <row r="673" ht="15.75" customHeight="1" s="22"/>
-    <row r="674" ht="15.75" customHeight="1" s="22"/>
-    <row r="675" ht="15.75" customHeight="1" s="22"/>
-    <row r="676" ht="15.75" customHeight="1" s="22"/>
-    <row r="677" ht="15.75" customHeight="1" s="22"/>
-    <row r="678" ht="15.75" customHeight="1" s="22"/>
-    <row r="679" ht="15.75" customHeight="1" s="22"/>
-    <row r="680" ht="15.75" customHeight="1" s="22"/>
-    <row r="681" ht="15.75" customHeight="1" s="22"/>
-    <row r="682" ht="15.75" customHeight="1" s="22"/>
-    <row r="683" ht="15.75" customHeight="1" s="22"/>
-    <row r="684" ht="15.75" customHeight="1" s="22"/>
-    <row r="685" ht="15.75" customHeight="1" s="22"/>
-    <row r="686" ht="15.75" customHeight="1" s="22"/>
-    <row r="687" ht="15.75" customHeight="1" s="22"/>
-    <row r="688" ht="15.75" customHeight="1" s="22"/>
-    <row r="689" ht="15.75" customHeight="1" s="22"/>
-    <row r="690" ht="15.75" customHeight="1" s="22"/>
-    <row r="691" ht="15.75" customHeight="1" s="22"/>
-    <row r="692" ht="15.75" customHeight="1" s="22"/>
-    <row r="693" ht="15.75" customHeight="1" s="22"/>
-    <row r="694" ht="15.75" customHeight="1" s="22"/>
-    <row r="695" ht="15.75" customHeight="1" s="22"/>
-    <row r="696" ht="15.75" customHeight="1" s="22"/>
-    <row r="697" ht="15.75" customHeight="1" s="22"/>
-    <row r="698" ht="15.75" customHeight="1" s="22"/>
-    <row r="699" ht="15.75" customHeight="1" s="22"/>
-    <row r="700" ht="15.75" customHeight="1" s="22"/>
-    <row r="701" ht="15.75" customHeight="1" s="22"/>
-    <row r="702" ht="15.75" customHeight="1" s="22"/>
-    <row r="703" ht="15.75" customHeight="1" s="22"/>
-    <row r="704" ht="15.75" customHeight="1" s="22"/>
-    <row r="705" ht="15.75" customHeight="1" s="22"/>
-    <row r="706" ht="15.75" customHeight="1" s="22"/>
-    <row r="707" ht="15.75" customHeight="1" s="22"/>
-    <row r="708" ht="15.75" customHeight="1" s="22"/>
-    <row r="709" ht="15.75" customHeight="1" s="22"/>
-    <row r="710" ht="15.75" customHeight="1" s="22"/>
-    <row r="711" ht="15.75" customHeight="1" s="22"/>
-    <row r="712" ht="15.75" customHeight="1" s="22"/>
-    <row r="713" ht="15.75" customHeight="1" s="22"/>
-    <row r="714" ht="15.75" customHeight="1" s="22"/>
-    <row r="715" ht="15.75" customHeight="1" s="22"/>
-    <row r="716" ht="15.75" customHeight="1" s="22"/>
-    <row r="717" ht="15.75" customHeight="1" s="22"/>
-    <row r="718" ht="15.75" customHeight="1" s="22"/>
-    <row r="719" ht="15.75" customHeight="1" s="22"/>
-    <row r="720" ht="15.75" customHeight="1" s="22"/>
-    <row r="721" ht="15.75" customHeight="1" s="22"/>
-    <row r="722" ht="15.75" customHeight="1" s="22"/>
-    <row r="723" ht="15.75" customHeight="1" s="22"/>
-    <row r="724" ht="15.75" customHeight="1" s="22"/>
-    <row r="725" ht="15.75" customHeight="1" s="22"/>
-    <row r="726" ht="15.75" customHeight="1" s="22"/>
-    <row r="727" ht="15.75" customHeight="1" s="22"/>
-    <row r="728" ht="15.75" customHeight="1" s="22"/>
-    <row r="729" ht="15.75" customHeight="1" s="22"/>
-    <row r="730" ht="15.75" customHeight="1" s="22"/>
-    <row r="731" ht="15.75" customHeight="1" s="22"/>
-    <row r="732" ht="15.75" customHeight="1" s="22"/>
-    <row r="733" ht="15.75" customHeight="1" s="22"/>
-    <row r="734" ht="15.75" customHeight="1" s="22"/>
-    <row r="735" ht="15.75" customHeight="1" s="22"/>
-    <row r="736" ht="15.75" customHeight="1" s="22"/>
-    <row r="737" ht="15.75" customHeight="1" s="22"/>
-    <row r="738" ht="15.75" customHeight="1" s="22"/>
-    <row r="739" ht="15.75" customHeight="1" s="22"/>
-    <row r="740" ht="15.75" customHeight="1" s="22"/>
-    <row r="741" ht="15.75" customHeight="1" s="22"/>
-    <row r="742" ht="15.75" customHeight="1" s="22"/>
-    <row r="743" ht="15.75" customHeight="1" s="22"/>
-    <row r="744" ht="15.75" customHeight="1" s="22"/>
-    <row r="745" ht="15.75" customHeight="1" s="22"/>
-    <row r="746" ht="15.75" customHeight="1" s="22"/>
-    <row r="747" ht="15.75" customHeight="1" s="22"/>
-    <row r="748" ht="15.75" customHeight="1" s="22"/>
-    <row r="749" ht="15.75" customHeight="1" s="22"/>
-    <row r="750" ht="15.75" customHeight="1" s="22"/>
-    <row r="751" ht="15.75" customHeight="1" s="22"/>
-    <row r="752" ht="15.75" customHeight="1" s="22"/>
-    <row r="753" ht="15.75" customHeight="1" s="22"/>
-    <row r="754" ht="15.75" customHeight="1" s="22"/>
-    <row r="755" ht="15.75" customHeight="1" s="22"/>
-    <row r="756" ht="15.75" customHeight="1" s="22"/>
-    <row r="757" ht="15.75" customHeight="1" s="22"/>
-    <row r="758" ht="15.75" customHeight="1" s="22"/>
-    <row r="759" ht="15.75" customHeight="1" s="22"/>
-    <row r="760" ht="15.75" customHeight="1" s="22"/>
-    <row r="761" ht="15.75" customHeight="1" s="22"/>
-    <row r="762" ht="15.75" customHeight="1" s="22"/>
-    <row r="763" ht="15.75" customHeight="1" s="22"/>
-    <row r="764" ht="15.75" customHeight="1" s="22"/>
-    <row r="765" ht="15.75" customHeight="1" s="22"/>
-    <row r="766" ht="15.75" customHeight="1" s="22"/>
-    <row r="767" ht="15.75" customHeight="1" s="22"/>
-    <row r="768" ht="15.75" customHeight="1" s="22"/>
-    <row r="769" ht="15.75" customHeight="1" s="22"/>
-    <row r="770" ht="15.75" customHeight="1" s="22"/>
-    <row r="771" ht="15.75" customHeight="1" s="22"/>
-    <row r="772" ht="15.75" customHeight="1" s="22"/>
-    <row r="773" ht="15.75" customHeight="1" s="22"/>
-    <row r="774" ht="15.75" customHeight="1" s="22"/>
-    <row r="775" ht="15.75" customHeight="1" s="22"/>
-    <row r="776" ht="15.75" customHeight="1" s="22"/>
-    <row r="777" ht="15.75" customHeight="1" s="22"/>
-    <row r="778" ht="15.75" customHeight="1" s="22"/>
-    <row r="779" ht="15.75" customHeight="1" s="22"/>
-    <row r="780" ht="15.75" customHeight="1" s="22"/>
-    <row r="781" ht="15.75" customHeight="1" s="22"/>
-    <row r="782" ht="15.75" customHeight="1" s="22"/>
-    <row r="783" ht="15.75" customHeight="1" s="22"/>
-    <row r="784" ht="15.75" customHeight="1" s="22"/>
-    <row r="785" ht="15.75" customHeight="1" s="22"/>
-    <row r="786" ht="15.75" customHeight="1" s="22"/>
-    <row r="787" ht="15.75" customHeight="1" s="22"/>
-    <row r="788" ht="15.75" customHeight="1" s="22"/>
-    <row r="789" ht="15.75" customHeight="1" s="22"/>
-    <row r="790" ht="15.75" customHeight="1" s="22"/>
-    <row r="791" ht="15.75" customHeight="1" s="22"/>
-    <row r="792" ht="15.75" customHeight="1" s="22"/>
-    <row r="793" ht="15.75" customHeight="1" s="22"/>
-    <row r="794" ht="15.75" customHeight="1" s="22"/>
-    <row r="795" ht="15.75" customHeight="1" s="22"/>
-    <row r="796" ht="15.75" customHeight="1" s="22"/>
-    <row r="797" ht="15.75" customHeight="1" s="22"/>
-    <row r="798" ht="15.75" customHeight="1" s="22"/>
-    <row r="799" ht="15.75" customHeight="1" s="22"/>
-    <row r="800" ht="15.75" customHeight="1" s="22"/>
-    <row r="801" ht="15.75" customHeight="1" s="22"/>
-    <row r="802" ht="15.75" customHeight="1" s="22"/>
-    <row r="803" ht="15.75" customHeight="1" s="22"/>
-    <row r="804" ht="15.75" customHeight="1" s="22"/>
-    <row r="805" ht="15.75" customHeight="1" s="22"/>
-    <row r="806" ht="15.75" customHeight="1" s="22"/>
-    <row r="807" ht="15.75" customHeight="1" s="22"/>
-    <row r="808" ht="15.75" customHeight="1" s="22"/>
-    <row r="809" ht="15.75" customHeight="1" s="22"/>
-    <row r="810" ht="15.75" customHeight="1" s="22"/>
-    <row r="811" ht="15.75" customHeight="1" s="22"/>
-    <row r="812" ht="15.75" customHeight="1" s="22"/>
-    <row r="813" ht="15.75" customHeight="1" s="22"/>
-    <row r="814" ht="15.75" customHeight="1" s="22"/>
-    <row r="815" ht="15.75" customHeight="1" s="22"/>
-    <row r="816" ht="15.75" customHeight="1" s="22"/>
-    <row r="817" ht="15.75" customHeight="1" s="22"/>
-    <row r="818" ht="15.75" customHeight="1" s="22"/>
-    <row r="819" ht="15.75" customHeight="1" s="22"/>
-    <row r="820" ht="15.75" customHeight="1" s="22"/>
-    <row r="821" ht="15.75" customHeight="1" s="22"/>
-    <row r="822" ht="15.75" customHeight="1" s="22"/>
-    <row r="823" ht="15.75" customHeight="1" s="22"/>
-    <row r="824" ht="15.75" customHeight="1" s="22"/>
-    <row r="825" ht="15.75" customHeight="1" s="22"/>
-    <row r="826" ht="15.75" customHeight="1" s="22"/>
-    <row r="827" ht="15.75" customHeight="1" s="22"/>
-    <row r="828" ht="15.75" customHeight="1" s="22"/>
-    <row r="829" ht="15.75" customHeight="1" s="22"/>
-    <row r="830" ht="15.75" customHeight="1" s="22"/>
-    <row r="831" ht="15.75" customHeight="1" s="22"/>
-    <row r="832" ht="15.75" customHeight="1" s="22"/>
-    <row r="833" ht="15.75" customHeight="1" s="22"/>
-    <row r="834" ht="15.75" customHeight="1" s="22"/>
-    <row r="835" ht="15.75" customHeight="1" s="22"/>
-    <row r="836" ht="15.75" customHeight="1" s="22"/>
-    <row r="837" ht="15.75" customHeight="1" s="22"/>
-    <row r="838" ht="15.75" customHeight="1" s="22"/>
-    <row r="839" ht="15.75" customHeight="1" s="22"/>
-    <row r="840" ht="15.75" customHeight="1" s="22"/>
-    <row r="841" ht="15.75" customHeight="1" s="22"/>
-    <row r="842" ht="15.75" customHeight="1" s="22"/>
-    <row r="843" ht="15.75" customHeight="1" s="22"/>
-    <row r="844" ht="15.75" customHeight="1" s="22"/>
-    <row r="845" ht="15.75" customHeight="1" s="22"/>
-    <row r="846" ht="15.75" customHeight="1" s="22"/>
-    <row r="847" ht="15.75" customHeight="1" s="22"/>
-    <row r="848" ht="15.75" customHeight="1" s="22"/>
-    <row r="849" ht="15.75" customHeight="1" s="22"/>
-    <row r="850" ht="15.75" customHeight="1" s="22"/>
-    <row r="851" ht="15.75" customHeight="1" s="22"/>
-    <row r="852" ht="15.75" customHeight="1" s="22"/>
-    <row r="853" ht="15.75" customHeight="1" s="22"/>
-    <row r="854" ht="15.75" customHeight="1" s="22"/>
-    <row r="855" ht="15.75" customHeight="1" s="22"/>
-    <row r="856" ht="15.75" customHeight="1" s="22"/>
-    <row r="857" ht="15.75" customHeight="1" s="22"/>
-    <row r="858" ht="15.75" customHeight="1" s="22"/>
-    <row r="859" ht="15.75" customHeight="1" s="22"/>
-    <row r="860" ht="15.75" customHeight="1" s="22"/>
-    <row r="861" ht="15.75" customHeight="1" s="22"/>
-    <row r="862" ht="15.75" customHeight="1" s="22"/>
-    <row r="863" ht="15.75" customHeight="1" s="22"/>
-    <row r="864" ht="15.75" customHeight="1" s="22"/>
-    <row r="865" ht="15.75" customHeight="1" s="22"/>
-    <row r="866" ht="15.75" customHeight="1" s="22"/>
-    <row r="867" ht="15.75" customHeight="1" s="22"/>
-    <row r="868" ht="15.75" customHeight="1" s="22"/>
-    <row r="869" ht="15.75" customHeight="1" s="22"/>
-    <row r="870" ht="15.75" customHeight="1" s="22"/>
-    <row r="871" ht="15.75" customHeight="1" s="22"/>
-    <row r="872" ht="15.75" customHeight="1" s="22"/>
-    <row r="873" ht="15.75" customHeight="1" s="22"/>
-    <row r="874" ht="15.75" customHeight="1" s="22"/>
-    <row r="875" ht="15.75" customHeight="1" s="22"/>
-    <row r="876" ht="15.75" customHeight="1" s="22"/>
-    <row r="877" ht="15.75" customHeight="1" s="22"/>
-    <row r="878" ht="15.75" customHeight="1" s="22"/>
-    <row r="879" ht="15.75" customHeight="1" s="22"/>
-    <row r="880" ht="15.75" customHeight="1" s="22"/>
-    <row r="881" ht="15.75" customHeight="1" s="22"/>
-    <row r="882" ht="15.75" customHeight="1" s="22"/>
-    <row r="883" ht="15.75" customHeight="1" s="22"/>
-    <row r="884" ht="15.75" customHeight="1" s="22"/>
-    <row r="885" ht="15.75" customHeight="1" s="22"/>
-    <row r="886" ht="15.75" customHeight="1" s="22"/>
-    <row r="887" ht="15.75" customHeight="1" s="22"/>
-    <row r="888" ht="15.75" customHeight="1" s="22"/>
-    <row r="889" ht="15.75" customHeight="1" s="22"/>
-    <row r="890" ht="15.75" customHeight="1" s="22"/>
-    <row r="891" ht="15.75" customHeight="1" s="22"/>
-    <row r="892" ht="15.75" customHeight="1" s="22"/>
-    <row r="893" ht="15.75" customHeight="1" s="22"/>
-    <row r="894" ht="15.75" customHeight="1" s="22"/>
-    <row r="895" ht="15.75" customHeight="1" s="22"/>
-    <row r="896" ht="15.75" customHeight="1" s="22"/>
-    <row r="897" ht="15.75" customHeight="1" s="22"/>
-    <row r="898" ht="15.75" customHeight="1" s="22"/>
-    <row r="899" ht="15.75" customHeight="1" s="22"/>
-    <row r="900" ht="15.75" customHeight="1" s="22"/>
-    <row r="901" ht="15.75" customHeight="1" s="22"/>
-    <row r="902" ht="15.75" customHeight="1" s="22"/>
-    <row r="903" ht="15.75" customHeight="1" s="22"/>
-    <row r="904" ht="15.75" customHeight="1" s="22"/>
-    <row r="905" ht="15.75" customHeight="1" s="22"/>
-    <row r="906" ht="15.75" customHeight="1" s="22"/>
-    <row r="907" ht="15.75" customHeight="1" s="22"/>
-    <row r="908" ht="15.75" customHeight="1" s="22"/>
-    <row r="909" ht="15.75" customHeight="1" s="22"/>
-    <row r="910" ht="15.75" customHeight="1" s="22"/>
-    <row r="911" ht="15.75" customHeight="1" s="22"/>
-    <row r="912" ht="15.75" customHeight="1" s="22"/>
-    <row r="913" ht="15.75" customHeight="1" s="22"/>
-    <row r="914" ht="15.75" customHeight="1" s="22"/>
-    <row r="915" ht="15.75" customHeight="1" s="22"/>
-    <row r="916" ht="15.75" customHeight="1" s="22"/>
-    <row r="917" ht="15.75" customHeight="1" s="22"/>
-    <row r="918" ht="15.75" customHeight="1" s="22"/>
-    <row r="919" ht="15.75" customHeight="1" s="22"/>
-    <row r="920" ht="15.75" customHeight="1" s="22"/>
-    <row r="921" ht="15.75" customHeight="1" s="22"/>
-    <row r="922" ht="15.75" customHeight="1" s="22"/>
-    <row r="923" ht="15.75" customHeight="1" s="22"/>
-    <row r="924" ht="15.75" customHeight="1" s="22"/>
-    <row r="925" ht="15.75" customHeight="1" s="22"/>
-    <row r="926" ht="15.75" customHeight="1" s="22"/>
-    <row r="927" ht="15.75" customHeight="1" s="22"/>
-    <row r="928" ht="15.75" customHeight="1" s="22"/>
-    <row r="929" ht="15.75" customHeight="1" s="22"/>
-    <row r="930" ht="15.75" customHeight="1" s="22"/>
-    <row r="931" ht="15.75" customHeight="1" s="22"/>
-    <row r="932" ht="15.75" customHeight="1" s="22"/>
-    <row r="933" ht="15.75" customHeight="1" s="22"/>
-    <row r="934" ht="15.75" customHeight="1" s="22"/>
-    <row r="935" ht="15.75" customHeight="1" s="22"/>
-    <row r="936" ht="15.75" customHeight="1" s="22"/>
-    <row r="937" ht="15.75" customHeight="1" s="22"/>
-    <row r="938" ht="15.75" customHeight="1" s="22"/>
-    <row r="939" ht="15.75" customHeight="1" s="22"/>
-    <row r="940" ht="15.75" customHeight="1" s="22"/>
-    <row r="941" ht="15.75" customHeight="1" s="22"/>
-    <row r="942" ht="15.75" customHeight="1" s="22"/>
-    <row r="943" ht="15.75" customHeight="1" s="22"/>
-    <row r="944" ht="15.75" customHeight="1" s="22"/>
-    <row r="945" ht="15.75" customHeight="1" s="22"/>
-    <row r="946" ht="15.75" customHeight="1" s="22"/>
-    <row r="947" ht="15.75" customHeight="1" s="22"/>
-    <row r="948" ht="15.75" customHeight="1" s="22"/>
-    <row r="949" ht="15.75" customHeight="1" s="22"/>
-    <row r="950" ht="15.75" customHeight="1" s="22"/>
-    <row r="951" ht="15.75" customHeight="1" s="22"/>
-    <row r="952" ht="15.75" customHeight="1" s="22"/>
-    <row r="953" ht="15.75" customHeight="1" s="22"/>
-    <row r="954" ht="15.75" customHeight="1" s="22"/>
-    <row r="955" ht="15.75" customHeight="1" s="22"/>
-    <row r="956" ht="15.75" customHeight="1" s="22"/>
-    <row r="957" ht="15.75" customHeight="1" s="22"/>
-    <row r="958" ht="15.75" customHeight="1" s="22"/>
-    <row r="959" ht="15.75" customHeight="1" s="22"/>
-    <row r="960" ht="15.75" customHeight="1" s="22"/>
-    <row r="961" ht="15.75" customHeight="1" s="22"/>
-    <row r="962" ht="15.75" customHeight="1" s="22"/>
-    <row r="963" ht="15.75" customHeight="1" s="22"/>
-    <row r="964" ht="15.75" customHeight="1" s="22"/>
-    <row r="965" ht="15.75" customHeight="1" s="22"/>
-    <row r="966" ht="15.75" customHeight="1" s="22"/>
-    <row r="967" ht="15.75" customHeight="1" s="22"/>
-    <row r="968" ht="15.75" customHeight="1" s="22"/>
-    <row r="969" ht="15.75" customHeight="1" s="22"/>
-    <row r="970" ht="15.75" customHeight="1" s="22"/>
-    <row r="971" ht="15.75" customHeight="1" s="22"/>
-    <row r="972" ht="15.75" customHeight="1" s="22"/>
-    <row r="973" ht="15.75" customHeight="1" s="22"/>
-    <row r="974" ht="15.75" customHeight="1" s="22"/>
-    <row r="975" ht="15.75" customHeight="1" s="22"/>
-    <row r="976" ht="15.75" customHeight="1" s="22"/>
-    <row r="977" ht="15.75" customHeight="1" s="22"/>
-    <row r="978" ht="15.75" customHeight="1" s="22"/>
-    <row r="979" ht="15.75" customHeight="1" s="22"/>
-    <row r="980" ht="15.75" customHeight="1" s="22"/>
-    <row r="981" ht="15.75" customHeight="1" s="22"/>
-    <row r="982" ht="15.75" customHeight="1" s="22"/>
-    <row r="983" ht="15.75" customHeight="1" s="22"/>
-    <row r="984" ht="15.75" customHeight="1" s="22"/>
-    <row r="985" ht="15.75" customHeight="1" s="22"/>
-    <row r="986" ht="15.75" customHeight="1" s="22"/>
-    <row r="987" ht="15.75" customHeight="1" s="22"/>
-    <row r="988" ht="15.75" customHeight="1" s="22"/>
-    <row r="989" ht="15.75" customHeight="1" s="22"/>
-    <row r="990" ht="15.75" customHeight="1" s="22"/>
-    <row r="991" ht="15.75" customHeight="1" s="22"/>
-    <row r="992" ht="15.75" customHeight="1" s="22"/>
-    <row r="993" ht="15.75" customHeight="1" s="22"/>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C22"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
-  <cols>
-    <col width="24.75" customWidth="1" style="22" min="1" max="1"/>
-    <col width="56.75" customWidth="1" style="22" min="2" max="2"/>
-    <col width="12.63" customWidth="1" style="22" min="3" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="15.75" customHeight="1" s="22">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="n"/>
-    </row>
-    <row r="2" ht="17.25" customHeight="1" s="22">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>Test Case ID</t>
-        </is>
-      </c>
-      <c r="B2" s="13" t="inlineStr">
-        <is>
-          <t>SPM-50-TC01</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="125.25" customHeight="1" s="22">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>Pre-conditions</t>
-        </is>
-      </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>Event 'Robotics Expo' (2027-08-02, status 'Planning') has two equipment lines recorded by its Coordinator:
-- 2x Wireless Presenter, technical requirements 'Must pair with the stage laptop over USB-C'
-- 3x Confidence Monitor, technical requirements 'Floor wedges facing the speaker, HDMI from the lectern'
-Data: run `npm run fixtures:spm50` first.
-Logged in as Technical Support Staff (vikram.nair@connectsphere.com, password123).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="71.25" customHeight="1" s="22">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Test Steps</t>
-        </is>
-      </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>1. Click Equipment Requests in the side menu
-2. Find the Robotics Expo row in the list
-3. Open the equipment request for the Robotics Expo event
-4. Read the Wireless Presenter line
-5. Read the Confidence Monitor line</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30.75" customHeight="1" s="22">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Test Data</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>Event: Robotics Expo
-Lines: Wireless Presenter x2, Confidence Monitor x3</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="138.75" customHeight="1" s="22">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Expected Result</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>Step 2: The Robotics Expo row shows 'Equipment lines' = 2.
-Step 3: The Equipment request page opens with the heading 'Equipment request' and the subtitle 'Robotics Expo · ' followed by the event's date and time.
-Step 4: The line shows 'Wireless Presenter', Requested 2, its Status chip, and 'Technical requirements: Must pair with the stage laptop over USB-C'.
-Step 5: The line shows 'Confidence Monitor', Requested 3, its Status chip, and 'Technical requirements: Floor wedges facing the speaker, HDMI from the lectern'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="17.25" customHeight="1" s="22">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>Created By</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>Janelle</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="15.75" customHeight="1" s="22">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>Creation Date</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="n">
-        <v>46297</v>
-      </c>
-    </row>
-    <row r="9" ht="15.75" customHeight="1" s="22"/>
-    <row r="10" ht="15.75" customHeight="1" s="22">
-      <c r="A10" s="11" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="n"/>
-      <c r="C10" s="14" t="n"/>
-    </row>
-    <row r="11" ht="15.75" customHeight="1" s="22">
-      <c r="A11" s="16" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>Step 2: The Robotics Expo row shows 'Equipment lines' = 2.
-Step 3: The Equipment request page opens with the heading 'Equipment request' and the subtitle 'Robotics Expo · ' followed by the event's date and time.
-Step 4: The line shows 'Wireless Presenter', Requested 2, its Status chip, and 'Technical requirements: Must pair with the stage laptop over USB-C'.
-Step 5: The line shows 'Confidence Monitor', Requested 3, its Status chip, and 'Technical requirements: Floor wedges facing the speaker, HDMI from the lectern'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="15.75" customHeight="1" s="22">
-      <c r="A12" s="16" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="15.75" customHeight="1" s="22">
-      <c r="A13" s="16" t="inlineStr">
-        <is>
-          <t>Remarks</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="15.75" customHeight="1" s="22">
-      <c r="A14" s="16" t="inlineStr">
-        <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>Janelle</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="15.75" customHeight="1" s="22">
-      <c r="A15" s="16" t="inlineStr">
-        <is>
-          <t>Date of Execution</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="n">
-        <v>46297</v>
-      </c>
-    </row>
-    <row r="16" ht="15.75" customHeight="1" s="22"/>
-    <row r="17" ht="15.75" customHeight="1" s="22">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B17" s="12" t="n"/>
-    </row>
-    <row r="18" ht="15.75" customHeight="1" s="22">
-      <c r="A18" s="16" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="B18" s="13" t="inlineStr">
-        <is>
-          <t>Step 2: The Robotics Expo row shows 'Equipment lines' = 2.
-Step 3: The Equipment request page opens with the heading 'Equipment request' and the subtitle 'Robotics Expo · ' followed by the event's date and time.
-Step 4: The line shows 'Wireless Presenter', Requested 2, its Status chip, and 'Technical requirements: Must pair with the stage laptop over USB-C'.
-Step 5: The line shows 'Confidence Monitor', Requested 3, its Status chip, and 'Technical requirements: Floor wedges facing the speaker, HDMI from the lectern'.</t>
+      <c r="B18" s="19" t="inlineStr">
+        <is>
+          <t>Step 1: Confirmed Launch is listed, with Event status 'Confirmed'.
+ Step 2: The page shows 'This event is confirmed — its equipment is final. A change now goes through a change request.' The Wireless Presenter line shows the Status chip 'Reserved' and Reserved 2.
+ Step 3: No 'Update' button and no 'Reserve' button are shown.</t>
         </is>
       </c>
     </row>
@@ -10920,6 +9697,1425 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C22"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
+  <cols>
+    <col width="24.75" customWidth="1" style="22" min="1" max="1"/>
+    <col width="56.75" customWidth="1" style="22" min="2" max="2"/>
+    <col width="12.63" customWidth="1" style="22" min="3" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.75" customHeight="1" s="22">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="n"/>
+    </row>
+    <row r="2" ht="17.25" customHeight="1" s="22">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="B2" s="26" t="inlineStr">
+        <is>
+          <t>SPM-50-TC14</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="175.5" customHeight="1" s="22">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>Pre-conditions</t>
+        </is>
+      </c>
+      <c r="B3" s="26" t="inlineStr">
+        <is>
+          <t>Rule (team decision, 3 Oct, following the BPMN): Technical Support's lane starts after the Coordinator's 'Record equipment request' - in Planning. Before that, the equipment is only part of the organiser's request.
+Event 'Pending Showcase' (2027-09-06, status 'Under review') and event 'Approved Briefing' (2027-09-13, status 'Approved', the Coordinator has not started planning) each request 1x Wireless Presenter.
+Their references (EVT-…) are printed by `npm run fixtures:spm50`.
+Data: run `npm run fixtures:spm50` first.
+Logged in as Technical Support Staff (vikram.nair@connectsphere.com, password123).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="88.5" customHeight="1" s="22">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Test Steps</t>
+        </is>
+      </c>
+      <c r="B4" s="26" t="inlineStr">
+        <is>
+          <t>1. Click Equipment Requests in the side menu
+2. Look for Pending Showcase and Approved Briefing in the list
+3. Type /equipment/requests/&lt;Pending Showcase's reference&gt; into the address bar
+4. Type /equipment/requests/&lt;Approved Briefing's reference&gt; into the address bar</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="17.25" customHeight="1" s="22">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Test Data</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>Event statuses: Under review, Approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="57.75" customHeight="1" s="22">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>Step 2: Neither event is listed.
+ Step 3: The page shows 'This event was not found, or its equipment is not ready for Technical Support yet.' No equipment lines, Update or Reserve buttons are shown.
+ Step 4: The same message is shown for Approved Briefing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="17.25" customHeight="1" s="22">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Created By</t>
+        </is>
+      </c>
+      <c r="B7" s="26" t="inlineStr">
+        <is>
+          <t>Janelle</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="15.75" customHeight="1" s="22">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Creation Date</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="n">
+        <v>46297</v>
+      </c>
+    </row>
+    <row r="9" ht="15.75" customHeight="1" s="22"/>
+    <row r="10" ht="15.75" customHeight="1" s="22">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="n"/>
+      <c r="C10" s="14" t="n"/>
+    </row>
+    <row r="11" ht="15.75" customHeight="1" s="22">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>Step 2: Neither event is listed.
+ Step 3: The page shows 'This event was not found, or its equipment is not ready for Technical Support yet.' No equipment lines, Update or Reserve buttons are shown.
+ Step 4: The same message is shown for Approved Briefing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15.75" customHeight="1" s="22">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>Pass/Fail/Not Executed/Blocked</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="15.75" customHeight="1" s="22">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15.75" customHeight="1" s="22">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>Janelle</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="15.75" customHeight="1" s="22">
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t>Date of Execution</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="n">
+        <v>46297</v>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1" s="22"/>
+    <row r="17" ht="15.75" customHeight="1" s="22">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="n"/>
+    </row>
+    <row r="18" ht="15.75" customHeight="1" s="22">
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>Step 2: Neither event is listed.
+ Step 3: The page shows 'This event was not found, or its equipment is not ready for Technical Support yet.' No equipment lines, Update or Reserve buttons are shown.
+ Step 4: The same message is shown for Approved Briefing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="15.75" customHeight="1" s="22">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>Pass/Fail/Not Executed/Blocked</t>
+        </is>
+      </c>
+      <c r="B19" s="16" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="15.75" customHeight="1" s="22">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B20" s="16" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="15.75" customHeight="1" s="22">
+      <c r="A21" s="16" t="inlineStr">
+        <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B21" s="16" t="inlineStr">
+        <is>
+          <t>Kristen</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15.75" customHeight="1" s="22">
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t>Date of Execution</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="n">
+        <v>46298</v>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1" s="22"/>
+    <row r="24" ht="15.75" customHeight="1" s="22"/>
+    <row r="25" ht="15.75" customHeight="1" s="22"/>
+    <row r="26" ht="15.75" customHeight="1" s="22"/>
+    <row r="27" ht="15.75" customHeight="1" s="22"/>
+    <row r="28" ht="15.75" customHeight="1" s="22"/>
+    <row r="29" ht="15.75" customHeight="1" s="22"/>
+    <row r="30" ht="15.75" customHeight="1" s="22"/>
+    <row r="31" ht="15.75" customHeight="1" s="22"/>
+    <row r="32" ht="15.75" customHeight="1" s="22"/>
+    <row r="33" ht="15.75" customHeight="1" s="22"/>
+    <row r="34" ht="15.75" customHeight="1" s="22"/>
+    <row r="35" ht="15.75" customHeight="1" s="22"/>
+    <row r="36" ht="15.75" customHeight="1" s="22"/>
+    <row r="37" ht="15.75" customHeight="1" s="22"/>
+    <row r="38" ht="15.75" customHeight="1" s="22"/>
+    <row r="39" ht="15.75" customHeight="1" s="22"/>
+    <row r="40" ht="15.75" customHeight="1" s="22"/>
+    <row r="41" ht="15.75" customHeight="1" s="22"/>
+    <row r="42" ht="15.75" customHeight="1" s="22"/>
+    <row r="43" ht="15.75" customHeight="1" s="22"/>
+    <row r="44" ht="15.75" customHeight="1" s="22"/>
+    <row r="45" ht="15.75" customHeight="1" s="22"/>
+    <row r="46" ht="15.75" customHeight="1" s="22"/>
+    <row r="47" ht="15.75" customHeight="1" s="22"/>
+    <row r="48" ht="15.75" customHeight="1" s="22"/>
+    <row r="49" ht="15.75" customHeight="1" s="22"/>
+    <row r="50" ht="15.75" customHeight="1" s="22"/>
+    <row r="51" ht="15.75" customHeight="1" s="22"/>
+    <row r="52" ht="15.75" customHeight="1" s="22"/>
+    <row r="53" ht="15.75" customHeight="1" s="22"/>
+    <row r="54" ht="15.75" customHeight="1" s="22"/>
+    <row r="55" ht="15.75" customHeight="1" s="22"/>
+    <row r="56" ht="15.75" customHeight="1" s="22"/>
+    <row r="57" ht="15.75" customHeight="1" s="22"/>
+    <row r="58" ht="15.75" customHeight="1" s="22"/>
+    <row r="59" ht="15.75" customHeight="1" s="22"/>
+    <row r="60" ht="15.75" customHeight="1" s="22"/>
+    <row r="61" ht="15.75" customHeight="1" s="22"/>
+    <row r="62" ht="15.75" customHeight="1" s="22"/>
+    <row r="63" ht="15.75" customHeight="1" s="22"/>
+    <row r="64" ht="15.75" customHeight="1" s="22"/>
+    <row r="65" ht="15.75" customHeight="1" s="22"/>
+    <row r="66" ht="15.75" customHeight="1" s="22"/>
+    <row r="67" ht="15.75" customHeight="1" s="22"/>
+    <row r="68" ht="15.75" customHeight="1" s="22"/>
+    <row r="69" ht="15.75" customHeight="1" s="22"/>
+    <row r="70" ht="15.75" customHeight="1" s="22"/>
+    <row r="71" ht="15.75" customHeight="1" s="22"/>
+    <row r="72" ht="15.75" customHeight="1" s="22"/>
+    <row r="73" ht="15.75" customHeight="1" s="22"/>
+    <row r="74" ht="15.75" customHeight="1" s="22"/>
+    <row r="75" ht="15.75" customHeight="1" s="22"/>
+    <row r="76" ht="15.75" customHeight="1" s="22"/>
+    <row r="77" ht="15.75" customHeight="1" s="22"/>
+    <row r="78" ht="15.75" customHeight="1" s="22"/>
+    <row r="79" ht="15.75" customHeight="1" s="22"/>
+    <row r="80" ht="15.75" customHeight="1" s="22"/>
+    <row r="81" ht="15.75" customHeight="1" s="22"/>
+    <row r="82" ht="15.75" customHeight="1" s="22"/>
+    <row r="83" ht="15.75" customHeight="1" s="22"/>
+    <row r="84" ht="15.75" customHeight="1" s="22"/>
+    <row r="85" ht="15.75" customHeight="1" s="22"/>
+    <row r="86" ht="15.75" customHeight="1" s="22"/>
+    <row r="87" ht="15.75" customHeight="1" s="22"/>
+    <row r="88" ht="15.75" customHeight="1" s="22"/>
+    <row r="89" ht="15.75" customHeight="1" s="22"/>
+    <row r="90" ht="15.75" customHeight="1" s="22"/>
+    <row r="91" ht="15.75" customHeight="1" s="22"/>
+    <row r="92" ht="15.75" customHeight="1" s="22"/>
+    <row r="93" ht="15.75" customHeight="1" s="22"/>
+    <row r="94" ht="15.75" customHeight="1" s="22"/>
+    <row r="95" ht="15.75" customHeight="1" s="22"/>
+    <row r="96" ht="15.75" customHeight="1" s="22"/>
+    <row r="97" ht="15.75" customHeight="1" s="22"/>
+    <row r="98" ht="15.75" customHeight="1" s="22"/>
+    <row r="99" ht="15.75" customHeight="1" s="22"/>
+    <row r="100" ht="15.75" customHeight="1" s="22"/>
+    <row r="101" ht="15.75" customHeight="1" s="22"/>
+    <row r="102" ht="15.75" customHeight="1" s="22"/>
+    <row r="103" ht="15.75" customHeight="1" s="22"/>
+    <row r="104" ht="15.75" customHeight="1" s="22"/>
+    <row r="105" ht="15.75" customHeight="1" s="22"/>
+    <row r="106" ht="15.75" customHeight="1" s="22"/>
+    <row r="107" ht="15.75" customHeight="1" s="22"/>
+    <row r="108" ht="15.75" customHeight="1" s="22"/>
+    <row r="109" ht="15.75" customHeight="1" s="22"/>
+    <row r="110" ht="15.75" customHeight="1" s="22"/>
+    <row r="111" ht="15.75" customHeight="1" s="22"/>
+    <row r="112" ht="15.75" customHeight="1" s="22"/>
+    <row r="113" ht="15.75" customHeight="1" s="22"/>
+    <row r="114" ht="15.75" customHeight="1" s="22"/>
+    <row r="115" ht="15.75" customHeight="1" s="22"/>
+    <row r="116" ht="15.75" customHeight="1" s="22"/>
+    <row r="117" ht="15.75" customHeight="1" s="22"/>
+    <row r="118" ht="15.75" customHeight="1" s="22"/>
+    <row r="119" ht="15.75" customHeight="1" s="22"/>
+    <row r="120" ht="15.75" customHeight="1" s="22"/>
+    <row r="121" ht="15.75" customHeight="1" s="22"/>
+    <row r="122" ht="15.75" customHeight="1" s="22"/>
+    <row r="123" ht="15.75" customHeight="1" s="22"/>
+    <row r="124" ht="15.75" customHeight="1" s="22"/>
+    <row r="125" ht="15.75" customHeight="1" s="22"/>
+    <row r="126" ht="15.75" customHeight="1" s="22"/>
+    <row r="127" ht="15.75" customHeight="1" s="22"/>
+    <row r="128" ht="15.75" customHeight="1" s="22"/>
+    <row r="129" ht="15.75" customHeight="1" s="22"/>
+    <row r="130" ht="15.75" customHeight="1" s="22"/>
+    <row r="131" ht="15.75" customHeight="1" s="22"/>
+    <row r="132" ht="15.75" customHeight="1" s="22"/>
+    <row r="133" ht="15.75" customHeight="1" s="22"/>
+    <row r="134" ht="15.75" customHeight="1" s="22"/>
+    <row r="135" ht="15.75" customHeight="1" s="22"/>
+    <row r="136" ht="15.75" customHeight="1" s="22"/>
+    <row r="137" ht="15.75" customHeight="1" s="22"/>
+    <row r="138" ht="15.75" customHeight="1" s="22"/>
+    <row r="139" ht="15.75" customHeight="1" s="22"/>
+    <row r="140" ht="15.75" customHeight="1" s="22"/>
+    <row r="141" ht="15.75" customHeight="1" s="22"/>
+    <row r="142" ht="15.75" customHeight="1" s="22"/>
+    <row r="143" ht="15.75" customHeight="1" s="22"/>
+    <row r="144" ht="15.75" customHeight="1" s="22"/>
+    <row r="145" ht="15.75" customHeight="1" s="22"/>
+    <row r="146" ht="15.75" customHeight="1" s="22"/>
+    <row r="147" ht="15.75" customHeight="1" s="22"/>
+    <row r="148" ht="15.75" customHeight="1" s="22"/>
+    <row r="149" ht="15.75" customHeight="1" s="22"/>
+    <row r="150" ht="15.75" customHeight="1" s="22"/>
+    <row r="151" ht="15.75" customHeight="1" s="22"/>
+    <row r="152" ht="15.75" customHeight="1" s="22"/>
+    <row r="153" ht="15.75" customHeight="1" s="22"/>
+    <row r="154" ht="15.75" customHeight="1" s="22"/>
+    <row r="155" ht="15.75" customHeight="1" s="22"/>
+    <row r="156" ht="15.75" customHeight="1" s="22"/>
+    <row r="157" ht="15.75" customHeight="1" s="22"/>
+    <row r="158" ht="15.75" customHeight="1" s="22"/>
+    <row r="159" ht="15.75" customHeight="1" s="22"/>
+    <row r="160" ht="15.75" customHeight="1" s="22"/>
+    <row r="161" ht="15.75" customHeight="1" s="22"/>
+    <row r="162" ht="15.75" customHeight="1" s="22"/>
+    <row r="163" ht="15.75" customHeight="1" s="22"/>
+    <row r="164" ht="15.75" customHeight="1" s="22"/>
+    <row r="165" ht="15.75" customHeight="1" s="22"/>
+    <row r="166" ht="15.75" customHeight="1" s="22"/>
+    <row r="167" ht="15.75" customHeight="1" s="22"/>
+    <row r="168" ht="15.75" customHeight="1" s="22"/>
+    <row r="169" ht="15.75" customHeight="1" s="22"/>
+    <row r="170" ht="15.75" customHeight="1" s="22"/>
+    <row r="171" ht="15.75" customHeight="1" s="22"/>
+    <row r="172" ht="15.75" customHeight="1" s="22"/>
+    <row r="173" ht="15.75" customHeight="1" s="22"/>
+    <row r="174" ht="15.75" customHeight="1" s="22"/>
+    <row r="175" ht="15.75" customHeight="1" s="22"/>
+    <row r="176" ht="15.75" customHeight="1" s="22"/>
+    <row r="177" ht="15.75" customHeight="1" s="22"/>
+    <row r="178" ht="15.75" customHeight="1" s="22"/>
+    <row r="179" ht="15.75" customHeight="1" s="22"/>
+    <row r="180" ht="15.75" customHeight="1" s="22"/>
+    <row r="181" ht="15.75" customHeight="1" s="22"/>
+    <row r="182" ht="15.75" customHeight="1" s="22"/>
+    <row r="183" ht="15.75" customHeight="1" s="22"/>
+    <row r="184" ht="15.75" customHeight="1" s="22"/>
+    <row r="185" ht="15.75" customHeight="1" s="22"/>
+    <row r="186" ht="15.75" customHeight="1" s="22"/>
+    <row r="187" ht="15.75" customHeight="1" s="22"/>
+    <row r="188" ht="15.75" customHeight="1" s="22"/>
+    <row r="189" ht="15.75" customHeight="1" s="22"/>
+    <row r="190" ht="15.75" customHeight="1" s="22"/>
+    <row r="191" ht="15.75" customHeight="1" s="22"/>
+    <row r="192" ht="15.75" customHeight="1" s="22"/>
+    <row r="193" ht="15.75" customHeight="1" s="22"/>
+    <row r="194" ht="15.75" customHeight="1" s="22"/>
+    <row r="195" ht="15.75" customHeight="1" s="22"/>
+    <row r="196" ht="15.75" customHeight="1" s="22"/>
+    <row r="197" ht="15.75" customHeight="1" s="22"/>
+    <row r="198" ht="15.75" customHeight="1" s="22"/>
+    <row r="199" ht="15.75" customHeight="1" s="22"/>
+    <row r="200" ht="15.75" customHeight="1" s="22"/>
+    <row r="201" ht="15.75" customHeight="1" s="22"/>
+    <row r="202" ht="15.75" customHeight="1" s="22"/>
+    <row r="203" ht="15.75" customHeight="1" s="22"/>
+    <row r="204" ht="15.75" customHeight="1" s="22"/>
+    <row r="205" ht="15.75" customHeight="1" s="22"/>
+    <row r="206" ht="15.75" customHeight="1" s="22"/>
+    <row r="207" ht="15.75" customHeight="1" s="22"/>
+    <row r="208" ht="15.75" customHeight="1" s="22"/>
+    <row r="209" ht="15.75" customHeight="1" s="22"/>
+    <row r="210" ht="15.75" customHeight="1" s="22"/>
+    <row r="211" ht="15.75" customHeight="1" s="22"/>
+    <row r="212" ht="15.75" customHeight="1" s="22"/>
+    <row r="213" ht="15.75" customHeight="1" s="22"/>
+    <row r="214" ht="15.75" customHeight="1" s="22"/>
+    <row r="215" ht="15.75" customHeight="1" s="22"/>
+    <row r="216" ht="15.75" customHeight="1" s="22"/>
+    <row r="217" ht="15.75" customHeight="1" s="22"/>
+    <row r="218" ht="15.75" customHeight="1" s="22"/>
+    <row r="219" ht="15.75" customHeight="1" s="22"/>
+    <row r="220" ht="15.75" customHeight="1" s="22"/>
+    <row r="221" ht="15.75" customHeight="1" s="22"/>
+    <row r="222" ht="15.75" customHeight="1" s="22"/>
+    <row r="223" ht="15.75" customHeight="1" s="22"/>
+    <row r="224" ht="15.75" customHeight="1" s="22"/>
+    <row r="225" ht="15.75" customHeight="1" s="22"/>
+    <row r="226" ht="15.75" customHeight="1" s="22"/>
+    <row r="227" ht="15.75" customHeight="1" s="22"/>
+    <row r="228" ht="15.75" customHeight="1" s="22"/>
+    <row r="229" ht="15.75" customHeight="1" s="22"/>
+    <row r="230" ht="15.75" customHeight="1" s="22"/>
+    <row r="231" ht="15.75" customHeight="1" s="22"/>
+    <row r="232" ht="15.75" customHeight="1" s="22"/>
+    <row r="233" ht="15.75" customHeight="1" s="22"/>
+    <row r="234" ht="15.75" customHeight="1" s="22"/>
+    <row r="235" ht="15.75" customHeight="1" s="22"/>
+    <row r="236" ht="15.75" customHeight="1" s="22"/>
+    <row r="237" ht="15.75" customHeight="1" s="22"/>
+    <row r="238" ht="15.75" customHeight="1" s="22"/>
+    <row r="239" ht="15.75" customHeight="1" s="22"/>
+    <row r="240" ht="15.75" customHeight="1" s="22"/>
+    <row r="241" ht="15.75" customHeight="1" s="22"/>
+    <row r="242" ht="15.75" customHeight="1" s="22"/>
+    <row r="243" ht="15.75" customHeight="1" s="22"/>
+    <row r="244" ht="15.75" customHeight="1" s="22"/>
+    <row r="245" ht="15.75" customHeight="1" s="22"/>
+    <row r="246" ht="15.75" customHeight="1" s="22"/>
+    <row r="247" ht="15.75" customHeight="1" s="22"/>
+    <row r="248" ht="15.75" customHeight="1" s="22"/>
+    <row r="249" ht="15.75" customHeight="1" s="22"/>
+    <row r="250" ht="15.75" customHeight="1" s="22"/>
+    <row r="251" ht="15.75" customHeight="1" s="22"/>
+    <row r="252" ht="15.75" customHeight="1" s="22"/>
+    <row r="253" ht="15.75" customHeight="1" s="22"/>
+    <row r="254" ht="15.75" customHeight="1" s="22"/>
+    <row r="255" ht="15.75" customHeight="1" s="22"/>
+    <row r="256" ht="15.75" customHeight="1" s="22"/>
+    <row r="257" ht="15.75" customHeight="1" s="22"/>
+    <row r="258" ht="15.75" customHeight="1" s="22"/>
+    <row r="259" ht="15.75" customHeight="1" s="22"/>
+    <row r="260" ht="15.75" customHeight="1" s="22"/>
+    <row r="261" ht="15.75" customHeight="1" s="22"/>
+    <row r="262" ht="15.75" customHeight="1" s="22"/>
+    <row r="263" ht="15.75" customHeight="1" s="22"/>
+    <row r="264" ht="15.75" customHeight="1" s="22"/>
+    <row r="265" ht="15.75" customHeight="1" s="22"/>
+    <row r="266" ht="15.75" customHeight="1" s="22"/>
+    <row r="267" ht="15.75" customHeight="1" s="22"/>
+    <row r="268" ht="15.75" customHeight="1" s="22"/>
+    <row r="269" ht="15.75" customHeight="1" s="22"/>
+    <row r="270" ht="15.75" customHeight="1" s="22"/>
+    <row r="271" ht="15.75" customHeight="1" s="22"/>
+    <row r="272" ht="15.75" customHeight="1" s="22"/>
+    <row r="273" ht="15.75" customHeight="1" s="22"/>
+    <row r="274" ht="15.75" customHeight="1" s="22"/>
+    <row r="275" ht="15.75" customHeight="1" s="22"/>
+    <row r="276" ht="15.75" customHeight="1" s="22"/>
+    <row r="277" ht="15.75" customHeight="1" s="22"/>
+    <row r="278" ht="15.75" customHeight="1" s="22"/>
+    <row r="279" ht="15.75" customHeight="1" s="22"/>
+    <row r="280" ht="15.75" customHeight="1" s="22"/>
+    <row r="281" ht="15.75" customHeight="1" s="22"/>
+    <row r="282" ht="15.75" customHeight="1" s="22"/>
+    <row r="283" ht="15.75" customHeight="1" s="22"/>
+    <row r="284" ht="15.75" customHeight="1" s="22"/>
+    <row r="285" ht="15.75" customHeight="1" s="22"/>
+    <row r="286" ht="15.75" customHeight="1" s="22"/>
+    <row r="287" ht="15.75" customHeight="1" s="22"/>
+    <row r="288" ht="15.75" customHeight="1" s="22"/>
+    <row r="289" ht="15.75" customHeight="1" s="22"/>
+    <row r="290" ht="15.75" customHeight="1" s="22"/>
+    <row r="291" ht="15.75" customHeight="1" s="22"/>
+    <row r="292" ht="15.75" customHeight="1" s="22"/>
+    <row r="293" ht="15.75" customHeight="1" s="22"/>
+    <row r="294" ht="15.75" customHeight="1" s="22"/>
+    <row r="295" ht="15.75" customHeight="1" s="22"/>
+    <row r="296" ht="15.75" customHeight="1" s="22"/>
+    <row r="297" ht="15.75" customHeight="1" s="22"/>
+    <row r="298" ht="15.75" customHeight="1" s="22"/>
+    <row r="299" ht="15.75" customHeight="1" s="22"/>
+    <row r="300" ht="15.75" customHeight="1" s="22"/>
+    <row r="301" ht="15.75" customHeight="1" s="22"/>
+    <row r="302" ht="15.75" customHeight="1" s="22"/>
+    <row r="303" ht="15.75" customHeight="1" s="22"/>
+    <row r="304" ht="15.75" customHeight="1" s="22"/>
+    <row r="305" ht="15.75" customHeight="1" s="22"/>
+    <row r="306" ht="15.75" customHeight="1" s="22"/>
+    <row r="307" ht="15.75" customHeight="1" s="22"/>
+    <row r="308" ht="15.75" customHeight="1" s="22"/>
+    <row r="309" ht="15.75" customHeight="1" s="22"/>
+    <row r="310" ht="15.75" customHeight="1" s="22"/>
+    <row r="311" ht="15.75" customHeight="1" s="22"/>
+    <row r="312" ht="15.75" customHeight="1" s="22"/>
+    <row r="313" ht="15.75" customHeight="1" s="22"/>
+    <row r="314" ht="15.75" customHeight="1" s="22"/>
+    <row r="315" ht="15.75" customHeight="1" s="22"/>
+    <row r="316" ht="15.75" customHeight="1" s="22"/>
+    <row r="317" ht="15.75" customHeight="1" s="22"/>
+    <row r="318" ht="15.75" customHeight="1" s="22"/>
+    <row r="319" ht="15.75" customHeight="1" s="22"/>
+    <row r="320" ht="15.75" customHeight="1" s="22"/>
+    <row r="321" ht="15.75" customHeight="1" s="22"/>
+    <row r="322" ht="15.75" customHeight="1" s="22"/>
+    <row r="323" ht="15.75" customHeight="1" s="22"/>
+    <row r="324" ht="15.75" customHeight="1" s="22"/>
+    <row r="325" ht="15.75" customHeight="1" s="22"/>
+    <row r="326" ht="15.75" customHeight="1" s="22"/>
+    <row r="327" ht="15.75" customHeight="1" s="22"/>
+    <row r="328" ht="15.75" customHeight="1" s="22"/>
+    <row r="329" ht="15.75" customHeight="1" s="22"/>
+    <row r="330" ht="15.75" customHeight="1" s="22"/>
+    <row r="331" ht="15.75" customHeight="1" s="22"/>
+    <row r="332" ht="15.75" customHeight="1" s="22"/>
+    <row r="333" ht="15.75" customHeight="1" s="22"/>
+    <row r="334" ht="15.75" customHeight="1" s="22"/>
+    <row r="335" ht="15.75" customHeight="1" s="22"/>
+    <row r="336" ht="15.75" customHeight="1" s="22"/>
+    <row r="337" ht="15.75" customHeight="1" s="22"/>
+    <row r="338" ht="15.75" customHeight="1" s="22"/>
+    <row r="339" ht="15.75" customHeight="1" s="22"/>
+    <row r="340" ht="15.75" customHeight="1" s="22"/>
+    <row r="341" ht="15.75" customHeight="1" s="22"/>
+    <row r="342" ht="15.75" customHeight="1" s="22"/>
+    <row r="343" ht="15.75" customHeight="1" s="22"/>
+    <row r="344" ht="15.75" customHeight="1" s="22"/>
+    <row r="345" ht="15.75" customHeight="1" s="22"/>
+    <row r="346" ht="15.75" customHeight="1" s="22"/>
+    <row r="347" ht="15.75" customHeight="1" s="22"/>
+    <row r="348" ht="15.75" customHeight="1" s="22"/>
+    <row r="349" ht="15.75" customHeight="1" s="22"/>
+    <row r="350" ht="15.75" customHeight="1" s="22"/>
+    <row r="351" ht="15.75" customHeight="1" s="22"/>
+    <row r="352" ht="15.75" customHeight="1" s="22"/>
+    <row r="353" ht="15.75" customHeight="1" s="22"/>
+    <row r="354" ht="15.75" customHeight="1" s="22"/>
+    <row r="355" ht="15.75" customHeight="1" s="22"/>
+    <row r="356" ht="15.75" customHeight="1" s="22"/>
+    <row r="357" ht="15.75" customHeight="1" s="22"/>
+    <row r="358" ht="15.75" customHeight="1" s="22"/>
+    <row r="359" ht="15.75" customHeight="1" s="22"/>
+    <row r="360" ht="15.75" customHeight="1" s="22"/>
+    <row r="361" ht="15.75" customHeight="1" s="22"/>
+    <row r="362" ht="15.75" customHeight="1" s="22"/>
+    <row r="363" ht="15.75" customHeight="1" s="22"/>
+    <row r="364" ht="15.75" customHeight="1" s="22"/>
+    <row r="365" ht="15.75" customHeight="1" s="22"/>
+    <row r="366" ht="15.75" customHeight="1" s="22"/>
+    <row r="367" ht="15.75" customHeight="1" s="22"/>
+    <row r="368" ht="15.75" customHeight="1" s="22"/>
+    <row r="369" ht="15.75" customHeight="1" s="22"/>
+    <row r="370" ht="15.75" customHeight="1" s="22"/>
+    <row r="371" ht="15.75" customHeight="1" s="22"/>
+    <row r="372" ht="15.75" customHeight="1" s="22"/>
+    <row r="373" ht="15.75" customHeight="1" s="22"/>
+    <row r="374" ht="15.75" customHeight="1" s="22"/>
+    <row r="375" ht="15.75" customHeight="1" s="22"/>
+    <row r="376" ht="15.75" customHeight="1" s="22"/>
+    <row r="377" ht="15.75" customHeight="1" s="22"/>
+    <row r="378" ht="15.75" customHeight="1" s="22"/>
+    <row r="379" ht="15.75" customHeight="1" s="22"/>
+    <row r="380" ht="15.75" customHeight="1" s="22"/>
+    <row r="381" ht="15.75" customHeight="1" s="22"/>
+    <row r="382" ht="15.75" customHeight="1" s="22"/>
+    <row r="383" ht="15.75" customHeight="1" s="22"/>
+    <row r="384" ht="15.75" customHeight="1" s="22"/>
+    <row r="385" ht="15.75" customHeight="1" s="22"/>
+    <row r="386" ht="15.75" customHeight="1" s="22"/>
+    <row r="387" ht="15.75" customHeight="1" s="22"/>
+    <row r="388" ht="15.75" customHeight="1" s="22"/>
+    <row r="389" ht="15.75" customHeight="1" s="22"/>
+    <row r="390" ht="15.75" customHeight="1" s="22"/>
+    <row r="391" ht="15.75" customHeight="1" s="22"/>
+    <row r="392" ht="15.75" customHeight="1" s="22"/>
+    <row r="393" ht="15.75" customHeight="1" s="22"/>
+    <row r="394" ht="15.75" customHeight="1" s="22"/>
+    <row r="395" ht="15.75" customHeight="1" s="22"/>
+    <row r="396" ht="15.75" customHeight="1" s="22"/>
+    <row r="397" ht="15.75" customHeight="1" s="22"/>
+    <row r="398" ht="15.75" customHeight="1" s="22"/>
+    <row r="399" ht="15.75" customHeight="1" s="22"/>
+    <row r="400" ht="15.75" customHeight="1" s="22"/>
+    <row r="401" ht="15.75" customHeight="1" s="22"/>
+    <row r="402" ht="15.75" customHeight="1" s="22"/>
+    <row r="403" ht="15.75" customHeight="1" s="22"/>
+    <row r="404" ht="15.75" customHeight="1" s="22"/>
+    <row r="405" ht="15.75" customHeight="1" s="22"/>
+    <row r="406" ht="15.75" customHeight="1" s="22"/>
+    <row r="407" ht="15.75" customHeight="1" s="22"/>
+    <row r="408" ht="15.75" customHeight="1" s="22"/>
+    <row r="409" ht="15.75" customHeight="1" s="22"/>
+    <row r="410" ht="15.75" customHeight="1" s="22"/>
+    <row r="411" ht="15.75" customHeight="1" s="22"/>
+    <row r="412" ht="15.75" customHeight="1" s="22"/>
+    <row r="413" ht="15.75" customHeight="1" s="22"/>
+    <row r="414" ht="15.75" customHeight="1" s="22"/>
+    <row r="415" ht="15.75" customHeight="1" s="22"/>
+    <row r="416" ht="15.75" customHeight="1" s="22"/>
+    <row r="417" ht="15.75" customHeight="1" s="22"/>
+    <row r="418" ht="15.75" customHeight="1" s="22"/>
+    <row r="419" ht="15.75" customHeight="1" s="22"/>
+    <row r="420" ht="15.75" customHeight="1" s="22"/>
+    <row r="421" ht="15.75" customHeight="1" s="22"/>
+    <row r="422" ht="15.75" customHeight="1" s="22"/>
+    <row r="423" ht="15.75" customHeight="1" s="22"/>
+    <row r="424" ht="15.75" customHeight="1" s="22"/>
+    <row r="425" ht="15.75" customHeight="1" s="22"/>
+    <row r="426" ht="15.75" customHeight="1" s="22"/>
+    <row r="427" ht="15.75" customHeight="1" s="22"/>
+    <row r="428" ht="15.75" customHeight="1" s="22"/>
+    <row r="429" ht="15.75" customHeight="1" s="22"/>
+    <row r="430" ht="15.75" customHeight="1" s="22"/>
+    <row r="431" ht="15.75" customHeight="1" s="22"/>
+    <row r="432" ht="15.75" customHeight="1" s="22"/>
+    <row r="433" ht="15.75" customHeight="1" s="22"/>
+    <row r="434" ht="15.75" customHeight="1" s="22"/>
+    <row r="435" ht="15.75" customHeight="1" s="22"/>
+    <row r="436" ht="15.75" customHeight="1" s="22"/>
+    <row r="437" ht="15.75" customHeight="1" s="22"/>
+    <row r="438" ht="15.75" customHeight="1" s="22"/>
+    <row r="439" ht="15.75" customHeight="1" s="22"/>
+    <row r="440" ht="15.75" customHeight="1" s="22"/>
+    <row r="441" ht="15.75" customHeight="1" s="22"/>
+    <row r="442" ht="15.75" customHeight="1" s="22"/>
+    <row r="443" ht="15.75" customHeight="1" s="22"/>
+    <row r="444" ht="15.75" customHeight="1" s="22"/>
+    <row r="445" ht="15.75" customHeight="1" s="22"/>
+    <row r="446" ht="15.75" customHeight="1" s="22"/>
+    <row r="447" ht="15.75" customHeight="1" s="22"/>
+    <row r="448" ht="15.75" customHeight="1" s="22"/>
+    <row r="449" ht="15.75" customHeight="1" s="22"/>
+    <row r="450" ht="15.75" customHeight="1" s="22"/>
+    <row r="451" ht="15.75" customHeight="1" s="22"/>
+    <row r="452" ht="15.75" customHeight="1" s="22"/>
+    <row r="453" ht="15.75" customHeight="1" s="22"/>
+    <row r="454" ht="15.75" customHeight="1" s="22"/>
+    <row r="455" ht="15.75" customHeight="1" s="22"/>
+    <row r="456" ht="15.75" customHeight="1" s="22"/>
+    <row r="457" ht="15.75" customHeight="1" s="22"/>
+    <row r="458" ht="15.75" customHeight="1" s="22"/>
+    <row r="459" ht="15.75" customHeight="1" s="22"/>
+    <row r="460" ht="15.75" customHeight="1" s="22"/>
+    <row r="461" ht="15.75" customHeight="1" s="22"/>
+    <row r="462" ht="15.75" customHeight="1" s="22"/>
+    <row r="463" ht="15.75" customHeight="1" s="22"/>
+    <row r="464" ht="15.75" customHeight="1" s="22"/>
+    <row r="465" ht="15.75" customHeight="1" s="22"/>
+    <row r="466" ht="15.75" customHeight="1" s="22"/>
+    <row r="467" ht="15.75" customHeight="1" s="22"/>
+    <row r="468" ht="15.75" customHeight="1" s="22"/>
+    <row r="469" ht="15.75" customHeight="1" s="22"/>
+    <row r="470" ht="15.75" customHeight="1" s="22"/>
+    <row r="471" ht="15.75" customHeight="1" s="22"/>
+    <row r="472" ht="15.75" customHeight="1" s="22"/>
+    <row r="473" ht="15.75" customHeight="1" s="22"/>
+    <row r="474" ht="15.75" customHeight="1" s="22"/>
+    <row r="475" ht="15.75" customHeight="1" s="22"/>
+    <row r="476" ht="15.75" customHeight="1" s="22"/>
+    <row r="477" ht="15.75" customHeight="1" s="22"/>
+    <row r="478" ht="15.75" customHeight="1" s="22"/>
+    <row r="479" ht="15.75" customHeight="1" s="22"/>
+    <row r="480" ht="15.75" customHeight="1" s="22"/>
+    <row r="481" ht="15.75" customHeight="1" s="22"/>
+    <row r="482" ht="15.75" customHeight="1" s="22"/>
+    <row r="483" ht="15.75" customHeight="1" s="22"/>
+    <row r="484" ht="15.75" customHeight="1" s="22"/>
+    <row r="485" ht="15.75" customHeight="1" s="22"/>
+    <row r="486" ht="15.75" customHeight="1" s="22"/>
+    <row r="487" ht="15.75" customHeight="1" s="22"/>
+    <row r="488" ht="15.75" customHeight="1" s="22"/>
+    <row r="489" ht="15.75" customHeight="1" s="22"/>
+    <row r="490" ht="15.75" customHeight="1" s="22"/>
+    <row r="491" ht="15.75" customHeight="1" s="22"/>
+    <row r="492" ht="15.75" customHeight="1" s="22"/>
+    <row r="493" ht="15.75" customHeight="1" s="22"/>
+    <row r="494" ht="15.75" customHeight="1" s="22"/>
+    <row r="495" ht="15.75" customHeight="1" s="22"/>
+    <row r="496" ht="15.75" customHeight="1" s="22"/>
+    <row r="497" ht="15.75" customHeight="1" s="22"/>
+    <row r="498" ht="15.75" customHeight="1" s="22"/>
+    <row r="499" ht="15.75" customHeight="1" s="22"/>
+    <row r="500" ht="15.75" customHeight="1" s="22"/>
+    <row r="501" ht="15.75" customHeight="1" s="22"/>
+    <row r="502" ht="15.75" customHeight="1" s="22"/>
+    <row r="503" ht="15.75" customHeight="1" s="22"/>
+    <row r="504" ht="15.75" customHeight="1" s="22"/>
+    <row r="505" ht="15.75" customHeight="1" s="22"/>
+    <row r="506" ht="15.75" customHeight="1" s="22"/>
+    <row r="507" ht="15.75" customHeight="1" s="22"/>
+    <row r="508" ht="15.75" customHeight="1" s="22"/>
+    <row r="509" ht="15.75" customHeight="1" s="22"/>
+    <row r="510" ht="15.75" customHeight="1" s="22"/>
+    <row r="511" ht="15.75" customHeight="1" s="22"/>
+    <row r="512" ht="15.75" customHeight="1" s="22"/>
+    <row r="513" ht="15.75" customHeight="1" s="22"/>
+    <row r="514" ht="15.75" customHeight="1" s="22"/>
+    <row r="515" ht="15.75" customHeight="1" s="22"/>
+    <row r="516" ht="15.75" customHeight="1" s="22"/>
+    <row r="517" ht="15.75" customHeight="1" s="22"/>
+    <row r="518" ht="15.75" customHeight="1" s="22"/>
+    <row r="519" ht="15.75" customHeight="1" s="22"/>
+    <row r="520" ht="15.75" customHeight="1" s="22"/>
+    <row r="521" ht="15.75" customHeight="1" s="22"/>
+    <row r="522" ht="15.75" customHeight="1" s="22"/>
+    <row r="523" ht="15.75" customHeight="1" s="22"/>
+    <row r="524" ht="15.75" customHeight="1" s="22"/>
+    <row r="525" ht="15.75" customHeight="1" s="22"/>
+    <row r="526" ht="15.75" customHeight="1" s="22"/>
+    <row r="527" ht="15.75" customHeight="1" s="22"/>
+    <row r="528" ht="15.75" customHeight="1" s="22"/>
+    <row r="529" ht="15.75" customHeight="1" s="22"/>
+    <row r="530" ht="15.75" customHeight="1" s="22"/>
+    <row r="531" ht="15.75" customHeight="1" s="22"/>
+    <row r="532" ht="15.75" customHeight="1" s="22"/>
+    <row r="533" ht="15.75" customHeight="1" s="22"/>
+    <row r="534" ht="15.75" customHeight="1" s="22"/>
+    <row r="535" ht="15.75" customHeight="1" s="22"/>
+    <row r="536" ht="15.75" customHeight="1" s="22"/>
+    <row r="537" ht="15.75" customHeight="1" s="22"/>
+    <row r="538" ht="15.75" customHeight="1" s="22"/>
+    <row r="539" ht="15.75" customHeight="1" s="22"/>
+    <row r="540" ht="15.75" customHeight="1" s="22"/>
+    <row r="541" ht="15.75" customHeight="1" s="22"/>
+    <row r="542" ht="15.75" customHeight="1" s="22"/>
+    <row r="543" ht="15.75" customHeight="1" s="22"/>
+    <row r="544" ht="15.75" customHeight="1" s="22"/>
+    <row r="545" ht="15.75" customHeight="1" s="22"/>
+    <row r="546" ht="15.75" customHeight="1" s="22"/>
+    <row r="547" ht="15.75" customHeight="1" s="22"/>
+    <row r="548" ht="15.75" customHeight="1" s="22"/>
+    <row r="549" ht="15.75" customHeight="1" s="22"/>
+    <row r="550" ht="15.75" customHeight="1" s="22"/>
+    <row r="551" ht="15.75" customHeight="1" s="22"/>
+    <row r="552" ht="15.75" customHeight="1" s="22"/>
+    <row r="553" ht="15.75" customHeight="1" s="22"/>
+    <row r="554" ht="15.75" customHeight="1" s="22"/>
+    <row r="555" ht="15.75" customHeight="1" s="22"/>
+    <row r="556" ht="15.75" customHeight="1" s="22"/>
+    <row r="557" ht="15.75" customHeight="1" s="22"/>
+    <row r="558" ht="15.75" customHeight="1" s="22"/>
+    <row r="559" ht="15.75" customHeight="1" s="22"/>
+    <row r="560" ht="15.75" customHeight="1" s="22"/>
+    <row r="561" ht="15.75" customHeight="1" s="22"/>
+    <row r="562" ht="15.75" customHeight="1" s="22"/>
+    <row r="563" ht="15.75" customHeight="1" s="22"/>
+    <row r="564" ht="15.75" customHeight="1" s="22"/>
+    <row r="565" ht="15.75" customHeight="1" s="22"/>
+    <row r="566" ht="15.75" customHeight="1" s="22"/>
+    <row r="567" ht="15.75" customHeight="1" s="22"/>
+    <row r="568" ht="15.75" customHeight="1" s="22"/>
+    <row r="569" ht="15.75" customHeight="1" s="22"/>
+    <row r="570" ht="15.75" customHeight="1" s="22"/>
+    <row r="571" ht="15.75" customHeight="1" s="22"/>
+    <row r="572" ht="15.75" customHeight="1" s="22"/>
+    <row r="573" ht="15.75" customHeight="1" s="22"/>
+    <row r="574" ht="15.75" customHeight="1" s="22"/>
+    <row r="575" ht="15.75" customHeight="1" s="22"/>
+    <row r="576" ht="15.75" customHeight="1" s="22"/>
+    <row r="577" ht="15.75" customHeight="1" s="22"/>
+    <row r="578" ht="15.75" customHeight="1" s="22"/>
+    <row r="579" ht="15.75" customHeight="1" s="22"/>
+    <row r="580" ht="15.75" customHeight="1" s="22"/>
+    <row r="581" ht="15.75" customHeight="1" s="22"/>
+    <row r="582" ht="15.75" customHeight="1" s="22"/>
+    <row r="583" ht="15.75" customHeight="1" s="22"/>
+    <row r="584" ht="15.75" customHeight="1" s="22"/>
+    <row r="585" ht="15.75" customHeight="1" s="22"/>
+    <row r="586" ht="15.75" customHeight="1" s="22"/>
+    <row r="587" ht="15.75" customHeight="1" s="22"/>
+    <row r="588" ht="15.75" customHeight="1" s="22"/>
+    <row r="589" ht="15.75" customHeight="1" s="22"/>
+    <row r="590" ht="15.75" customHeight="1" s="22"/>
+    <row r="591" ht="15.75" customHeight="1" s="22"/>
+    <row r="592" ht="15.75" customHeight="1" s="22"/>
+    <row r="593" ht="15.75" customHeight="1" s="22"/>
+    <row r="594" ht="15.75" customHeight="1" s="22"/>
+    <row r="595" ht="15.75" customHeight="1" s="22"/>
+    <row r="596" ht="15.75" customHeight="1" s="22"/>
+    <row r="597" ht="15.75" customHeight="1" s="22"/>
+    <row r="598" ht="15.75" customHeight="1" s="22"/>
+    <row r="599" ht="15.75" customHeight="1" s="22"/>
+    <row r="600" ht="15.75" customHeight="1" s="22"/>
+    <row r="601" ht="15.75" customHeight="1" s="22"/>
+    <row r="602" ht="15.75" customHeight="1" s="22"/>
+    <row r="603" ht="15.75" customHeight="1" s="22"/>
+    <row r="604" ht="15.75" customHeight="1" s="22"/>
+    <row r="605" ht="15.75" customHeight="1" s="22"/>
+    <row r="606" ht="15.75" customHeight="1" s="22"/>
+    <row r="607" ht="15.75" customHeight="1" s="22"/>
+    <row r="608" ht="15.75" customHeight="1" s="22"/>
+    <row r="609" ht="15.75" customHeight="1" s="22"/>
+    <row r="610" ht="15.75" customHeight="1" s="22"/>
+    <row r="611" ht="15.75" customHeight="1" s="22"/>
+    <row r="612" ht="15.75" customHeight="1" s="22"/>
+    <row r="613" ht="15.75" customHeight="1" s="22"/>
+    <row r="614" ht="15.75" customHeight="1" s="22"/>
+    <row r="615" ht="15.75" customHeight="1" s="22"/>
+    <row r="616" ht="15.75" customHeight="1" s="22"/>
+    <row r="617" ht="15.75" customHeight="1" s="22"/>
+    <row r="618" ht="15.75" customHeight="1" s="22"/>
+    <row r="619" ht="15.75" customHeight="1" s="22"/>
+    <row r="620" ht="15.75" customHeight="1" s="22"/>
+    <row r="621" ht="15.75" customHeight="1" s="22"/>
+    <row r="622" ht="15.75" customHeight="1" s="22"/>
+    <row r="623" ht="15.75" customHeight="1" s="22"/>
+    <row r="624" ht="15.75" customHeight="1" s="22"/>
+    <row r="625" ht="15.75" customHeight="1" s="22"/>
+    <row r="626" ht="15.75" customHeight="1" s="22"/>
+    <row r="627" ht="15.75" customHeight="1" s="22"/>
+    <row r="628" ht="15.75" customHeight="1" s="22"/>
+    <row r="629" ht="15.75" customHeight="1" s="22"/>
+    <row r="630" ht="15.75" customHeight="1" s="22"/>
+    <row r="631" ht="15.75" customHeight="1" s="22"/>
+    <row r="632" ht="15.75" customHeight="1" s="22"/>
+    <row r="633" ht="15.75" customHeight="1" s="22"/>
+    <row r="634" ht="15.75" customHeight="1" s="22"/>
+    <row r="635" ht="15.75" customHeight="1" s="22"/>
+    <row r="636" ht="15.75" customHeight="1" s="22"/>
+    <row r="637" ht="15.75" customHeight="1" s="22"/>
+    <row r="638" ht="15.75" customHeight="1" s="22"/>
+    <row r="639" ht="15.75" customHeight="1" s="22"/>
+    <row r="640" ht="15.75" customHeight="1" s="22"/>
+    <row r="641" ht="15.75" customHeight="1" s="22"/>
+    <row r="642" ht="15.75" customHeight="1" s="22"/>
+    <row r="643" ht="15.75" customHeight="1" s="22"/>
+    <row r="644" ht="15.75" customHeight="1" s="22"/>
+    <row r="645" ht="15.75" customHeight="1" s="22"/>
+    <row r="646" ht="15.75" customHeight="1" s="22"/>
+    <row r="647" ht="15.75" customHeight="1" s="22"/>
+    <row r="648" ht="15.75" customHeight="1" s="22"/>
+    <row r="649" ht="15.75" customHeight="1" s="22"/>
+    <row r="650" ht="15.75" customHeight="1" s="22"/>
+    <row r="651" ht="15.75" customHeight="1" s="22"/>
+    <row r="652" ht="15.75" customHeight="1" s="22"/>
+    <row r="653" ht="15.75" customHeight="1" s="22"/>
+    <row r="654" ht="15.75" customHeight="1" s="22"/>
+    <row r="655" ht="15.75" customHeight="1" s="22"/>
+    <row r="656" ht="15.75" customHeight="1" s="22"/>
+    <row r="657" ht="15.75" customHeight="1" s="22"/>
+    <row r="658" ht="15.75" customHeight="1" s="22"/>
+    <row r="659" ht="15.75" customHeight="1" s="22"/>
+    <row r="660" ht="15.75" customHeight="1" s="22"/>
+    <row r="661" ht="15.75" customHeight="1" s="22"/>
+    <row r="662" ht="15.75" customHeight="1" s="22"/>
+    <row r="663" ht="15.75" customHeight="1" s="22"/>
+    <row r="664" ht="15.75" customHeight="1" s="22"/>
+    <row r="665" ht="15.75" customHeight="1" s="22"/>
+    <row r="666" ht="15.75" customHeight="1" s="22"/>
+    <row r="667" ht="15.75" customHeight="1" s="22"/>
+    <row r="668" ht="15.75" customHeight="1" s="22"/>
+    <row r="669" ht="15.75" customHeight="1" s="22"/>
+    <row r="670" ht="15.75" customHeight="1" s="22"/>
+    <row r="671" ht="15.75" customHeight="1" s="22"/>
+    <row r="672" ht="15.75" customHeight="1" s="22"/>
+    <row r="673" ht="15.75" customHeight="1" s="22"/>
+    <row r="674" ht="15.75" customHeight="1" s="22"/>
+    <row r="675" ht="15.75" customHeight="1" s="22"/>
+    <row r="676" ht="15.75" customHeight="1" s="22"/>
+    <row r="677" ht="15.75" customHeight="1" s="22"/>
+    <row r="678" ht="15.75" customHeight="1" s="22"/>
+    <row r="679" ht="15.75" customHeight="1" s="22"/>
+    <row r="680" ht="15.75" customHeight="1" s="22"/>
+    <row r="681" ht="15.75" customHeight="1" s="22"/>
+    <row r="682" ht="15.75" customHeight="1" s="22"/>
+    <row r="683" ht="15.75" customHeight="1" s="22"/>
+    <row r="684" ht="15.75" customHeight="1" s="22"/>
+    <row r="685" ht="15.75" customHeight="1" s="22"/>
+    <row r="686" ht="15.75" customHeight="1" s="22"/>
+    <row r="687" ht="15.75" customHeight="1" s="22"/>
+    <row r="688" ht="15.75" customHeight="1" s="22"/>
+    <row r="689" ht="15.75" customHeight="1" s="22"/>
+    <row r="690" ht="15.75" customHeight="1" s="22"/>
+    <row r="691" ht="15.75" customHeight="1" s="22"/>
+    <row r="692" ht="15.75" customHeight="1" s="22"/>
+    <row r="693" ht="15.75" customHeight="1" s="22"/>
+    <row r="694" ht="15.75" customHeight="1" s="22"/>
+    <row r="695" ht="15.75" customHeight="1" s="22"/>
+    <row r="696" ht="15.75" customHeight="1" s="22"/>
+    <row r="697" ht="15.75" customHeight="1" s="22"/>
+    <row r="698" ht="15.75" customHeight="1" s="22"/>
+    <row r="699" ht="15.75" customHeight="1" s="22"/>
+    <row r="700" ht="15.75" customHeight="1" s="22"/>
+    <row r="701" ht="15.75" customHeight="1" s="22"/>
+    <row r="702" ht="15.75" customHeight="1" s="22"/>
+    <row r="703" ht="15.75" customHeight="1" s="22"/>
+    <row r="704" ht="15.75" customHeight="1" s="22"/>
+    <row r="705" ht="15.75" customHeight="1" s="22"/>
+    <row r="706" ht="15.75" customHeight="1" s="22"/>
+    <row r="707" ht="15.75" customHeight="1" s="22"/>
+    <row r="708" ht="15.75" customHeight="1" s="22"/>
+    <row r="709" ht="15.75" customHeight="1" s="22"/>
+    <row r="710" ht="15.75" customHeight="1" s="22"/>
+    <row r="711" ht="15.75" customHeight="1" s="22"/>
+    <row r="712" ht="15.75" customHeight="1" s="22"/>
+    <row r="713" ht="15.75" customHeight="1" s="22"/>
+    <row r="714" ht="15.75" customHeight="1" s="22"/>
+    <row r="715" ht="15.75" customHeight="1" s="22"/>
+    <row r="716" ht="15.75" customHeight="1" s="22"/>
+    <row r="717" ht="15.75" customHeight="1" s="22"/>
+    <row r="718" ht="15.75" customHeight="1" s="22"/>
+    <row r="719" ht="15.75" customHeight="1" s="22"/>
+    <row r="720" ht="15.75" customHeight="1" s="22"/>
+    <row r="721" ht="15.75" customHeight="1" s="22"/>
+    <row r="722" ht="15.75" customHeight="1" s="22"/>
+    <row r="723" ht="15.75" customHeight="1" s="22"/>
+    <row r="724" ht="15.75" customHeight="1" s="22"/>
+    <row r="725" ht="15.75" customHeight="1" s="22"/>
+    <row r="726" ht="15.75" customHeight="1" s="22"/>
+    <row r="727" ht="15.75" customHeight="1" s="22"/>
+    <row r="728" ht="15.75" customHeight="1" s="22"/>
+    <row r="729" ht="15.75" customHeight="1" s="22"/>
+    <row r="730" ht="15.75" customHeight="1" s="22"/>
+    <row r="731" ht="15.75" customHeight="1" s="22"/>
+    <row r="732" ht="15.75" customHeight="1" s="22"/>
+    <row r="733" ht="15.75" customHeight="1" s="22"/>
+    <row r="734" ht="15.75" customHeight="1" s="22"/>
+    <row r="735" ht="15.75" customHeight="1" s="22"/>
+    <row r="736" ht="15.75" customHeight="1" s="22"/>
+    <row r="737" ht="15.75" customHeight="1" s="22"/>
+    <row r="738" ht="15.75" customHeight="1" s="22"/>
+    <row r="739" ht="15.75" customHeight="1" s="22"/>
+    <row r="740" ht="15.75" customHeight="1" s="22"/>
+    <row r="741" ht="15.75" customHeight="1" s="22"/>
+    <row r="742" ht="15.75" customHeight="1" s="22"/>
+    <row r="743" ht="15.75" customHeight="1" s="22"/>
+    <row r="744" ht="15.75" customHeight="1" s="22"/>
+    <row r="745" ht="15.75" customHeight="1" s="22"/>
+    <row r="746" ht="15.75" customHeight="1" s="22"/>
+    <row r="747" ht="15.75" customHeight="1" s="22"/>
+    <row r="748" ht="15.75" customHeight="1" s="22"/>
+    <row r="749" ht="15.75" customHeight="1" s="22"/>
+    <row r="750" ht="15.75" customHeight="1" s="22"/>
+    <row r="751" ht="15.75" customHeight="1" s="22"/>
+    <row r="752" ht="15.75" customHeight="1" s="22"/>
+    <row r="753" ht="15.75" customHeight="1" s="22"/>
+    <row r="754" ht="15.75" customHeight="1" s="22"/>
+    <row r="755" ht="15.75" customHeight="1" s="22"/>
+    <row r="756" ht="15.75" customHeight="1" s="22"/>
+    <row r="757" ht="15.75" customHeight="1" s="22"/>
+    <row r="758" ht="15.75" customHeight="1" s="22"/>
+    <row r="759" ht="15.75" customHeight="1" s="22"/>
+    <row r="760" ht="15.75" customHeight="1" s="22"/>
+    <row r="761" ht="15.75" customHeight="1" s="22"/>
+    <row r="762" ht="15.75" customHeight="1" s="22"/>
+    <row r="763" ht="15.75" customHeight="1" s="22"/>
+    <row r="764" ht="15.75" customHeight="1" s="22"/>
+    <row r="765" ht="15.75" customHeight="1" s="22"/>
+    <row r="766" ht="15.75" customHeight="1" s="22"/>
+    <row r="767" ht="15.75" customHeight="1" s="22"/>
+    <row r="768" ht="15.75" customHeight="1" s="22"/>
+    <row r="769" ht="15.75" customHeight="1" s="22"/>
+    <row r="770" ht="15.75" customHeight="1" s="22"/>
+    <row r="771" ht="15.75" customHeight="1" s="22"/>
+    <row r="772" ht="15.75" customHeight="1" s="22"/>
+    <row r="773" ht="15.75" customHeight="1" s="22"/>
+    <row r="774" ht="15.75" customHeight="1" s="22"/>
+    <row r="775" ht="15.75" customHeight="1" s="22"/>
+    <row r="776" ht="15.75" customHeight="1" s="22"/>
+    <row r="777" ht="15.75" customHeight="1" s="22"/>
+    <row r="778" ht="15.75" customHeight="1" s="22"/>
+    <row r="779" ht="15.75" customHeight="1" s="22"/>
+    <row r="780" ht="15.75" customHeight="1" s="22"/>
+    <row r="781" ht="15.75" customHeight="1" s="22"/>
+    <row r="782" ht="15.75" customHeight="1" s="22"/>
+    <row r="783" ht="15.75" customHeight="1" s="22"/>
+    <row r="784" ht="15.75" customHeight="1" s="22"/>
+    <row r="785" ht="15.75" customHeight="1" s="22"/>
+    <row r="786" ht="15.75" customHeight="1" s="22"/>
+    <row r="787" ht="15.75" customHeight="1" s="22"/>
+    <row r="788" ht="15.75" customHeight="1" s="22"/>
+    <row r="789" ht="15.75" customHeight="1" s="22"/>
+    <row r="790" ht="15.75" customHeight="1" s="22"/>
+    <row r="791" ht="15.75" customHeight="1" s="22"/>
+    <row r="792" ht="15.75" customHeight="1" s="22"/>
+    <row r="793" ht="15.75" customHeight="1" s="22"/>
+    <row r="794" ht="15.75" customHeight="1" s="22"/>
+    <row r="795" ht="15.75" customHeight="1" s="22"/>
+    <row r="796" ht="15.75" customHeight="1" s="22"/>
+    <row r="797" ht="15.75" customHeight="1" s="22"/>
+    <row r="798" ht="15.75" customHeight="1" s="22"/>
+    <row r="799" ht="15.75" customHeight="1" s="22"/>
+    <row r="800" ht="15.75" customHeight="1" s="22"/>
+    <row r="801" ht="15.75" customHeight="1" s="22"/>
+    <row r="802" ht="15.75" customHeight="1" s="22"/>
+    <row r="803" ht="15.75" customHeight="1" s="22"/>
+    <row r="804" ht="15.75" customHeight="1" s="22"/>
+    <row r="805" ht="15.75" customHeight="1" s="22"/>
+    <row r="806" ht="15.75" customHeight="1" s="22"/>
+    <row r="807" ht="15.75" customHeight="1" s="22"/>
+    <row r="808" ht="15.75" customHeight="1" s="22"/>
+    <row r="809" ht="15.75" customHeight="1" s="22"/>
+    <row r="810" ht="15.75" customHeight="1" s="22"/>
+    <row r="811" ht="15.75" customHeight="1" s="22"/>
+    <row r="812" ht="15.75" customHeight="1" s="22"/>
+    <row r="813" ht="15.75" customHeight="1" s="22"/>
+    <row r="814" ht="15.75" customHeight="1" s="22"/>
+    <row r="815" ht="15.75" customHeight="1" s="22"/>
+    <row r="816" ht="15.75" customHeight="1" s="22"/>
+    <row r="817" ht="15.75" customHeight="1" s="22"/>
+    <row r="818" ht="15.75" customHeight="1" s="22"/>
+    <row r="819" ht="15.75" customHeight="1" s="22"/>
+    <row r="820" ht="15.75" customHeight="1" s="22"/>
+    <row r="821" ht="15.75" customHeight="1" s="22"/>
+    <row r="822" ht="15.75" customHeight="1" s="22"/>
+    <row r="823" ht="15.75" customHeight="1" s="22"/>
+    <row r="824" ht="15.75" customHeight="1" s="22"/>
+    <row r="825" ht="15.75" customHeight="1" s="22"/>
+    <row r="826" ht="15.75" customHeight="1" s="22"/>
+    <row r="827" ht="15.75" customHeight="1" s="22"/>
+    <row r="828" ht="15.75" customHeight="1" s="22"/>
+    <row r="829" ht="15.75" customHeight="1" s="22"/>
+    <row r="830" ht="15.75" customHeight="1" s="22"/>
+    <row r="831" ht="15.75" customHeight="1" s="22"/>
+    <row r="832" ht="15.75" customHeight="1" s="22"/>
+    <row r="833" ht="15.75" customHeight="1" s="22"/>
+    <row r="834" ht="15.75" customHeight="1" s="22"/>
+    <row r="835" ht="15.75" customHeight="1" s="22"/>
+    <row r="836" ht="15.75" customHeight="1" s="22"/>
+    <row r="837" ht="15.75" customHeight="1" s="22"/>
+    <row r="838" ht="15.75" customHeight="1" s="22"/>
+    <row r="839" ht="15.75" customHeight="1" s="22"/>
+    <row r="840" ht="15.75" customHeight="1" s="22"/>
+    <row r="841" ht="15.75" customHeight="1" s="22"/>
+    <row r="842" ht="15.75" customHeight="1" s="22"/>
+    <row r="843" ht="15.75" customHeight="1" s="22"/>
+    <row r="844" ht="15.75" customHeight="1" s="22"/>
+    <row r="845" ht="15.75" customHeight="1" s="22"/>
+    <row r="846" ht="15.75" customHeight="1" s="22"/>
+    <row r="847" ht="15.75" customHeight="1" s="22"/>
+    <row r="848" ht="15.75" customHeight="1" s="22"/>
+    <row r="849" ht="15.75" customHeight="1" s="22"/>
+    <row r="850" ht="15.75" customHeight="1" s="22"/>
+    <row r="851" ht="15.75" customHeight="1" s="22"/>
+    <row r="852" ht="15.75" customHeight="1" s="22"/>
+    <row r="853" ht="15.75" customHeight="1" s="22"/>
+    <row r="854" ht="15.75" customHeight="1" s="22"/>
+    <row r="855" ht="15.75" customHeight="1" s="22"/>
+    <row r="856" ht="15.75" customHeight="1" s="22"/>
+    <row r="857" ht="15.75" customHeight="1" s="22"/>
+    <row r="858" ht="15.75" customHeight="1" s="22"/>
+    <row r="859" ht="15.75" customHeight="1" s="22"/>
+    <row r="860" ht="15.75" customHeight="1" s="22"/>
+    <row r="861" ht="15.75" customHeight="1" s="22"/>
+    <row r="862" ht="15.75" customHeight="1" s="22"/>
+    <row r="863" ht="15.75" customHeight="1" s="22"/>
+    <row r="864" ht="15.75" customHeight="1" s="22"/>
+    <row r="865" ht="15.75" customHeight="1" s="22"/>
+    <row r="866" ht="15.75" customHeight="1" s="22"/>
+    <row r="867" ht="15.75" customHeight="1" s="22"/>
+    <row r="868" ht="15.75" customHeight="1" s="22"/>
+    <row r="869" ht="15.75" customHeight="1" s="22"/>
+    <row r="870" ht="15.75" customHeight="1" s="22"/>
+    <row r="871" ht="15.75" customHeight="1" s="22"/>
+    <row r="872" ht="15.75" customHeight="1" s="22"/>
+    <row r="873" ht="15.75" customHeight="1" s="22"/>
+    <row r="874" ht="15.75" customHeight="1" s="22"/>
+    <row r="875" ht="15.75" customHeight="1" s="22"/>
+    <row r="876" ht="15.75" customHeight="1" s="22"/>
+    <row r="877" ht="15.75" customHeight="1" s="22"/>
+    <row r="878" ht="15.75" customHeight="1" s="22"/>
+    <row r="879" ht="15.75" customHeight="1" s="22"/>
+    <row r="880" ht="15.75" customHeight="1" s="22"/>
+    <row r="881" ht="15.75" customHeight="1" s="22"/>
+    <row r="882" ht="15.75" customHeight="1" s="22"/>
+    <row r="883" ht="15.75" customHeight="1" s="22"/>
+    <row r="884" ht="15.75" customHeight="1" s="22"/>
+    <row r="885" ht="15.75" customHeight="1" s="22"/>
+    <row r="886" ht="15.75" customHeight="1" s="22"/>
+    <row r="887" ht="15.75" customHeight="1" s="22"/>
+    <row r="888" ht="15.75" customHeight="1" s="22"/>
+    <row r="889" ht="15.75" customHeight="1" s="22"/>
+    <row r="890" ht="15.75" customHeight="1" s="22"/>
+    <row r="891" ht="15.75" customHeight="1" s="22"/>
+    <row r="892" ht="15.75" customHeight="1" s="22"/>
+    <row r="893" ht="15.75" customHeight="1" s="22"/>
+    <row r="894" ht="15.75" customHeight="1" s="22"/>
+    <row r="895" ht="15.75" customHeight="1" s="22"/>
+    <row r="896" ht="15.75" customHeight="1" s="22"/>
+    <row r="897" ht="15.75" customHeight="1" s="22"/>
+    <row r="898" ht="15.75" customHeight="1" s="22"/>
+    <row r="899" ht="15.75" customHeight="1" s="22"/>
+    <row r="900" ht="15.75" customHeight="1" s="22"/>
+    <row r="901" ht="15.75" customHeight="1" s="22"/>
+    <row r="902" ht="15.75" customHeight="1" s="22"/>
+    <row r="903" ht="15.75" customHeight="1" s="22"/>
+    <row r="904" ht="15.75" customHeight="1" s="22"/>
+    <row r="905" ht="15.75" customHeight="1" s="22"/>
+    <row r="906" ht="15.75" customHeight="1" s="22"/>
+    <row r="907" ht="15.75" customHeight="1" s="22"/>
+    <row r="908" ht="15.75" customHeight="1" s="22"/>
+    <row r="909" ht="15.75" customHeight="1" s="22"/>
+    <row r="910" ht="15.75" customHeight="1" s="22"/>
+    <row r="911" ht="15.75" customHeight="1" s="22"/>
+    <row r="912" ht="15.75" customHeight="1" s="22"/>
+    <row r="913" ht="15.75" customHeight="1" s="22"/>
+    <row r="914" ht="15.75" customHeight="1" s="22"/>
+    <row r="915" ht="15.75" customHeight="1" s="22"/>
+    <row r="916" ht="15.75" customHeight="1" s="22"/>
+    <row r="917" ht="15.75" customHeight="1" s="22"/>
+    <row r="918" ht="15.75" customHeight="1" s="22"/>
+    <row r="919" ht="15.75" customHeight="1" s="22"/>
+    <row r="920" ht="15.75" customHeight="1" s="22"/>
+    <row r="921" ht="15.75" customHeight="1" s="22"/>
+    <row r="922" ht="15.75" customHeight="1" s="22"/>
+    <row r="923" ht="15.75" customHeight="1" s="22"/>
+    <row r="924" ht="15.75" customHeight="1" s="22"/>
+    <row r="925" ht="15.75" customHeight="1" s="22"/>
+    <row r="926" ht="15.75" customHeight="1" s="22"/>
+    <row r="927" ht="15.75" customHeight="1" s="22"/>
+    <row r="928" ht="15.75" customHeight="1" s="22"/>
+    <row r="929" ht="15.75" customHeight="1" s="22"/>
+    <row r="930" ht="15.75" customHeight="1" s="22"/>
+    <row r="931" ht="15.75" customHeight="1" s="22"/>
+    <row r="932" ht="15.75" customHeight="1" s="22"/>
+    <row r="933" ht="15.75" customHeight="1" s="22"/>
+    <row r="934" ht="15.75" customHeight="1" s="22"/>
+    <row r="935" ht="15.75" customHeight="1" s="22"/>
+    <row r="936" ht="15.75" customHeight="1" s="22"/>
+    <row r="937" ht="15.75" customHeight="1" s="22"/>
+    <row r="938" ht="15.75" customHeight="1" s="22"/>
+    <row r="939" ht="15.75" customHeight="1" s="22"/>
+    <row r="940" ht="15.75" customHeight="1" s="22"/>
+    <row r="941" ht="15.75" customHeight="1" s="22"/>
+    <row r="942" ht="15.75" customHeight="1" s="22"/>
+    <row r="943" ht="15.75" customHeight="1" s="22"/>
+    <row r="944" ht="15.75" customHeight="1" s="22"/>
+    <row r="945" ht="15.75" customHeight="1" s="22"/>
+    <row r="946" ht="15.75" customHeight="1" s="22"/>
+    <row r="947" ht="15.75" customHeight="1" s="22"/>
+    <row r="948" ht="15.75" customHeight="1" s="22"/>
+    <row r="949" ht="15.75" customHeight="1" s="22"/>
+    <row r="950" ht="15.75" customHeight="1" s="22"/>
+    <row r="951" ht="15.75" customHeight="1" s="22"/>
+    <row r="952" ht="15.75" customHeight="1" s="22"/>
+    <row r="953" ht="15.75" customHeight="1" s="22"/>
+    <row r="954" ht="15.75" customHeight="1" s="22"/>
+    <row r="955" ht="15.75" customHeight="1" s="22"/>
+    <row r="956" ht="15.75" customHeight="1" s="22"/>
+    <row r="957" ht="15.75" customHeight="1" s="22"/>
+    <row r="958" ht="15.75" customHeight="1" s="22"/>
+    <row r="959" ht="15.75" customHeight="1" s="22"/>
+    <row r="960" ht="15.75" customHeight="1" s="22"/>
+    <row r="961" ht="15.75" customHeight="1" s="22"/>
+    <row r="962" ht="15.75" customHeight="1" s="22"/>
+    <row r="963" ht="15.75" customHeight="1" s="22"/>
+    <row r="964" ht="15.75" customHeight="1" s="22"/>
+    <row r="965" ht="15.75" customHeight="1" s="22"/>
+    <row r="966" ht="15.75" customHeight="1" s="22"/>
+    <row r="967" ht="15.75" customHeight="1" s="22"/>
+    <row r="968" ht="15.75" customHeight="1" s="22"/>
+    <row r="969" ht="15.75" customHeight="1" s="22"/>
+    <row r="970" ht="15.75" customHeight="1" s="22"/>
+    <row r="971" ht="15.75" customHeight="1" s="22"/>
+    <row r="972" ht="15.75" customHeight="1" s="22"/>
+    <row r="973" ht="15.75" customHeight="1" s="22"/>
+    <row r="974" ht="15.75" customHeight="1" s="22"/>
+    <row r="975" ht="15.75" customHeight="1" s="22"/>
+    <row r="976" ht="15.75" customHeight="1" s="22"/>
+    <row r="977" ht="15.75" customHeight="1" s="22"/>
+    <row r="978" ht="15.75" customHeight="1" s="22"/>
+    <row r="979" ht="15.75" customHeight="1" s="22"/>
+    <row r="980" ht="15.75" customHeight="1" s="22"/>
+    <row r="981" ht="15.75" customHeight="1" s="22"/>
+    <row r="982" ht="15.75" customHeight="1" s="22"/>
+    <row r="983" ht="15.75" customHeight="1" s="22"/>
+    <row r="984" ht="15.75" customHeight="1" s="22"/>
+    <row r="985" ht="15.75" customHeight="1" s="22"/>
+    <row r="986" ht="15.75" customHeight="1" s="22"/>
+    <row r="987" ht="15.75" customHeight="1" s="22"/>
+    <row r="988" ht="15.75" customHeight="1" s="22"/>
+    <row r="989" ht="15.75" customHeight="1" s="22"/>
+    <row r="990" ht="15.75" customHeight="1" s="22"/>
+    <row r="991" ht="15.75" customHeight="1" s="22"/>
+    <row r="992" ht="15.75" customHeight="1" s="22"/>
+    <row r="993" ht="15.75" customHeight="1" s="22"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup orientation="landscape"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" style="22" min="1" max="1"/>
+    <col width="75" customWidth="1" style="22" min="2" max="2"/>
+    <col width="40" customWidth="1" style="22" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="27" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="27" t="inlineStr">
+        <is>
+          <t>Question / ambiguity for the PO or developer</t>
+        </is>
+      </c>
+      <c r="C1" s="27" t="inlineStr">
+        <is>
+          <t>Answer</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="85" customHeight="1" s="22">
+      <c r="A2" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="28" t="inlineStr">
+        <is>
+          <t>OPEN - screen design (TC02–TC14): built as an 'Update' panel on each line of the Equipment request page, with 'Fulfilment status' and 'Technical notes' fields and Save / Cancel. Messages such as 'Update saved.', 'Give a reason when equipment cannot be provided.', 'Technical notes must be 500 characters or fewer.' and 'Last updated by …' are our own wording. No AC constrains the design, so the team should confirm it.</t>
+        </is>
+      </c>
+      <c r="C2" s="28" t="n"/>
+    </row>
+    <row r="3" ht="85" customHeight="1" s="22">
+      <c r="A3" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="28" t="inlineStr">
+        <is>
+          <t>DECIDED (Janelle, 2 Oct) - Reserve stays on a line marked 'Cannot be provided': if stock frees up, Technical Support can reserve it in one click. Reserving it clears the old 'cannot be provided' reason, so the line never shows 'Reserved' next to a reason that no longer holds (TC07; reserveClearsStaffNotes() in src/lib/equipmentFulfilment.ts, used by the SPM-49 reserve route).</t>
+        </is>
+      </c>
+      <c r="C3" s="28" t="n"/>
+    </row>
+    <row r="4" ht="58" customHeight="1" s="22">
+      <c r="A4" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="28" t="inlineStr">
+        <is>
+          <t>DECIDED (Janelle, 2 Oct) - no link from the Equipment request page back to the event. The page shows everything Technical Support needs (the Coordinator's requirements, status, notes), and no test case depends on the link.</t>
+        </is>
+      </c>
+      <c r="C4" s="28" t="n"/>
+    </row>
+    <row r="5" ht="58" customHeight="1" s="22">
+      <c r="A5" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="28" t="inlineStr">
+        <is>
+          <t>OPEN - Coordinator changes a quantity after review or reservation (Q&amp;A #114): should the line return to 'Requested' / 'Under review' so it is re-checked? This crosses into SPM-34 / the change-request flow. No case will be written until ownership is settled.</t>
+        </is>
+      </c>
+      <c r="C5" s="28" t="n"/>
+    </row>
+    <row r="6" ht="166" customHeight="1" s="22">
+      <c r="A6" s="28" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="28" t="inlineStr">
+        <is>
+          <t>OPEN (answered by customer Q&amp;A #19) - fulfilment status vs approve/reject (Kristen's comment on the ticket): venue booking has request then approve/reject (SPM-42 then SPM-43), but equipment goes record, check, reserve (SPM-47, 48, 49) with fulfilment statuses. Every story in the SPM-47 to SPM-50 chain is written against the fulfilment-status model, so switching would mean revisiting ACs on shipped stories. Team to confirm the divergence is intentional; meanwhile these cases follow the model already used across the chain. Customer Q&amp;A #19 asked whether equipment has a formal request → approval workflow like venue booking: the answer is that the Coordinator records the requirement, Technical Support reviews suitability and availability, and available equipment can then be reserved - no approval step.</t>
+        </is>
+      </c>
+      <c r="C6" s="28" t="n"/>
+    </row>
+    <row r="7" ht="166" customHeight="1" s="22">
+      <c r="A7" s="28" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="28" t="inlineStr">
+        <is>
+          <t>DECIDED (Kristen, 3 Oct, following the BPMN) - Technical Support sees an event's equipment only in Planning and Confirmed (TECH_SUPPORT_EQUIPMENT_STATUSES): the BPMN's Technical Support lane starts after the Coordinator's 'Record equipment request', with 'Check equipment availability' and 'Reserve equipment' in Planning and 'Prepare equipment' in Confirmed. Checking, reserving and updating happen in Planning only; Confirmed is read-only (TC13). Before Planning - including Approved, when the Coordinator has not started - and after it (postponed, cancelled, rejected, completed) the event is not listed and a direct link says it is not found (TC14). Not in SPM-48/49/50's ACs: a process alignment, applied to all three; supersedes the earlier 'Approved onwards' rule and the Reserve gap.</t>
+        </is>
+      </c>
+      <c r="C7" s="28" t="n"/>
+    </row>
+    <row r="8" ht="98.5" customHeight="1" s="22">
+      <c r="A8" s="28" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="28" t="inlineStr">
+        <is>
+          <t>DECIDED (Janelle, 2 Oct) - labels: the request status 'unavailable' is shown as 'Cannot be provided' (Technical Support's decision) and the availability result 'unavailable' as 'None available' (no stock free for those dates), so the two never read the same on one line. Only the displayed text changed; the stored value is still 'unavailable'. Differs from the S-25 mockup, which says 'Unavailable'. SPM-48/49 expected results updated to match.</t>
+        </is>
+      </c>
+      <c r="C8" s="28" t="n"/>
+    </row>
+    <row r="9" ht="85" customHeight="1" s="22">
+      <c r="A9" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="28" t="inlineStr">
+        <is>
+          <t>DECIDED - hand-pickable statuses (TC02, TC03): 'Reserved' and 'Partially fulfilled' are set only by the Reserve button, which keeps Reserved = the smaller of requested and available everywhere (the SPM-49 rule). 'Requested' can be chosen to undo 'Under review'. A Reserved or Partially fulfilled line cannot be moved back to 'Requested' or 'Under review'; leaving it goes through 'Cannot be provided' with a reason.</t>
+        </is>
+      </c>
+      <c r="C9" s="28" t="n"/>
+    </row>
+    <row r="10" ht="44.5" customHeight="1" s="22">
+      <c r="A10" s="28" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="28" t="inlineStr">
+        <is>
+          <t>DECIDED - reason for 'Cannot be provided' (TC06, TC09): required, as Q&amp;A #90 needs text the Coordinator can act on. Technical notes are capped at 500 characters to match SPM-55's out-of-service reason.</t>
+        </is>
+      </c>
+      <c r="C10" s="28" t="n"/>
+    </row>
+    <row r="11" ht="112" customHeight="1" s="22">
+      <c r="A11" s="28" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="28" t="inlineStr">
+        <is>
+          <t>DECIDED - releasing stock when a line is marked 'Cannot be provided' (TC07): availability counts only lines with status 'reserved' or 'partially_fulfilled' (committedQuantity in src/lib/equipmentAvailability.ts), so the status change alone frees the units, whatever is left in quantityReserved. TC07 therefore checks the other event's availability, not the stored field. Clearing quantityReserved when marking 'Cannot be provided' is still recommended as data hygiene, so no row reads 'unavailable' with 1 reserved, but it is not needed for correctness.</t>
+        </is>
+      </c>
+      <c r="C11" s="28" t="n"/>
+    </row>
+    <row r="12" ht="58" customHeight="1" s="22">
+      <c r="A12" s="28" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="28" t="inlineStr">
+        <is>
+          <t>DECIDED - technical notes storage (TC08, TC10): stored in the existing EquipmentRequest.staffNotes column, separate from the Coordinator's technicalRequirements. The assigned Coordinator and the owning Organiser see them read-only.</t>
+        </is>
+      </c>
+      <c r="C12" s="28" t="n"/>
+    </row>
+    <row r="13" ht="44.5" customHeight="1" s="22">
+      <c r="A13" s="28" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="28" t="inlineStr">
+        <is>
+          <t>ANSWERED, out of scope - notifying the Coordinator when an item is marked 'Cannot be provided' belongs to the batched notification story, so no case is written here (same position as SPM-49).</t>
+        </is>
+      </c>
+      <c r="C13" s="28" t="n"/>
+    </row>
+    <row r="14" ht="44.5" customHeight="1" s="22">
+      <c r="A14" s="28" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="28" t="inlineStr">
+        <is>
+          <t>BUILT (AC1) - the Equipment request page now shows each line's 'Technical requirements' from the Coordinator, 'Technical Support notes', and 'Last updated by' (TC01, TC08, TC08).</t>
+        </is>
+      </c>
+      <c r="C14" s="28" t="n"/>
+    </row>
+    <row r="15" ht="85" customHeight="1" s="22">
+      <c r="A15" s="28" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="28" t="inlineStr">
+        <is>
+          <t>Test data - `npm run fixtures:spm50` (scripts/seed-spm50.ts) creates or resets the SPM-50 events: Robotics Expo, Design Week, Charity Briefing, Charity Gala, Confirmed Launch, Pending Showcase and Approved Briefing (Aug-Sep 2027, assigned Coordinator daniel.tan, Robotics Expo owned by Rachel Ng). prisma/seed.ts creates the same rows. Run the script again before repeating any case that saves a change.</t>
+        </is>
+      </c>
+      <c r="C15" s="28" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -10948,43 +11144,41 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
-        <is>
-          <t>SPM-50-TC02</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="84.75" customHeight="1" s="22">
+      <c r="B2" s="26" t="inlineStr">
+        <is>
+          <t>SPM-50-TC01</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="125.25" customHeight="1" s="22">
       <c r="A3" s="6" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>Robotics Expo's Wireless Presenter line has status 'Requested' and nothing reserved.
-Data: run `npm run fixtures:spm50` first, and again before repeating the case.
+      <c r="B3" s="26" t="inlineStr">
+        <is>
+          <t>Event 'Robotics Expo' (2027-08-02, status 'Planning') has two equipment lines recorded by its Coordinator:
+- 2x Wireless Presenter, technical requirements 'Must pair with the stage laptop over USB-C'
+- 3x Confidence Monitor, technical requirements 'Floor wedges facing the speaker, HDMI from the lectern'
+Data: run `npm run fixtures:spm50` first.
 Logged in as Technical Support Staff (vikram.nair@connectsphere.com, password123).</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="125.25" customHeight="1" s="22">
+    <row r="4" ht="71.25" customHeight="1" s="22">
       <c r="A4" s="6" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="26" t="inlineStr">
         <is>
           <t>1. Click Equipment Requests in the side menu
-2. Open the equipment request for the Robotics Expo event
-3. On the Wireless Presenter line, click 'Update'
-4. In 'Fulfilment status', choose 'Under review'
-5. Click 'Save'
-6. Refresh the page
-7. On the Wireless Presenter line, click 'Update' again
-8. In 'Fulfilment status', choose 'Requested'
-9. Click 'Save'</t>
+2. Find the Robotics Expo row in the list
+3. Open the equipment request for the Robotics Expo event
+4. Read the Wireless Presenter line
+5. Read the Confidence Monitor line</t>
         </is>
       </c>
     </row>
@@ -10994,25 +11188,25 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>Line: Wireless Presenter
-Fulfilment status: Requested -&gt; Under review -&gt; Requested</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="125.25" customHeight="1" s="22">
+      <c r="B5" s="26" t="inlineStr">
+        <is>
+          <t>Event: Robotics Expo
+Lines: Wireless Presenter x2, Confidence Monitor x3</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="138.75" customHeight="1" s="22">
       <c r="A6" s="6" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>Step 3: The Fulfilment status and Technical notes fields appear on the Wireless Presenter line, with Fulfilment status showing 'Requested'.
-Step 5: A confirmation 'Update saved.' appears on the line and its Status chip shows 'Under review'.
-Step 6: The Status chip still shows 'Under review'. The Confidence Monitor line is unchanged.
-Step 9: 'Update saved.' appears and the Status chip shows 'Requested' again. The Reserve button is still offered.</t>
+      <c r="B6" s="26" t="inlineStr">
+        <is>
+          <t>Step 2: The Robotics Expo row shows 'Equipment lines' = 2.
+Step 3: The Equipment request page opens with the heading 'Equipment request' and the subtitle 'Robotics Expo · ' followed by the event's date and time.
+Step 4: The line shows 'Wireless Presenter', Requested 2, its Status chip, and 'Technical requirements: Must pair with the stage laptop over USB-C'.
+Step 5: The line shows 'Confidence Monitor', Requested 3, its Status chip, and 'Technical requirements: Floor wedges facing the speaker, HDMI from the lectern'.</t>
         </is>
       </c>
     </row>
@@ -11022,7 +11216,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="26" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -11054,12 +11248,12 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>Step 3: The Fulfilment status and Technical notes fields appear on the Wireless Presenter line, with Fulfilment status showing 'Requested'.
-Step 5: A confirmation 'Update saved.' appears on the line and its Status chip shows 'Under review'.
-Step 6: The Status chip still shows 'Under review'. The Confidence Monitor line is unchanged.
-Step 9: 'Update saved.' appears and the Status chip shows 'Requested' again. The Reserve button is still offered.</t>
+      <c r="B11" s="26" t="inlineStr">
+        <is>
+          <t>Step 2: The Robotics Expo row shows 'Equipment lines' = 2.
+Step 3: The Equipment request page opens with the heading 'Equipment request' and the subtitle 'Robotics Expo · ' followed by the event's date and time.
+Step 4: The line shows 'Wireless Presenter', Requested 2, its Status chip, and 'Technical requirements: Must pair with the stage laptop over USB-C'.
+Step 5: The line shows 'Confidence Monitor', Requested 3, its Status chip, and 'Technical requirements: Floor wedges facing the speaker, HDMI from the lectern'.</t>
         </is>
       </c>
     </row>
@@ -11124,12 +11318,12 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="13" t="inlineStr">
-        <is>
-          <t>Step 3: The Fulfilment status and Technical notes fields appear on the Wireless Presenter line, with Fulfilment status showing 'Requested'.
-Step 5: A confirmation 'Update saved.' appears on the line and its Status chip shows 'Under review'.
-Step 6: The Status chip still shows 'Under review'. The Confidence Monitor line is unchanged.
-Step 9: 'Update saved.' appears and the Status chip shows 'Requested' again. The Reserve button is still offered.</t>
+      <c r="B18" s="26" t="inlineStr">
+        <is>
+          <t>Step 2: The Robotics Expo row shows 'Equipment lines' = 2.
+Step 3: The Equipment request page opens with the heading 'Equipment request' and the subtitle 'Robotics Expo · ' followed by the event's date and time.
+Step 4: The line shows 'Wireless Presenter', Requested 2, its Status chip, and 'Technical requirements: Must pair with the stage laptop over USB-C'.
+Step 5: The line shows 'Confidence Monitor', Requested 3, its Status chip, and 'Technical requirements: Floor wedges facing the speaker, HDMI from the lectern'.</t>
         </is>
       </c>
     </row>
@@ -12191,42 +12385,43 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
-        <is>
-          <t>SPM-50-TC03</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="152.25" customHeight="1" s="22">
+      <c r="B2" s="26" t="inlineStr">
+        <is>
+          <t>SPM-50-TC02</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="84.75" customHeight="1" s="22">
       <c r="A3" s="6" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>Rule (team decision): 'Reserved' and 'Partially fulfilled' mean stock is held, so only the Reserve button (SPM-49), which checks availability, can set them. Leaving them releases stock, so a reserved line can only be marked 'Cannot be provided' (with a reason, TC07).
-Robotics Expo's Wireless Presenter line is 'Requested'. Charity Briefing's Mobile Charging Cart line is 'Reserved' (Reserved = 1).
-Data: run `npm run fixtures:spm50` first.
+      <c r="B3" s="26" t="inlineStr">
+        <is>
+          <t>Robotics Expo's Wireless Presenter line has status 'Requested' and nothing reserved.
+Data: run `npm run fixtures:spm50` first, and again before repeating the case.
 Logged in as Technical Support Staff (vikram.nair@connectsphere.com, password123).</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="111.75" customHeight="1" s="22">
+    <row r="4" ht="125.25" customHeight="1" s="22">
       <c r="A4" s="6" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>1. Open the equipment request for the Robotics Expo event
-2. On the Wireless Presenter line, click 'Update'
-3. Open the 'Fulfilment status' list. It should offer exactly three options: Requested, Under review and Cannot be provided. "Reserved" and "Partially fulfilled" should not be there.
-4. Click 'Cancel'
-5. Click Equipment Requests and open the Charity Briefing event
-6. On the Mobile Charging Cart line, click 'Update'
-7. Open the 'Fulfilment status' list</t>
+      <c r="B4" s="26" t="inlineStr">
+        <is>
+          <t>1. Click Equipment Requests in the side menu
+2. Open the equipment request for the Robotics Expo event
+3. On the Wireless Presenter line, click 'Update'
+4. In 'Fulfilment status', choose 'Under review'
+5. Click 'Save'
+6. Refresh the page
+7. On the Wireless Presenter line, click 'Update' again
+8. In 'Fulfilment status', choose 'Requested'
+9. Click 'Save'</t>
         </is>
       </c>
     </row>
@@ -12236,22 +12431,25 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>Lines: Wireless Presenter (Requested), Mobile Charging Cart (Reserved, Reserved = 1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="84.75" customHeight="1" s="22">
+      <c r="B5" s="26" t="inlineStr">
+        <is>
+          <t>Line: Wireless Presenter
+Fulfilment status: Requested -&gt; Under review -&gt; Requested</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="125.25" customHeight="1" s="22">
       <c r="A6" s="6" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>Step 3: The list offers 'Requested', 'Under review' and 'Cannot be provided' only. 'Reserved' and 'Partially fulfilled' are not offered. The Reserve button remains on the line.
-Step 7: The list offers 'Reserved' (the current status) and 'Cannot be provided' only. 'Requested' and 'Under review' are not offered.</t>
+      <c r="B6" s="26" t="inlineStr">
+        <is>
+          <t>Step 3: The Fulfilment status and Technical notes fields appear on the Wireless Presenter line, with Fulfilment status showing 'Requested'.
+Step 5: A confirmation 'Update saved.' appears on the line and its Status chip shows 'Under review'.
+Step 6: The Status chip still shows 'Under review'. The Confidence Monitor line is unchanged.
+Step 9: 'Update saved.' appears and the Status chip shows 'Requested' again. The Reserve button is still offered.</t>
         </is>
       </c>
     </row>
@@ -12261,7 +12459,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="26" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -12293,10 +12491,12 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>Step 3: The list offers 'Requested', 'Under review' and 'Cannot be provided' only. 'Reserved' and 'Partially fulfilled' are not offered. The Reserve button remains on the line.
-Step 7: The list offers 'Reserved' (the current status) and 'Cannot be provided' only. 'Requested' and 'Under review' are not offered.</t>
+      <c r="B11" s="26" t="inlineStr">
+        <is>
+          <t>Step 3: The Fulfilment status and Technical notes fields appear on the Wireless Presenter line, with Fulfilment status showing 'Requested'.
+Step 5: A confirmation 'Update saved.' appears on the line and its Status chip shows 'Under review'.
+Step 6: The Status chip still shows 'Under review'. The Confidence Monitor line is unchanged.
+Step 9: 'Update saved.' appears and the Status chip shows 'Requested' again. The Reserve button is still offered.</t>
         </is>
       </c>
     </row>
@@ -12361,10 +12561,12 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="13" t="inlineStr">
-        <is>
-          <t>Step 3: The list offers 'Requested', 'Under review' and 'Cannot be provided' only. 'Reserved' and 'Partially fulfilled' are not offered. The Reserve button remains on the line.
-Step 7: The list offers 'Reserved' (the current status) and 'Cannot be provided' only. 'Requested' and 'Under review' are not offered.</t>
+      <c r="B18" s="26" t="inlineStr">
+        <is>
+          <t>Step 3: The Fulfilment status and Technical notes fields appear on the Wireless Presenter line, with Fulfilment status showing 'Requested'.
+Step 5: A confirmation 'Update saved.' appears on the line and its Status chip shows 'Under review'.
+Step 6: The Status chip still shows 'Under review'. The Confidence Monitor line is unchanged.
+Step 9: 'Update saved.' appears and the Status chip shows 'Requested' again. The Reserve button is still offered.</t>
         </is>
       </c>
     </row>
@@ -13426,64 +13628,67 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
-        <is>
-          <t>SPM-50-TC04</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="98.25" customHeight="1" s="22">
+      <c r="B2" s="26" t="inlineStr">
+        <is>
+          <t>SPM-50-TC03</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="152.25" customHeight="1" s="22">
       <c r="A3" s="6" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>Event 'Design Week' (2027-08-16, status 'Planning') has a 'Ring Light' x2 line already marked 'Cannot be provided' with technical notes 'Both units out for repair'.
-Data: run `npm run fixtures:spm50` first, and again before repeating the case.
+      <c r="B3" s="26" t="inlineStr">
+        <is>
+          <t>Rule (team decision): 'Reserved' and 'Partially fulfilled' mean stock is held, so only the Reserve button (SPM-49), which checks availability, can set them. Leaving them releases stock, so a reserved line can only be marked 'Cannot be provided' (with a reason, TC07).
+Robotics Expo's Wireless Presenter line is 'Requested'. Charity Briefing's Mobile Charging Cart line is 'Reserved' (Reserved = 1).
+Data: run `npm run fixtures:spm50` first.
 Logged in as Technical Support Staff (vikram.nair@connectsphere.com, password123).</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="71.25" customHeight="1" s="22">
+    <row r="4" ht="111.75" customHeight="1" s="22">
       <c r="A4" s="6" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>1. Open the equipment request for the Design Week event
-2. On the Ring Light line, click 'Update'
-3. In 'Fulfilment status', choose 'Under review'
-4. In 'Technical notes', replace the text with 'Repair finished early, re-checking availability'.
-5. Click 'Save'</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="44.25" customHeight="1" s="22">
+      <c r="B4" s="26" t="inlineStr">
+        <is>
+          <t>1. Open the equipment request for the Robotics Expo event
+2. On the Wireless Presenter line, click 'Update'
+3. Open the 'Fulfilment status' list. It should offer exactly three options: Requested, Under review and Cannot be provided. "Reserved" and "Partially fulfilled" should not be there.
+4. Click 'Cancel'
+5. Click Equipment Requests and open the Charity Briefing event
+6. On the Mobile Charging Cart line, click 'Update'
+7. Open the 'Fulfilment status' list</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30.75" customHeight="1" s="22">
       <c r="A5" s="6" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>Fulfilment status: Cannot be provided -&gt; Under review
-Technical notes: Repair finished early, re-checking availability</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="44.25" customHeight="1" s="22">
+      <c r="B5" s="26" t="inlineStr">
+        <is>
+          <t>Lines: Wireless Presenter (Requested), Mobile Charging Cart (Reserved, Reserved = 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="84.75" customHeight="1" s="22">
       <c r="A6" s="6" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>Step 5: 'Update saved.' appears. The Status chip shows 'Under review' and the line's technical notes read 'Repair finished early, re-checking availability'.</t>
+      <c r="B6" s="26" t="inlineStr">
+        <is>
+          <t>Step 3: The list offers 'Requested', 'Under review' and 'Cannot be provided' only. 'Reserved' and 'Partially fulfilled' are not offered. The Reserve button remains on the line.
+Step 7: The list offers 'Reserved' (the current status) and 'Cannot be provided' only. 'Requested' and 'Under review' are not offered.</t>
         </is>
       </c>
     </row>
@@ -13493,7 +13698,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="26" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -13525,9 +13730,10 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>The row moves to the bottom.Step 5: 'Update saved.' appears. The Status chip shows 'Under review' and the line's technical notes read 'Repair finished early, re-checking availability'.</t>
+      <c r="B11" s="26" t="inlineStr">
+        <is>
+          <t>Step 3: The list offers 'Requested', 'Under review' and 'Cannot be provided' only. 'Reserved' and 'Partially fulfilled' are not offered. The Reserve button remains on the line.
+Step 7: The list offers 'Reserved' (the current status) and 'Cannot be provided' only. 'Requested' and 'Under review' are not offered.</t>
         </is>
       </c>
     </row>
@@ -13592,9 +13798,10 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="13" t="inlineStr">
-        <is>
-          <t>Step 5: 'Update saved.' appears. The Status chip shows 'Under review' and the line's technical notes read 'Repair finished early, re-checking availability'.</t>
+      <c r="B18" s="26" t="inlineStr">
+        <is>
+          <t>Step 3: The list offers 'Requested', 'Under review' and 'Cannot be provided' only. 'Reserved' and 'Partially fulfilled' are not offered. The Reserve button remains on the line.
+Step 7: The list offers 'Reserved' (the current status) and 'Cannot be provided' only. 'Requested' and 'Under review' are not offered.</t>
         </is>
       </c>
     </row>
@@ -14656,41 +14863,39 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
-        <is>
-          <t>SPM-50-TC05</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="84.75" customHeight="1" s="22">
+      <c r="B2" s="26" t="inlineStr">
+        <is>
+          <t>SPM-50-TC04</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="98.25" customHeight="1" s="22">
       <c r="A3" s="6" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>Robotics Expo's Confidence Monitor line is 'Requested' with nothing reserved.
+      <c r="B3" s="26" t="inlineStr">
+        <is>
+          <t>Event 'Design Week' (2027-08-16, status 'Planning') has a 'Ring Light' x2 line already marked 'Cannot be provided' with technical notes 'Both units out for repair'.
 Data: run `npm run fixtures:spm50` first, and again before repeating the case.
 Logged in as Technical Support Staff (vikram.nair@connectsphere.com, password123).</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="98.25" customHeight="1" s="22">
+    <row r="4" ht="71.25" customHeight="1" s="22">
       <c r="A4" s="6" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>1. Open the equipment request for the Robotics Expo event
-2. On the Confidence Monitor line, click 'Update'
-3. In 'Fulfilment status', choose 'Cannot be provided'
-4. In 'Technical notes', enter Only 1 working unit; suggest 2x 55-inch TV on stands as an alternative'
-5. Click 'Save'
-6. Refresh the page
-7. Read the Wireless Presenter line</t>
+      <c r="B4" s="26" t="inlineStr">
+        <is>
+          <t>1. Open the equipment request for the Design Week event
+2. On the Ring Light line, click 'Update'
+3. In 'Fulfilment status', choose 'Under review'
+4. In 'Technical notes', replace the text with 'Repair finished early, re-checking availability'.
+5. Click 'Save'</t>
         </is>
       </c>
     </row>
@@ -14700,24 +14905,22 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>Fulfilment status: Cannot be provided
-Technical notes: Only 1 working unit; suggest 2x 55-inch TV on stands as an alternative</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="138.75" customHeight="1" s="22">
+      <c r="B5" s="26" t="inlineStr">
+        <is>
+          <t>Fulfilment status: Cannot be provided -&gt; Under review
+Technical notes: Repair finished early, re-checking availability</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="44.25" customHeight="1" s="22">
       <c r="A6" s="6" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>Step 5: 'Update saved.' appears. The Status chip shows 'Cannot be provided' (red).
-Step 6: The Status chip still shows 'Cannot be provided' and the notes 'Only 1 working unit; suggest 2x 55-inch TV on stands as an alternative' are shown on the line after 'Technical Support notes:'.
-Step 7: The Wireless Presenter line still shows the Status chip 'Requested' and no Technical Support notes. Because the lines are no longer at the same stage, the 'Requested items' header shows no single status chip.</t>
+      <c r="B6" s="26" t="inlineStr">
+        <is>
+          <t>Step 5: 'Update saved.' appears. The Status chip shows 'Under review' and the line's technical notes read 'Repair finished early, re-checking availability'.</t>
         </is>
       </c>
     </row>
@@ -14727,7 +14930,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="26" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -14759,11 +14962,9 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>Step 5: 'Update saved.' appears. The Status chip shows 'Cannot be provided' (red).
-Step 6: The Status chip still shows 'Cannot be provided' and the notes 'Only 1 working unit; suggest 2x 55-inch TV on stands as an alternative' are shown on the line after 'Technical Support notes:'.
-Step 7: The Wireless Presenter line still shows the Status chip 'Requested' and no Technical Support notes. Because the lines are no longer at the same stage, the 'Requested items' header shows no single status chip.</t>
+      <c r="B11" s="26" t="inlineStr">
+        <is>
+          <t>The row moves to the bottom.Step 5: 'Update saved.' appears. The Status chip shows 'Under review' and the line's technical notes read 'Repair finished early, re-checking availability'.</t>
         </is>
       </c>
     </row>
@@ -14828,11 +15029,9 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="13" t="inlineStr">
-        <is>
-          <t>Step 5: 'Update saved.' appears. The Status chip shows 'Cannot be provided' (red).
-Step 6: The Status chip still shows 'Cannot be provided' and the notes 'Only 1 working unit; suggest 2x 55-inch TV on stands as an alternative' are shown on the line after 'Technical Support notes:'.
-Step 7: The Wireless Presenter line still shows the Status chip 'Requested' and no Technical Support notes. Because the lines are no longer at the same stage, the 'Requested items' header shows no single status chip.</t>
+      <c r="B18" s="26" t="inlineStr">
+        <is>
+          <t>Step 5: 'Update saved.' appears. The Status chip shows 'Under review' and the line's technical notes read 'Repair finished early, re-checking availability'.</t>
         </is>
       </c>
     </row>
@@ -15894,9 +16093,9 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
-        <is>
-          <t>SPM-50-TC06</t>
+      <c r="B2" s="26" t="inlineStr">
+        <is>
+          <t>SPM-50-TC05</t>
         </is>
       </c>
     </row>
@@ -15906,10 +16105,10 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>Rule (team decision): a reason is required when equipment cannot be provided, so the Coordinator knows why and can plan around it (Q&amp;A #90).
-Robotics Expo's Confidence Monitor line is 'Requested'.
+      <c r="B3" s="26" t="inlineStr">
+        <is>
+          <t>Robotics Expo's Confidence Monitor line is 'Requested' with nothing reserved.
+Data: run `npm run fixtures:spm50` first, and again before repeating the case.
 Logged in as Technical Support Staff (vikram.nair@connectsphere.com, password123).</t>
         </is>
       </c>
@@ -15920,41 +16119,42 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="26" t="inlineStr">
         <is>
           <t>1. Open the equipment request for the Robotics Expo event
 2. On the Confidence Monitor line, click 'Update'
 3. In 'Fulfilment status', choose 'Cannot be provided'
-4. Leave 'Technical notes' empty
+4. In 'Technical notes', enter Only 1 working unit; suggest 2x 55-inch TV on stands as an alternative'
 5. Click 'Save'
-6. In 'Technical notes', type three spaces
-7. Click 'Save'</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30.75" customHeight="1" s="22">
+6. Refresh the page
+7. Read the Wireless Presenter line</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="44.25" customHeight="1" s="22">
       <c r="A5" s="6" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="26" t="inlineStr">
         <is>
           <t>Fulfilment status: Cannot be provided
-Technical notes: (empty), then '   ' (3 spaces)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="84.75" customHeight="1" s="22">
+Technical notes: Only 1 working unit; suggest 2x 55-inch TV on stands as an alternative</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="138.75" customHeight="1" s="22">
       <c r="A6" s="6" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>Step 5: The error 'Give a reason when equipment cannot be provided.' is shown under Technical notes. Nothing is saved
-Step 7: The same error is shown, because a reason made only of spaces counts as empty. Nothing is saved</t>
+      <c r="B6" s="26" t="inlineStr">
+        <is>
+          <t>Step 5: 'Update saved.' appears. The Status chip shows 'Cannot be provided' (red).
+Step 6: The Status chip still shows 'Cannot be provided' and the notes 'Only 1 working unit; suggest 2x 55-inch TV on stands as an alternative' are shown on the line after 'Technical Support notes:'.
+Step 7: The Wireless Presenter line still shows the Status chip 'Requested' and no Technical Support notes. Because the lines are no longer at the same stage, the 'Requested items' header shows no single status chip.</t>
         </is>
       </c>
     </row>
@@ -15964,7 +16164,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="26" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -15996,10 +16196,11 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>Step 5: The error 'Give a reason when equipment cannot be provided.' is shown under Technical notes. Nothing is saved
-Step 7: The same error is shown, because a reason made only of spaces counts as empty. Nothing is saved</t>
+      <c r="B11" s="26" t="inlineStr">
+        <is>
+          <t>Step 5: 'Update saved.' appears. The Status chip shows 'Cannot be provided' (red).
+Step 6: The Status chip still shows 'Cannot be provided' and the notes 'Only 1 working unit; suggest 2x 55-inch TV on stands as an alternative' are shown on the line after 'Technical Support notes:'.
+Step 7: The Wireless Presenter line still shows the Status chip 'Requested' and no Technical Support notes. Because the lines are no longer at the same stage, the 'Requested items' header shows no single status chip.</t>
         </is>
       </c>
     </row>
@@ -16064,10 +16265,11 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="13" t="inlineStr">
-        <is>
-          <t>Step 5: The error 'Give a reason when equipment cannot be provided.' is shown under Technical notes. Nothing is saved
-Step 7: The same error is shown, because a reason made only of spaces counts as empty. Nothing is saved</t>
+      <c r="B18" s="26" t="inlineStr">
+        <is>
+          <t>Step 5: 'Update saved.' appears. The Status chip shows 'Cannot be provided' (red).
+Step 6: The Status chip still shows 'Cannot be provided' and the notes 'Only 1 working unit; suggest 2x 55-inch TV on stands as an alternative' are shown on the line after 'Technical Support notes:'.
+Step 7: The Wireless Presenter line still shows the Status chip 'Requested' and no Technical Support notes. Because the lines are no longer at the same stage, the 'Requested items' header shows no single status chip.</t>
         </is>
       </c>
     </row>
@@ -17129,75 +17331,67 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
-        <is>
-          <t>SPM-50-TC07</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="165.75" customHeight="1" s="22">
+      <c r="B2" s="26" t="inlineStr">
+        <is>
+          <t>SPM-50-TC06</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="84.75" customHeight="1" s="22">
       <c r="A3" s="6" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>Rule: only lines with status 'Reserved' or 'Partially fulfilled' count against stock, so changing the status to 'Cannot be provided' frees the units by itself.
-'Mobile Charging Cart' has 1 unit in total.
-Event 'Charity Briefing' (2027-08-23) has 1x Mobile Charging Cart already 'Reserved' (Reserved = 1).
-Event 'Charity Gala' (same date, overlapping times) requests 1x Mobile Charging Cart, status 'Requested'.
-Data: run `npm run fixtures:spm50` first, and again before repeating the case.
+      <c r="B3" s="26" t="inlineStr">
+        <is>
+          <t>Rule (team decision): a reason is required when equipment cannot be provided, so the Coordinator knows why and can plan around it (Q&amp;A #90).
+Robotics Expo's Confidence Monitor line is 'Requested'.
 Logged in as Technical Support Staff (vikram.nair@connectsphere.com, password123).</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="152.25" customHeight="1" s="22">
+    <row r="4" ht="98.25" customHeight="1" s="22">
       <c r="A4" s="6" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>1. Open the equipment request for the Charity Gala event
-2. Read the Mobile Charging Cart line
-3. Click Equipment Requests in the breadcrumb and open the Charity Briefing event
-4. On the Mobile Charging Cart line, click 'Update'
-5. In 'Fulfilment status', choose 'Cannot be provided'
-6. In 'Technical notes', enter the test data
-7. Click 'Save'
-8. Go back to the Charity Gala equipment request
-9. Go back to the Charity Briefing equipment request
-10. Click Reserve on the Mobile Charging Cart line</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="44.25" customHeight="1" s="22">
+      <c r="B4" s="26" t="inlineStr">
+        <is>
+          <t>1. Open the equipment request for the Robotics Expo event
+2. On the Confidence Monitor line, click 'Update'
+3. In 'Fulfilment status', choose 'Cannot be provided'
+4. Leave 'Technical notes' empty
+5. Click 'Save'
+6. In 'Technical notes', type three spaces
+7. Click 'Save'</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30.75" customHeight="1" s="22">
       <c r="A5" s="6" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>Technical notes: Cart battery failed inspection, cannot be sent out
-Mobile Charging Cart: 1 in total</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="206.25" customHeight="1" s="22">
+      <c r="B5" s="26" t="inlineStr">
+        <is>
+          <t>Fulfilment status: Cannot be provided
+Technical notes: (empty), then '   ' (3 spaces)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="84.75" customHeight="1" s="22">
       <c r="A6" s="6" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>Step 2: Charity Gala's line shows '1 total − 0 in maintenance − 1 reserved elsewhere = 0 available' and the Availability chip 'None available', with 'Held by Charity Briefing (1 unit)'.
-Step 7: Charity Briefing's line shows the Status chip 'Cannot be provided'.
-Step 8: Charity Gala's line now shows '1 total − 0 in maintenance − 0 reserved elsewhere = 1 available' with the Availability chip 'Available'. Charity Briefing is no longer listed as holding it, and the Reserve button is offered.
-Step 10: 'Reservation saved: 1 reserved.' appears. The Status chip shows 'Reserved', the Reserved box shows 1, and the line shows 'Technical Support notes: —': the old reason 'Cart battery failed inspection, cannot be sent out' is cleared, because it no longer holds.</t>
+      <c r="B6" s="26" t="inlineStr">
+        <is>
+          <t>Step 5: The error 'Give a reason when equipment cannot be provided.' is shown under Technical notes. Nothing is saved
+Step 7: The same error is shown, because a reason made only of spaces counts as empty. Nothing is saved</t>
         </is>
       </c>
     </row>
@@ -17207,7 +17401,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="26" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -17239,12 +17433,10 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>Step 2: Charity Gala's line shows '1 total − 0 in maintenance − 1 reserved elsewhere = 0 available' and the Availability chip 'None available', with 'Held by Charity Briefing (1 unit)'.
-Step 7: Charity Briefing's line shows the Status chip 'Cannot be provided'.
-Step 8: Charity Gala's line now shows '1 total − 0 in maintenance − 0 reserved elsewhere = 1 available' with the Availability chip 'Available'. Charity Briefing is no longer listed as holding it, and the Reserve button is offered.
-Step 10: 'Reservation saved: 1 reserved.' appears. The Status chip shows 'Reserved', the Reserved box shows 1, and the line shows 'Technical Support notes: —': the old reason 'Cart battery failed inspection, cannot be sent out' is cleared, because it no longer holds.</t>
+      <c r="B11" s="26" t="inlineStr">
+        <is>
+          <t>Step 5: The error 'Give a reason when equipment cannot be provided.' is shown under Technical notes. Nothing is saved
+Step 7: The same error is shown, because a reason made only of spaces counts as empty. Nothing is saved</t>
         </is>
       </c>
     </row>
@@ -17309,12 +17501,10 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="13" t="inlineStr">
-        <is>
-          <t>Step 2: Charity Gala's line shows '1 total − 0 in maintenance − 1 reserved elsewhere = 0 available' and the Availability chip 'None available', with 'Held by Charity Briefing (1 unit)'.
-Step 7: Charity Briefing's line shows the Status chip 'Cannot be provided'.
-Step 8: Charity Gala's line now shows '1 total − 0 in maintenance − 0 reserved elsewhere = 1 available' with the Availability chip 'Available'. Charity Briefing is no longer listed as holding it, and the Reserve button is offered.
-Step 10: 'Reservation saved: 1 reserved.' appears. The Status chip shows 'Reserved', the Reserved box shows 1, and the line shows 'Technical Support notes: —': the old reason 'Cart battery failed inspection, cannot be sent out' is cleared, because it no longer holds.</t>
+      <c r="B18" s="26" t="inlineStr">
+        <is>
+          <t>Step 5: The error 'Give a reason when equipment cannot be provided.' is shown under Technical notes. Nothing is saved
+Step 7: The same error is shown, because a reason made only of spaces counts as empty. Nothing is saved</t>
         </is>
       </c>
     </row>
@@ -18376,69 +18566,75 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
-        <is>
-          <t>SPM-50-TC08</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="84.75" customHeight="1" s="22">
+      <c r="B2" s="26" t="inlineStr">
+        <is>
+          <t>SPM-50-TC07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="165.75" customHeight="1" s="22">
       <c r="A3" s="6" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>Robotics Expo's Wireless Presenter line is 'Requested' with no technical notes.
+      <c r="B3" s="26" t="inlineStr">
+        <is>
+          <t>Rule: only lines with status 'Reserved' or 'Partially fulfilled' count against stock, so changing the status to 'Cannot be provided' frees the units by itself.
+'Mobile Charging Cart' has 1 unit in total.
+Event 'Charity Briefing' (2027-08-23) has 1x Mobile Charging Cart already 'Reserved' (Reserved = 1).
+Event 'Charity Gala' (same date, overlapping times) requests 1x Mobile Charging Cart, status 'Requested'.
 Data: run `npm run fixtures:spm50` first, and again before repeating the case.
 Logged in as Technical Support Staff (vikram.nair@connectsphere.com, password123).</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="125.25" customHeight="1" s="22">
+    <row r="4" ht="152.25" customHeight="1" s="22">
       <c r="A4" s="6" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>1. Open the equipment request for the Robotics Expo event
-2. On the Wireless Presenter line, click 'Update'
-3. Leave 'Fulfilment status' as 'Requested'
-4. In 'Technical notes', enter "Presenters need fresh AAA batteries; USB-C dongle is in kit bag 3'
-5. Click 'Save'
-6. Refresh the page
-7. On the Wireless Presenter line, click 'Update'
-8. Delete all text in 'Technical notes'
-9. Click 'Save'</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30.75" customHeight="1" s="22">
+      <c r="B4" s="26" t="inlineStr">
+        <is>
+          <t>1. Open the equipment request for the Charity Gala event
+2. Read the Mobile Charging Cart line
+3. Click Equipment Requests in the breadcrumb and open the Charity Briefing event
+4. On the Mobile Charging Cart line, click 'Update'
+5. In 'Fulfilment status', choose 'Cannot be provided'
+6. In 'Technical notes', enter the test data
+7. Click 'Save'
+8. Go back to the Charity Gala equipment request
+9. Go back to the Charity Briefing equipment request
+10. Click Reserve on the Mobile Charging Cart line</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="44.25" customHeight="1" s="22">
       <c r="A5" s="6" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>Technical notes: Presenters need fresh AAA batteries; USB-C dongle is in kit bag 3 -&gt; (empty)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="152.25" customHeight="1" s="22">
+      <c r="B5" s="26" t="inlineStr">
+        <is>
+          <t>Technical notes: Cart battery failed inspection, cannot be sent out
+Mobile Charging Cart: 1 in total</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="206.25" customHeight="1" s="22">
       <c r="A6" s="6" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>Step 5: 'Update saved.' appears. The Status chip still shows 'Requested'.
-Step 6: The line shows 'Technical Support notes: Presenters need fresh AAA batteries; USB-C dongle is in kit bag 3', separately from 'Technical requirements: Must pair with the stage laptop over USB-C', which is unchanged. It also shows 'Last updated by Vikram Nair, ' followed by the date and time of the save (for example '2 Oct 2026, 14:05').
-Step 9: 'Update saved.' appears and the line shows 'Technical Support notes: —'. The Status chip still shows 'Requested'.</t>
+      <c r="B6" s="26" t="inlineStr">
+        <is>
+          <t>Step 2: Charity Gala's line shows '1 total − 0 in maintenance − 1 reserved elsewhere = 0 available' and the Availability chip 'None available', with 'Held by Charity Briefing (1 unit)'.
+Step 7: Charity Briefing's line shows the Status chip 'Cannot be provided'.
+Step 8: Charity Gala's line now shows '1 total − 0 in maintenance − 0 reserved elsewhere = 1 available' with the Availability chip 'Available'. Charity Briefing is no longer listed as holding it, and the Reserve button is offered.
+Step 10: 'Reservation saved: 1 reserved.' appears. The Status chip shows 'Reserved', the Reserved box shows 1, and the line shows 'Technical Support notes: —': the old reason 'Cart battery failed inspection, cannot be sent out' is cleared, because it no longer holds.</t>
         </is>
       </c>
     </row>
@@ -18448,7 +18644,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="26" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -18480,11 +18676,12 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>Step 5: 'Update saved.' appears. The Status chip still shows 'Requested'.
-Step 6: The line shows 'Technical Support notes: Presenters need fresh AAA batteries; USB-C dongle is in kit bag 3', separately from 'Technical requirements: Must pair with the stage laptop over USB-C', which is unchanged. It also shows 'Last updated by Vikram Nair, ' followed by the date and time of the save (for example '2 Oct 2026, 14:05').
-Step 9: 'Update saved.' appears and the line shows 'Technical Support notes: —'. The Status chip still shows 'Requested'.</t>
+      <c r="B11" s="26" t="inlineStr">
+        <is>
+          <t>Step 2: Charity Gala's line shows '1 total − 0 in maintenance − 1 reserved elsewhere = 0 available' and the Availability chip 'None available', with 'Held by Charity Briefing (1 unit)'.
+Step 7: Charity Briefing's line shows the Status chip 'Cannot be provided'.
+Step 8: Charity Gala's line now shows '1 total − 0 in maintenance − 0 reserved elsewhere = 1 available' with the Availability chip 'Available'. Charity Briefing is no longer listed as holding it, and the Reserve button is offered.
+Step 10: 'Reservation saved: 1 reserved.' appears. The Status chip shows 'Reserved', the Reserved box shows 1, and the line shows 'Technical Support notes: —': the old reason 'Cart battery failed inspection, cannot be sent out' is cleared, because it no longer holds.</t>
         </is>
       </c>
     </row>
@@ -18520,7 +18717,7 @@
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Janelle </t>
+          <t>Janelle</t>
         </is>
       </c>
     </row>
@@ -18549,11 +18746,12 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="13" t="inlineStr">
-        <is>
-          <t>Step 5: 'Update saved.' appears. The Status chip still shows 'Requested'.
-Step 6: The line shows 'Technical Support notes: Presenters need fresh AAA batteries; USB-C dongle is in kit bag 3', separately from 'Technical requirements: Must pair with the stage laptop over USB-C', which is unchanged. It also shows 'Last updated by Vikram Nair, ' followed by the date and time of the save (for example '2 Oct 2026, 14:05').
-Step 9: 'Update saved.' appears and the line shows 'Technical Support notes: —'. The Status chip still shows 'Requested'.</t>
+      <c r="B18" s="26" t="inlineStr">
+        <is>
+          <t>Step 2: Charity Gala's line shows '1 total − 0 in maintenance − 1 reserved elsewhere = 0 available' and the Availability chip 'None available', with 'Held by Charity Briefing (1 unit)'.
+Step 7: Charity Briefing's line shows the Status chip 'Cannot be provided'.
+Step 8: Charity Gala's line now shows '1 total − 0 in maintenance − 0 reserved elsewhere = 1 available' with the Availability chip 'Available'. Charity Briefing is no longer listed as holding it, and the Reserve button is offered.
+Step 10: 'Reservation saved: 1 reserved.' appears. The Status chip shows 'Reserved', the Reserved box shows 1, and the line shows 'Technical Support notes: —': the old reason 'Cart battery failed inspection, cannot be sent out' is cleared, because it no longer holds.</t>
         </is>
       </c>
     </row>
